--- a/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
+++ b/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eganw\ece445l_lab7-10_fall26-4-ew-js-tp-ak\sw\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghakk\ece445l_lab7-10_fall26-4-ew-js-tp-ak\sw\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF02F2B-6C6F-4D0A-9C31-4E9197103945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF195610-3F4D-44B3-9BEF-DDE3E1F20168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VSSOP-32" sheetId="1" r:id="rId1"/>
@@ -5905,19 +5905,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:XEU44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.5546875" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.08984375" style="2" customWidth="1"/>
     <col min="5" max="5" width="6" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30.36328125" customWidth="1"/>
+    <col min="8" max="8" width="5.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="G1" s="7"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>364</v>
       </c>
@@ -5951,7 +5951,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>210</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>171</v>
@@ -5991,7 +5991,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>363</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>363</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>172</v>
@@ -6052,7 +6052,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>173</v>
@@ -6071,7 +6071,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>174</v>
@@ -6090,7 +6090,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>363</v>
       </c>
@@ -6111,7 +6111,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>363</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>364</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>176</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>175</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>364</v>
       </c>
@@ -6219,7 +6219,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>134</v>
       </c>
@@ -6243,7 +6243,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>137</v>
       </c>
@@ -6267,13 +6267,13 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>324</v>
       </c>
@@ -6285,12 +6285,12 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>331</v>
       </c>
@@ -6298,7 +6298,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>332</v>
       </c>
@@ -6306,27 +6306,27 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -6334,19 +6334,19 @@
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -12491,48 +12491,48 @@
       <c r="XET31" s="2"/>
       <c r="XEU31" s="2"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B33"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B34"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B35"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B36"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B37"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B38"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="14"/>
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="15"/>
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
@@ -12547,19 +12547,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC81E62-902F-426A-8169-496CDAF34664}">
   <dimension ref="A1:XEU44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.5546875" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.08984375" style="2" customWidth="1"/>
     <col min="5" max="5" width="6" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30.36328125" customWidth="1"/>
+    <col min="8" max="8" width="5.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>369</v>
       </c>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="G1" s="7"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>364</v>
       </c>
@@ -12593,7 +12593,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
       <c r="B3" s="24" t="s">
         <v>15</v>
@@ -12612,7 +12612,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>171</v>
@@ -12631,7 +12631,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>363</v>
       </c>
@@ -12652,7 +12652,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>363</v>
       </c>
@@ -12673,7 +12673,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>172</v>
@@ -12692,7 +12692,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>173</v>
@@ -12711,7 +12711,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>174</v>
@@ -12730,7 +12730,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>372</v>
       </c>
@@ -12751,7 +12751,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>363</v>
       </c>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="G11" s="25"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>364</v>
       </c>
@@ -12791,7 +12791,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>176</v>
       </c>
@@ -12812,7 +12812,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>175</v>
       </c>
@@ -12833,7 +12833,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>364</v>
       </c>
@@ -12857,7 +12857,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>378</v>
       </c>
@@ -12881,7 +12881,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>379</v>
       </c>
@@ -12905,7 +12905,7 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>382</v>
       </c>
@@ -12913,7 +12913,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>370</v>
       </c>
@@ -12928,7 +12928,7 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>365</v>
       </c>
@@ -12953,7 +12953,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>210</v>
       </c>
@@ -12977,7 +12977,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>171</v>
@@ -12999,7 +12999,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>38</v>
@@ -13038,7 +13038,7 @@
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>172</v>
@@ -13060,7 +13060,7 @@
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>173</v>
@@ -13082,7 +13082,7 @@
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="B27" s="2" t="s">
         <v>174</v>
@@ -13104,7 +13104,7 @@
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>372</v>
       </c>
@@ -13128,7 +13128,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>10</v>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>380</v>
       </c>
@@ -13171,7 +13171,7 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
         <v>176</v>
       </c>
@@ -19327,7 +19327,7 @@
       <c r="XET31" s="2"/>
       <c r="XEU31" s="2"/>
     </row>
-    <row r="32" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
         <v>175</v>
       </c>
@@ -19348,7 +19348,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="B33" s="2" t="s">
         <v>14</v>
@@ -19367,7 +19367,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>367</v>
       </c>
@@ -19388,7 +19388,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>381</v>
       </c>
@@ -19409,45 +19409,45 @@
         <v>368</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>383</v>
       </c>
       <c r="B36"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>384</v>
       </c>
       <c r="B37"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B38"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="14"/>
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="15"/>
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
@@ -19462,22 +19462,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E972CE-2F8B-4DAB-AD48-DA87002CAF65}">
   <dimension ref="A1:O44"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" style="31" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="30" customWidth="1"/>
-    <col min="3" max="3" width="27.109375" style="30" customWidth="1"/>
+    <col min="1" max="1" width="12.90625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" style="30" customWidth="1"/>
+    <col min="3" max="3" width="27.08984375" style="30" customWidth="1"/>
     <col min="4" max="4" width="14" style="30" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" style="30" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" style="30" customWidth="1"/>
     <col min="6" max="6" width="24" style="30" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" style="30" customWidth="1"/>
-    <col min="8" max="8" width="29.6640625" style="30" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" style="30" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" style="36"/>
-    <col min="11" max="16384" width="9.109375" style="30"/>
+    <col min="7" max="7" width="12.6328125" style="30" customWidth="1"/>
+    <col min="8" max="8" width="29.6328125" style="30" customWidth="1"/>
+    <col min="9" max="9" width="14.36328125" style="30" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="36"/>
+    <col min="11" max="16384" width="9.08984375" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="I1" s="30" t="s">
         <v>350</v>
       </c>
@@ -19485,7 +19485,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="I2" s="30">
         <f>SUM(I4:I51)</f>
         <v>36.134999999999998</v>
@@ -19495,7 +19495,7 @@
         <v>83.68</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="31" t="s">
         <v>190</v>
       </c>
@@ -19530,7 +19530,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="31">
         <v>2</v>
       </c>
@@ -19557,7 +19557,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="31">
         <v>2</v>
       </c>
@@ -19590,7 +19590,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="31">
         <v>1</v>
       </c>
@@ -19617,7 +19617,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="31">
         <v>2</v>
       </c>
@@ -19644,7 +19644,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="31">
         <v>1</v>
       </c>
@@ -19677,7 +19677,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="31">
         <v>1</v>
       </c>
@@ -19704,7 +19704,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="31">
         <v>2</v>
       </c>
@@ -19734,7 +19734,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="31">
         <v>0</v>
       </c>
@@ -19764,7 +19764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="31">
         <v>1</v>
       </c>
@@ -19797,7 +19797,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="31">
         <v>1</v>
       </c>
@@ -19842,7 +19842,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="31">
         <v>0</v>
       </c>
@@ -19872,7 +19872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="31">
         <v>1</v>
       </c>
@@ -19908,7 +19908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="31">
         <v>1</v>
       </c>
@@ -19944,7 +19944,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="31">
         <v>1</v>
       </c>
@@ -19980,7 +19980,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="31">
         <v>1</v>
       </c>
@@ -20012,7 +20012,7 @@
         <v>29.81</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="31">
         <v>1</v>
       </c>
@@ -20047,7 +20047,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="31">
         <v>2</v>
       </c>
@@ -20083,7 +20083,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="31">
         <v>1</v>
       </c>
@@ -20106,7 +20106,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="31">
         <v>1</v>
       </c>
@@ -20142,7 +20142,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="31">
         <v>2</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="31">
         <v>1</v>
       </c>
@@ -20208,7 +20208,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="31">
         <v>2</v>
       </c>
@@ -20241,7 +20241,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="31">
         <v>1</v>
       </c>
@@ -20274,7 +20274,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="31">
         <v>0</v>
       </c>
@@ -20307,10 +20307,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B34" s="32"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="31">
         <v>5</v>
       </c>
@@ -20340,7 +20340,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="31">
         <v>1</v>
       </c>
@@ -20354,7 +20354,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="31">
         <v>1</v>
       </c>
@@ -20365,7 +20365,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="31">
         <v>1</v>
       </c>
@@ -20376,7 +20376,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="31">
         <v>1</v>
       </c>
@@ -20387,7 +20387,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="31">
         <v>1</v>
       </c>
@@ -20417,7 +20417,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="31">
         <v>1</v>
       </c>
@@ -20447,7 +20447,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="31">
         <v>1</v>
       </c>
@@ -20485,14 +20485,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E84313-7CEE-4179-AFC3-CFF55EB9327F}">
   <dimension ref="A1:M336"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" customWidth="1"/>
-    <col min="7" max="7" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.90625" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" customWidth="1"/>
+    <col min="7" max="7" width="17.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>69</v>
       </c>
@@ -20516,7 +20516,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -20538,7 +20538,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -20554,7 +20554,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -20588,7 +20588,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>10</v>
       </c>
@@ -20628,7 +20628,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>25</v>
       </c>
@@ -20669,7 +20669,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>35</v>
       </c>
@@ -20709,7 +20709,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L8">
         <f t="shared" si="0"/>
         <v>1839</v>
@@ -20719,7 +20719,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L9">
         <f t="shared" si="0"/>
         <v>1840</v>
@@ -20729,7 +20729,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L10">
         <f t="shared" si="0"/>
         <v>1841</v>
@@ -20739,7 +20739,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L11">
         <f t="shared" si="0"/>
         <v>1842</v>
@@ -20749,7 +20749,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L12">
         <f t="shared" si="0"/>
         <v>1843</v>
@@ -20759,7 +20759,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L13">
         <f t="shared" si="0"/>
         <v>1844</v>
@@ -20769,7 +20769,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L14">
         <f t="shared" si="0"/>
         <v>1845</v>
@@ -20779,7 +20779,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L15">
         <f t="shared" si="0"/>
         <v>1846</v>
@@ -20789,7 +20789,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L16">
         <f t="shared" si="0"/>
         <v>1847</v>
@@ -20799,7 +20799,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="17" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L17">
         <f t="shared" si="0"/>
         <v>1848</v>
@@ -20809,7 +20809,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="18" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L18">
         <f t="shared" si="0"/>
         <v>1849</v>
@@ -20819,7 +20819,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="19" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L19">
         <f t="shared" si="0"/>
         <v>1850</v>
@@ -20829,7 +20829,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="20" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L20">
         <f t="shared" si="0"/>
         <v>1851</v>
@@ -20839,7 +20839,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="21" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L21">
         <f t="shared" si="0"/>
         <v>1852</v>
@@ -20849,7 +20849,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="22" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L22">
         <f t="shared" si="0"/>
         <v>1853</v>
@@ -20859,7 +20859,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="23" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L23">
         <f t="shared" si="0"/>
         <v>1854</v>
@@ -20869,7 +20869,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="24" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L24">
         <f t="shared" si="0"/>
         <v>1855</v>
@@ -20879,7 +20879,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="25" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L25">
         <f t="shared" si="0"/>
         <v>1856</v>
@@ -20889,7 +20889,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="26" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L26">
         <f t="shared" si="0"/>
         <v>1857</v>
@@ -20899,7 +20899,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="27" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L27">
         <f t="shared" si="0"/>
         <v>1858</v>
@@ -20909,7 +20909,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="28" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L28">
         <f t="shared" si="0"/>
         <v>1859</v>
@@ -20919,7 +20919,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="29" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L29">
         <f t="shared" si="0"/>
         <v>1860</v>
@@ -20929,7 +20929,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="30" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L30">
         <f t="shared" si="0"/>
         <v>1861</v>
@@ -20939,7 +20939,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="31" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L31">
         <f t="shared" si="0"/>
         <v>1862</v>
@@ -20949,7 +20949,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="32" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L32">
         <f t="shared" si="0"/>
         <v>1863</v>
@@ -20959,7 +20959,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="33" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L33">
         <f t="shared" si="0"/>
         <v>1864</v>
@@ -20969,7 +20969,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="34" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L34">
         <f t="shared" si="0"/>
         <v>1865</v>
@@ -20979,7 +20979,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="35" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L35">
         <f t="shared" si="0"/>
         <v>1866</v>
@@ -20989,7 +20989,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="36" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L36">
         <f t="shared" si="0"/>
         <v>1867</v>
@@ -20999,7 +20999,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="37" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L37">
         <f t="shared" si="0"/>
         <v>1868</v>
@@ -21009,7 +21009,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="38" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L38">
         <f t="shared" si="0"/>
         <v>1869</v>
@@ -21019,7 +21019,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="39" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L39">
         <f t="shared" si="0"/>
         <v>1870</v>
@@ -21029,7 +21029,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="40" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L40">
         <f t="shared" si="0"/>
         <v>1871</v>
@@ -21039,7 +21039,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="41" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L41">
         <f t="shared" si="0"/>
         <v>1872</v>
@@ -21049,7 +21049,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="42" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L42">
         <f t="shared" si="0"/>
         <v>1873</v>
@@ -21059,7 +21059,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="43" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L43">
         <f t="shared" si="0"/>
         <v>1874</v>
@@ -21069,7 +21069,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="44" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L44">
         <f t="shared" si="0"/>
         <v>1875</v>
@@ -21079,7 +21079,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="45" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L45">
         <f t="shared" si="0"/>
         <v>1876</v>
@@ -21089,7 +21089,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="46" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L46">
         <f t="shared" si="0"/>
         <v>1877</v>
@@ -21099,7 +21099,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="47" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L47">
         <f t="shared" si="0"/>
         <v>1878</v>
@@ -21109,7 +21109,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="48" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L48">
         <f t="shared" si="0"/>
         <v>1879</v>
@@ -21119,7 +21119,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="49" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L49">
         <f t="shared" si="0"/>
         <v>1880</v>
@@ -21129,7 +21129,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="50" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L50">
         <f t="shared" si="0"/>
         <v>1881</v>
@@ -21139,7 +21139,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="51" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L51">
         <f t="shared" si="0"/>
         <v>1882</v>
@@ -21149,7 +21149,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="52" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L52">
         <f t="shared" si="0"/>
         <v>1883</v>
@@ -21159,7 +21159,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="53" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L53">
         <f t="shared" si="0"/>
         <v>1884</v>
@@ -21169,7 +21169,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="54" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L54">
         <f t="shared" si="0"/>
         <v>1885</v>
@@ -21179,7 +21179,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="55" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L55">
         <f t="shared" si="0"/>
         <v>1886</v>
@@ -21189,7 +21189,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="56" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L56">
         <f t="shared" si="0"/>
         <v>1887</v>
@@ -21199,7 +21199,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="57" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L57">
         <f t="shared" si="0"/>
         <v>1888</v>
@@ -21209,7 +21209,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="58" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L58">
         <f t="shared" si="0"/>
         <v>1889</v>
@@ -21219,7 +21219,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="59" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L59">
         <f t="shared" si="0"/>
         <v>1890</v>
@@ -21229,7 +21229,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="60" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L60">
         <f t="shared" si="0"/>
         <v>1891</v>
@@ -21239,7 +21239,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="61" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L61">
         <f t="shared" si="0"/>
         <v>1892</v>
@@ -21249,7 +21249,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="62" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L62">
         <f t="shared" si="0"/>
         <v>1893</v>
@@ -21259,7 +21259,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="63" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L63">
         <f t="shared" si="0"/>
         <v>1894</v>
@@ -21269,7 +21269,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="64" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L64">
         <f t="shared" si="0"/>
         <v>1895</v>
@@ -21279,7 +21279,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="65" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L65">
         <f t="shared" si="0"/>
         <v>1896</v>
@@ -21289,7 +21289,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="66" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L66">
         <f t="shared" si="0"/>
         <v>1897</v>
@@ -21299,7 +21299,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="67" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L67">
         <f t="shared" si="0"/>
         <v>1898</v>
@@ -21309,7 +21309,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="68" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L68">
         <f t="shared" ref="L68:L131" si="2">L67+1</f>
         <v>1899</v>
@@ -21319,7 +21319,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="69" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L69">
         <f t="shared" si="2"/>
         <v>1900</v>
@@ -21329,7 +21329,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="70" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L70">
         <f t="shared" si="2"/>
         <v>1901</v>
@@ -21339,7 +21339,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="71" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L71">
         <f t="shared" si="2"/>
         <v>1902</v>
@@ -21349,7 +21349,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="72" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L72">
         <f t="shared" si="2"/>
         <v>1903</v>
@@ -21359,7 +21359,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="73" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L73">
         <f t="shared" si="2"/>
         <v>1904</v>
@@ -21369,7 +21369,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="74" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L74">
         <f t="shared" si="2"/>
         <v>1905</v>
@@ -21379,7 +21379,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="75" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L75">
         <f t="shared" si="2"/>
         <v>1906</v>
@@ -21389,7 +21389,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="76" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L76">
         <f t="shared" si="2"/>
         <v>1907</v>
@@ -21399,7 +21399,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="77" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L77">
         <f t="shared" si="2"/>
         <v>1908</v>
@@ -21409,7 +21409,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="78" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L78">
         <f t="shared" si="2"/>
         <v>1909</v>
@@ -21419,7 +21419,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="79" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L79">
         <f t="shared" si="2"/>
         <v>1910</v>
@@ -21429,7 +21429,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="80" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L80">
         <f t="shared" si="2"/>
         <v>1911</v>
@@ -21439,7 +21439,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="81" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L81">
         <f t="shared" si="2"/>
         <v>1912</v>
@@ -21449,7 +21449,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="82" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L82">
         <f t="shared" si="2"/>
         <v>1913</v>
@@ -21459,7 +21459,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="83" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L83">
         <f t="shared" si="2"/>
         <v>1914</v>
@@ -21469,7 +21469,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="84" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L84">
         <f t="shared" si="2"/>
         <v>1915</v>
@@ -21479,7 +21479,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="85" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L85">
         <f t="shared" si="2"/>
         <v>1916</v>
@@ -21489,7 +21489,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="86" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L86">
         <f t="shared" si="2"/>
         <v>1917</v>
@@ -21499,7 +21499,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="87" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L87">
         <f t="shared" si="2"/>
         <v>1918</v>
@@ -21509,7 +21509,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="88" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L88">
         <f t="shared" si="2"/>
         <v>1919</v>
@@ -21519,7 +21519,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="89" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L89">
         <f t="shared" si="2"/>
         <v>1920</v>
@@ -21529,7 +21529,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="90" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L90">
         <f t="shared" si="2"/>
         <v>1921</v>
@@ -21539,7 +21539,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="91" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L91">
         <f t="shared" si="2"/>
         <v>1922</v>
@@ -21549,7 +21549,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="92" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L92">
         <f t="shared" si="2"/>
         <v>1923</v>
@@ -21559,7 +21559,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="93" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L93">
         <f t="shared" si="2"/>
         <v>1924</v>
@@ -21569,7 +21569,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="94" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L94">
         <f t="shared" si="2"/>
         <v>1925</v>
@@ -21579,7 +21579,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="95" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L95">
         <f t="shared" si="2"/>
         <v>1926</v>
@@ -21589,7 +21589,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="96" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L96">
         <f t="shared" si="2"/>
         <v>1927</v>
@@ -21599,7 +21599,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="97" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L97">
         <f t="shared" si="2"/>
         <v>1928</v>
@@ -21609,7 +21609,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="98" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L98">
         <f t="shared" si="2"/>
         <v>1929</v>
@@ -21619,7 +21619,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="99" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L99">
         <f t="shared" si="2"/>
         <v>1930</v>
@@ -21629,7 +21629,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="100" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L100">
         <f t="shared" si="2"/>
         <v>1931</v>
@@ -21639,7 +21639,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="101" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L101">
         <f t="shared" si="2"/>
         <v>1932</v>
@@ -21649,7 +21649,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="102" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L102">
         <f t="shared" si="2"/>
         <v>1933</v>
@@ -21659,7 +21659,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="103" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L103">
         <f t="shared" si="2"/>
         <v>1934</v>
@@ -21669,7 +21669,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="104" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L104">
         <f t="shared" si="2"/>
         <v>1935</v>
@@ -21679,7 +21679,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="105" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L105">
         <f t="shared" si="2"/>
         <v>1936</v>
@@ -21689,7 +21689,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="106" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L106">
         <f t="shared" si="2"/>
         <v>1937</v>
@@ -21699,7 +21699,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="107" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L107">
         <f t="shared" si="2"/>
         <v>1938</v>
@@ -21709,7 +21709,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="108" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L108">
         <f t="shared" si="2"/>
         <v>1939</v>
@@ -21719,7 +21719,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="109" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L109">
         <f t="shared" si="2"/>
         <v>1940</v>
@@ -21729,7 +21729,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="110" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L110">
         <f t="shared" si="2"/>
         <v>1941</v>
@@ -21739,7 +21739,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="111" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L111">
         <f t="shared" si="2"/>
         <v>1942</v>
@@ -21749,7 +21749,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="112" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L112">
         <f t="shared" si="2"/>
         <v>1943</v>
@@ -21759,7 +21759,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="113" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L113">
         <f t="shared" si="2"/>
         <v>1944</v>
@@ -21769,7 +21769,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="114" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L114">
         <f t="shared" si="2"/>
         <v>1945</v>
@@ -21779,7 +21779,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="115" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L115">
         <f t="shared" si="2"/>
         <v>1946</v>
@@ -21789,7 +21789,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="116" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L116">
         <f t="shared" si="2"/>
         <v>1947</v>
@@ -21799,7 +21799,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="117" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L117">
         <f t="shared" si="2"/>
         <v>1948</v>
@@ -21809,7 +21809,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="118" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L118">
         <f t="shared" si="2"/>
         <v>1949</v>
@@ -21819,7 +21819,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="119" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L119">
         <f t="shared" si="2"/>
         <v>1950</v>
@@ -21829,7 +21829,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="120" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L120">
         <f t="shared" si="2"/>
         <v>1951</v>
@@ -21839,7 +21839,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="121" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L121">
         <f t="shared" si="2"/>
         <v>1952</v>
@@ -21849,7 +21849,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="122" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L122">
         <f t="shared" si="2"/>
         <v>1953</v>
@@ -21859,7 +21859,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="123" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L123">
         <f t="shared" si="2"/>
         <v>1954</v>
@@ -21869,7 +21869,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="124" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L124">
         <f t="shared" si="2"/>
         <v>1955</v>
@@ -21879,7 +21879,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="125" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L125">
         <f t="shared" si="2"/>
         <v>1956</v>
@@ -21889,7 +21889,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="126" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L126">
         <f t="shared" si="2"/>
         <v>1957</v>
@@ -21899,7 +21899,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="127" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L127">
         <f t="shared" si="2"/>
         <v>1958</v>
@@ -21909,7 +21909,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="128" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L128">
         <f t="shared" si="2"/>
         <v>1959</v>
@@ -21919,7 +21919,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="129" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L129">
         <f t="shared" si="2"/>
         <v>1960</v>
@@ -21929,7 +21929,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="130" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L130">
         <f t="shared" si="2"/>
         <v>1961</v>
@@ -21939,7 +21939,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="131" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L131">
         <f t="shared" si="2"/>
         <v>1962</v>
@@ -21949,7 +21949,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="132" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L132">
         <f t="shared" ref="L132:L195" si="4">L131+1</f>
         <v>1963</v>
@@ -21959,7 +21959,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="133" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L133">
         <f t="shared" si="4"/>
         <v>1964</v>
@@ -21969,7 +21969,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="134" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L134">
         <f t="shared" si="4"/>
         <v>1965</v>
@@ -21979,7 +21979,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="135" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L135">
         <f t="shared" si="4"/>
         <v>1966</v>
@@ -21989,7 +21989,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="136" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L136">
         <f t="shared" si="4"/>
         <v>1967</v>
@@ -21999,7 +21999,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="137" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L137">
         <f t="shared" si="4"/>
         <v>1968</v>
@@ -22009,7 +22009,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="138" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L138">
         <f t="shared" si="4"/>
         <v>1969</v>
@@ -22019,7 +22019,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="139" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L139">
         <f t="shared" si="4"/>
         <v>1970</v>
@@ -22029,7 +22029,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="140" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L140">
         <f t="shared" si="4"/>
         <v>1971</v>
@@ -22039,7 +22039,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="141" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L141">
         <f t="shared" si="4"/>
         <v>1972</v>
@@ -22049,7 +22049,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="142" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L142">
         <f t="shared" si="4"/>
         <v>1973</v>
@@ -22059,7 +22059,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="143" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L143">
         <f t="shared" si="4"/>
         <v>1974</v>
@@ -22069,7 +22069,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="144" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L144">
         <f t="shared" si="4"/>
         <v>1975</v>
@@ -22079,7 +22079,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="145" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L145">
         <f t="shared" si="4"/>
         <v>1976</v>
@@ -22089,7 +22089,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="146" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L146">
         <f t="shared" si="4"/>
         <v>1977</v>
@@ -22099,7 +22099,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="147" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L147">
         <f t="shared" si="4"/>
         <v>1978</v>
@@ -22109,7 +22109,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="148" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L148">
         <f t="shared" si="4"/>
         <v>1979</v>
@@ -22119,7 +22119,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="149" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L149">
         <f t="shared" si="4"/>
         <v>1980</v>
@@ -22129,7 +22129,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="150" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L150">
         <f t="shared" si="4"/>
         <v>1981</v>
@@ -22139,7 +22139,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="151" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L151">
         <f t="shared" si="4"/>
         <v>1982</v>
@@ -22149,7 +22149,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="152" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L152">
         <f t="shared" si="4"/>
         <v>1983</v>
@@ -22159,7 +22159,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="153" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L153">
         <f t="shared" si="4"/>
         <v>1984</v>
@@ -22169,7 +22169,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="154" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L154">
         <f t="shared" si="4"/>
         <v>1985</v>
@@ -22179,7 +22179,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="155" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L155">
         <f t="shared" si="4"/>
         <v>1986</v>
@@ -22189,7 +22189,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="156" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L156">
         <f t="shared" si="4"/>
         <v>1987</v>
@@ -22199,7 +22199,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="157" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L157">
         <f t="shared" si="4"/>
         <v>1988</v>
@@ -22209,7 +22209,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="158" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L158">
         <f t="shared" si="4"/>
         <v>1989</v>
@@ -22219,7 +22219,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="159" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L159">
         <f t="shared" si="4"/>
         <v>1990</v>
@@ -22229,7 +22229,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="160" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L160">
         <f t="shared" si="4"/>
         <v>1991</v>
@@ -22239,7 +22239,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="161" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L161">
         <f t="shared" si="4"/>
         <v>1992</v>
@@ -22249,7 +22249,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="162" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L162">
         <f t="shared" si="4"/>
         <v>1993</v>
@@ -22259,7 +22259,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="163" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L163">
         <f t="shared" si="4"/>
         <v>1994</v>
@@ -22269,7 +22269,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="164" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L164">
         <f t="shared" si="4"/>
         <v>1995</v>
@@ -22279,7 +22279,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="165" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L165">
         <f t="shared" si="4"/>
         <v>1996</v>
@@ -22289,7 +22289,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="166" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L166">
         <f t="shared" si="4"/>
         <v>1997</v>
@@ -22299,7 +22299,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="167" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L167">
         <f t="shared" si="4"/>
         <v>1998</v>
@@ -22309,7 +22309,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="168" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L168">
         <f t="shared" si="4"/>
         <v>1999</v>
@@ -22319,7 +22319,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="169" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L169">
         <f t="shared" si="4"/>
         <v>2000</v>
@@ -22329,7 +22329,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="170" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L170">
         <f t="shared" si="4"/>
         <v>2001</v>
@@ -22339,7 +22339,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="171" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L171">
         <f t="shared" si="4"/>
         <v>2002</v>
@@ -22349,7 +22349,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="172" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L172">
         <f t="shared" si="4"/>
         <v>2003</v>
@@ -22359,7 +22359,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="173" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L173">
         <f t="shared" si="4"/>
         <v>2004</v>
@@ -22369,7 +22369,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="174" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L174">
         <f t="shared" si="4"/>
         <v>2005</v>
@@ -22379,7 +22379,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="175" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L175">
         <f t="shared" si="4"/>
         <v>2006</v>
@@ -22389,7 +22389,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="176" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L176">
         <f t="shared" si="4"/>
         <v>2007</v>
@@ -22399,7 +22399,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="177" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L177">
         <f t="shared" si="4"/>
         <v>2008</v>
@@ -22409,7 +22409,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="178" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L178">
         <f t="shared" si="4"/>
         <v>2009</v>
@@ -22419,7 +22419,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="179" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L179">
         <f t="shared" si="4"/>
         <v>2010</v>
@@ -22429,7 +22429,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="180" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L180">
         <f t="shared" si="4"/>
         <v>2011</v>
@@ -22439,7 +22439,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="181" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L181">
         <f t="shared" si="4"/>
         <v>2012</v>
@@ -22449,7 +22449,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="182" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L182">
         <f t="shared" si="4"/>
         <v>2013</v>
@@ -22459,7 +22459,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="183" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L183">
         <f t="shared" si="4"/>
         <v>2014</v>
@@ -22469,7 +22469,7 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="184" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L184">
         <f t="shared" si="4"/>
         <v>2015</v>
@@ -22479,7 +22479,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L185">
         <f t="shared" si="4"/>
         <v>2016</v>
@@ -22489,7 +22489,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="186" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L186">
         <f t="shared" si="4"/>
         <v>2017</v>
@@ -22499,7 +22499,7 @@
         <v>2270</v>
       </c>
     </row>
-    <row r="187" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L187">
         <f t="shared" si="4"/>
         <v>2018</v>
@@ -22509,7 +22509,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="188" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="188" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L188">
         <f t="shared" si="4"/>
         <v>2019</v>
@@ -22519,7 +22519,7 @@
         <v>2285</v>
       </c>
     </row>
-    <row r="189" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="189" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L189">
         <f t="shared" si="4"/>
         <v>2020</v>
@@ -22529,7 +22529,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="190" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="190" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L190">
         <f t="shared" si="4"/>
         <v>2021</v>
@@ -22539,7 +22539,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="191" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="191" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L191">
         <f t="shared" si="4"/>
         <v>2022</v>
@@ -22549,7 +22549,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="192" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L192">
         <f t="shared" si="4"/>
         <v>2023</v>
@@ -22559,7 +22559,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="193" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="193" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L193">
         <f t="shared" si="4"/>
         <v>2024</v>
@@ -22569,7 +22569,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="194" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="194" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L194">
         <f t="shared" si="4"/>
         <v>2025</v>
@@ -22579,7 +22579,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="195" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="195" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L195">
         <f t="shared" si="4"/>
         <v>2026</v>
@@ -22589,7 +22589,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="196" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="196" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L196">
         <f t="shared" ref="L196:L259" si="6">L195+1</f>
         <v>2027</v>
@@ -22599,7 +22599,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="197" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="197" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L197">
         <f t="shared" si="6"/>
         <v>2028</v>
@@ -22609,7 +22609,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="198" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="198" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L198">
         <f t="shared" si="6"/>
         <v>2029</v>
@@ -22619,7 +22619,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="199" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="199" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L199">
         <f t="shared" si="6"/>
         <v>2030</v>
@@ -22629,7 +22629,7 @@
         <v>2366</v>
       </c>
     </row>
-    <row r="200" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="200" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L200">
         <f t="shared" si="6"/>
         <v>2031</v>
@@ -22639,7 +22639,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="201" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="201" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L201">
         <f t="shared" si="6"/>
         <v>2032</v>
@@ -22649,7 +22649,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="202" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="202" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L202">
         <f t="shared" si="6"/>
         <v>2033</v>
@@ -22659,7 +22659,7 @@
         <v>2389</v>
       </c>
     </row>
-    <row r="203" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="203" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L203">
         <f t="shared" si="6"/>
         <v>2034</v>
@@ -22669,7 +22669,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="204" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="204" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L204">
         <f t="shared" si="6"/>
         <v>2035</v>
@@ -22679,7 +22679,7 @@
         <v>2404</v>
       </c>
     </row>
-    <row r="205" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="205" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L205">
         <f t="shared" si="6"/>
         <v>2036</v>
@@ -22689,7 +22689,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="206" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="206" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L206">
         <f t="shared" si="6"/>
         <v>2037</v>
@@ -22699,7 +22699,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="207" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="207" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L207">
         <f t="shared" si="6"/>
         <v>2038</v>
@@ -22709,7 +22709,7 @@
         <v>2426</v>
       </c>
     </row>
-    <row r="208" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="208" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L208">
         <f t="shared" si="6"/>
         <v>2039</v>
@@ -22719,7 +22719,7 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="209" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L209">
         <f t="shared" si="6"/>
         <v>2040</v>
@@ -22729,7 +22729,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="210" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L210">
         <f t="shared" si="6"/>
         <v>2041</v>
@@ -22739,7 +22739,7 @@
         <v>2448</v>
       </c>
     </row>
-    <row r="211" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L211">
         <f t="shared" si="6"/>
         <v>2042</v>
@@ -22749,7 +22749,7 @@
         <v>2455</v>
       </c>
     </row>
-    <row r="212" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="212" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L212">
         <f t="shared" si="6"/>
         <v>2043</v>
@@ -22759,7 +22759,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="213" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L213">
         <f t="shared" si="6"/>
         <v>2044</v>
@@ -22769,7 +22769,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="214" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L214">
         <f t="shared" si="6"/>
         <v>2045</v>
@@ -22779,7 +22779,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="215" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L215">
         <f t="shared" si="6"/>
         <v>2046</v>
@@ -22789,7 +22789,7 @@
         <v>2485</v>
       </c>
     </row>
-    <row r="216" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L216">
         <f t="shared" si="6"/>
         <v>2047</v>
@@ -22799,7 +22799,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="217" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L217">
         <f t="shared" si="6"/>
         <v>2048</v>
@@ -22809,7 +22809,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="218" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L218">
         <f t="shared" si="6"/>
         <v>2049</v>
@@ -22819,7 +22819,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="219" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L219">
         <f t="shared" si="6"/>
         <v>2050</v>
@@ -22829,7 +22829,7 @@
         <v>2515</v>
       </c>
     </row>
-    <row r="220" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L220">
         <f t="shared" si="6"/>
         <v>2051</v>
@@ -22839,7 +22839,7 @@
         <v>2522</v>
       </c>
     </row>
-    <row r="221" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L221">
         <f t="shared" si="6"/>
         <v>2052</v>
@@ -22849,7 +22849,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="222" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L222">
         <f t="shared" si="6"/>
         <v>2053</v>
@@ -22859,7 +22859,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="223" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L223">
         <f t="shared" si="6"/>
         <v>2054</v>
@@ -22869,7 +22869,7 @@
         <v>2545</v>
       </c>
     </row>
-    <row r="224" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L224">
         <f t="shared" si="6"/>
         <v>2055</v>
@@ -22879,7 +22879,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="225" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="225" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L225">
         <f t="shared" si="6"/>
         <v>2056</v>
@@ -22889,7 +22889,7 @@
         <v>2559</v>
       </c>
     </row>
-    <row r="226" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L226">
         <f t="shared" si="6"/>
         <v>2057</v>
@@ -22899,7 +22899,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="227" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="227" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L227">
         <f t="shared" si="6"/>
         <v>2058</v>
@@ -22909,7 +22909,7 @@
         <v>2574</v>
       </c>
     </row>
-    <row r="228" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="228" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L228">
         <f t="shared" si="6"/>
         <v>2059</v>
@@ -22919,7 +22919,7 @@
         <v>2582</v>
       </c>
     </row>
-    <row r="229" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="229" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L229">
         <f t="shared" si="6"/>
         <v>2060</v>
@@ -22929,7 +22929,7 @@
         <v>2589</v>
       </c>
     </row>
-    <row r="230" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="230" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L230">
         <f t="shared" si="6"/>
         <v>2061</v>
@@ -22939,7 +22939,7 @@
         <v>2596</v>
       </c>
     </row>
-    <row r="231" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="231" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L231">
         <f t="shared" si="6"/>
         <v>2062</v>
@@ -22949,7 +22949,7 @@
         <v>2604</v>
       </c>
     </row>
-    <row r="232" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="232" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L232">
         <f t="shared" si="6"/>
         <v>2063</v>
@@ -22959,7 +22959,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="233" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="233" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L233">
         <f t="shared" si="6"/>
         <v>2064</v>
@@ -22969,7 +22969,7 @@
         <v>2619</v>
       </c>
     </row>
-    <row r="234" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="234" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L234">
         <f t="shared" si="6"/>
         <v>2065</v>
@@ -22979,7 +22979,7 @@
         <v>2626</v>
       </c>
     </row>
-    <row r="235" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="235" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L235">
         <f t="shared" si="6"/>
         <v>2066</v>
@@ -22989,7 +22989,7 @@
         <v>2634</v>
       </c>
     </row>
-    <row r="236" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="236" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L236">
         <f t="shared" si="6"/>
         <v>2067</v>
@@ -22999,7 +22999,7 @@
         <v>2641</v>
       </c>
     </row>
-    <row r="237" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="237" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L237">
         <f t="shared" si="6"/>
         <v>2068</v>
@@ -23009,7 +23009,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="238" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="238" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L238">
         <f t="shared" si="6"/>
         <v>2069</v>
@@ -23019,7 +23019,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="239" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="239" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L239">
         <f t="shared" si="6"/>
         <v>2070</v>
@@ -23029,7 +23029,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="240" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="240" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L240">
         <f t="shared" si="6"/>
         <v>2071</v>
@@ -23039,7 +23039,7 @@
         <v>2671</v>
       </c>
     </row>
-    <row r="241" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="241" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L241">
         <f t="shared" si="6"/>
         <v>2072</v>
@@ -23049,7 +23049,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="242" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="242" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L242">
         <f t="shared" si="6"/>
         <v>2073</v>
@@ -23059,7 +23059,7 @@
         <v>2685</v>
       </c>
     </row>
-    <row r="243" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="243" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L243">
         <f t="shared" si="6"/>
         <v>2074</v>
@@ -23069,7 +23069,7 @@
         <v>2693</v>
       </c>
     </row>
-    <row r="244" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="244" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L244">
         <f t="shared" si="6"/>
         <v>2075</v>
@@ -23079,7 +23079,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="245" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="245" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L245">
         <f t="shared" si="6"/>
         <v>2076</v>
@@ -23089,7 +23089,7 @@
         <v>2708</v>
       </c>
     </row>
-    <row r="246" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="246" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L246">
         <f t="shared" si="6"/>
         <v>2077</v>
@@ -23099,7 +23099,7 @@
         <v>2715</v>
       </c>
     </row>
-    <row r="247" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="247" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L247">
         <f t="shared" si="6"/>
         <v>2078</v>
@@ -23109,7 +23109,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="248" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="248" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L248">
         <f t="shared" si="6"/>
         <v>2079</v>
@@ -23119,7 +23119,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="249" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="249" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L249">
         <f t="shared" si="6"/>
         <v>2080</v>
@@ -23129,7 +23129,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="250" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="250" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L250">
         <f t="shared" si="6"/>
         <v>2081</v>
@@ -23139,7 +23139,7 @@
         <v>2745</v>
       </c>
     </row>
-    <row r="251" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="251" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L251">
         <f t="shared" si="6"/>
         <v>2082</v>
@@ -23149,7 +23149,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="252" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="252" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L252">
         <f t="shared" si="6"/>
         <v>2083</v>
@@ -23159,7 +23159,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="253" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="253" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L253">
         <f t="shared" si="6"/>
         <v>2084</v>
@@ -23169,7 +23169,7 @@
         <v>2767</v>
       </c>
     </row>
-    <row r="254" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="254" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L254">
         <f t="shared" si="6"/>
         <v>2085</v>
@@ -23179,7 +23179,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="255" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="255" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L255">
         <f t="shared" si="6"/>
         <v>2086</v>
@@ -23189,7 +23189,7 @@
         <v>2782</v>
       </c>
     </row>
-    <row r="256" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="256" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L256">
         <f t="shared" si="6"/>
         <v>2087</v>
@@ -23199,7 +23199,7 @@
         <v>2789</v>
       </c>
     </row>
-    <row r="257" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="257" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L257">
         <f t="shared" si="6"/>
         <v>2088</v>
@@ -23209,7 +23209,7 @@
         <v>2797</v>
       </c>
     </row>
-    <row r="258" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="258" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L258">
         <f t="shared" si="6"/>
         <v>2089</v>
@@ -23219,7 +23219,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="259" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="259" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L259">
         <f t="shared" si="6"/>
         <v>2090</v>
@@ -23229,7 +23229,7 @@
         <v>2812</v>
       </c>
     </row>
-    <row r="260" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="260" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L260">
         <f t="shared" ref="L260:L323" si="8">L259+1</f>
         <v>2091</v>
@@ -23239,7 +23239,7 @@
         <v>2819</v>
       </c>
     </row>
-    <row r="261" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="261" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L261">
         <f t="shared" si="8"/>
         <v>2092</v>
@@ -23249,7 +23249,7 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="262" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="262" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L262">
         <f t="shared" si="8"/>
         <v>2093</v>
@@ -23259,7 +23259,7 @@
         <v>2834</v>
       </c>
     </row>
-    <row r="263" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="263" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L263">
         <f t="shared" si="8"/>
         <v>2094</v>
@@ -23269,7 +23269,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="264" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="264" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L264">
         <f t="shared" si="8"/>
         <v>2095</v>
@@ -23279,7 +23279,7 @@
         <v>2849</v>
       </c>
     </row>
-    <row r="265" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="265" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L265">
         <f t="shared" si="8"/>
         <v>2096</v>
@@ -23289,7 +23289,7 @@
         <v>2856</v>
       </c>
     </row>
-    <row r="266" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="266" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L266">
         <f t="shared" si="8"/>
         <v>2097</v>
@@ -23299,7 +23299,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="267" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="267" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L267">
         <f t="shared" si="8"/>
         <v>2098</v>
@@ -23309,7 +23309,7 @@
         <v>2871</v>
       </c>
     </row>
-    <row r="268" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="268" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L268">
         <f t="shared" si="8"/>
         <v>2099</v>
@@ -23319,7 +23319,7 @@
         <v>2878</v>
       </c>
     </row>
-    <row r="269" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="269" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L269">
         <f t="shared" si="8"/>
         <v>2100</v>
@@ -23329,7 +23329,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="270" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="270" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L270">
         <f t="shared" si="8"/>
         <v>2101</v>
@@ -23339,7 +23339,7 @@
         <v>2893</v>
       </c>
     </row>
-    <row r="271" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="271" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L271">
         <f t="shared" si="8"/>
         <v>2102</v>
@@ -23349,7 +23349,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="272" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="272" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L272">
         <f t="shared" si="8"/>
         <v>2103</v>
@@ -23359,7 +23359,7 @@
         <v>2908</v>
       </c>
     </row>
-    <row r="273" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="273" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L273">
         <f t="shared" si="8"/>
         <v>2104</v>
@@ -23369,7 +23369,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="274" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="274" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L274">
         <f t="shared" si="8"/>
         <v>2105</v>
@@ -23379,7 +23379,7 @@
         <v>2923</v>
       </c>
     </row>
-    <row r="275" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="275" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L275">
         <f t="shared" si="8"/>
         <v>2106</v>
@@ -23389,7 +23389,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="276" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="276" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L276">
         <f t="shared" si="8"/>
         <v>2107</v>
@@ -23399,7 +23399,7 @@
         <v>2938</v>
       </c>
     </row>
-    <row r="277" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="277" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L277">
         <f t="shared" si="8"/>
         <v>2108</v>
@@ -23409,7 +23409,7 @@
         <v>2945</v>
       </c>
     </row>
-    <row r="278" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="278" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L278">
         <f t="shared" si="8"/>
         <v>2109</v>
@@ -23419,7 +23419,7 @@
         <v>2953</v>
       </c>
     </row>
-    <row r="279" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="279" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L279">
         <f t="shared" si="8"/>
         <v>2110</v>
@@ -23429,7 +23429,7 @@
         <v>2960</v>
       </c>
     </row>
-    <row r="280" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="280" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L280">
         <f t="shared" si="8"/>
         <v>2111</v>
@@ -23439,7 +23439,7 @@
         <v>2967</v>
       </c>
     </row>
-    <row r="281" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="281" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L281">
         <f t="shared" si="8"/>
         <v>2112</v>
@@ -23449,7 +23449,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="282" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="282" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L282">
         <f t="shared" si="8"/>
         <v>2113</v>
@@ -23459,7 +23459,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="283" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="283" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L283">
         <f t="shared" si="8"/>
         <v>2114</v>
@@ -23469,7 +23469,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="284" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="284" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L284">
         <f t="shared" si="8"/>
         <v>2115</v>
@@ -23479,7 +23479,7 @@
         <v>2997</v>
       </c>
     </row>
-    <row r="285" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="285" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L285">
         <f t="shared" si="8"/>
         <v>2116</v>
@@ -23489,7 +23489,7 @@
         <v>3004</v>
       </c>
     </row>
-    <row r="286" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="286" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L286">
         <f t="shared" si="8"/>
         <v>2117</v>
@@ -23499,7 +23499,7 @@
         <v>3012</v>
       </c>
     </row>
-    <row r="287" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="287" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L287">
         <f t="shared" si="8"/>
         <v>2118</v>
@@ -23509,7 +23509,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="288" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="288" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L288">
         <f t="shared" si="8"/>
         <v>2119</v>
@@ -23519,7 +23519,7 @@
         <v>3027</v>
       </c>
     </row>
-    <row r="289" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="289" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L289">
         <f t="shared" si="8"/>
         <v>2120</v>
@@ -23529,7 +23529,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="290" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="290" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L290">
         <f t="shared" si="8"/>
         <v>2121</v>
@@ -23539,7 +23539,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="291" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="291" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L291">
         <f t="shared" si="8"/>
         <v>2122</v>
@@ -23549,7 +23549,7 @@
         <v>3049</v>
       </c>
     </row>
-    <row r="292" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="292" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L292">
         <f t="shared" si="8"/>
         <v>2123</v>
@@ -23559,7 +23559,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="293" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="293" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L293">
         <f t="shared" si="8"/>
         <v>2124</v>
@@ -23569,7 +23569,7 @@
         <v>3064</v>
       </c>
     </row>
-    <row r="294" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="294" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L294">
         <f t="shared" si="8"/>
         <v>2125</v>
@@ -23579,7 +23579,7 @@
         <v>3071</v>
       </c>
     </row>
-    <row r="295" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="295" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L295">
         <f t="shared" si="8"/>
         <v>2126</v>
@@ -23589,7 +23589,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="296" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="296" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L296">
         <f t="shared" si="8"/>
         <v>2127</v>
@@ -23599,7 +23599,7 @@
         <v>3086</v>
       </c>
     </row>
-    <row r="297" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="297" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L297">
         <f t="shared" si="8"/>
         <v>2128</v>
@@ -23609,7 +23609,7 @@
         <v>3093</v>
       </c>
     </row>
-    <row r="298" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="298" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L298">
         <f t="shared" si="8"/>
         <v>2129</v>
@@ -23619,7 +23619,7 @@
         <v>3101</v>
       </c>
     </row>
-    <row r="299" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="299" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L299">
         <f t="shared" si="8"/>
         <v>2130</v>
@@ -23629,7 +23629,7 @@
         <v>3108</v>
       </c>
     </row>
-    <row r="300" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="300" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L300">
         <f t="shared" si="8"/>
         <v>2131</v>
@@ -23639,7 +23639,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="301" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="301" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L301">
         <f t="shared" si="8"/>
         <v>2132</v>
@@ -23649,7 +23649,7 @@
         <v>3123</v>
       </c>
     </row>
-    <row r="302" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="302" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L302">
         <f t="shared" si="8"/>
         <v>2133</v>
@@ -23659,7 +23659,7 @@
         <v>3131</v>
       </c>
     </row>
-    <row r="303" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="303" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L303">
         <f t="shared" si="8"/>
         <v>2134</v>
@@ -23669,7 +23669,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="304" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="304" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L304">
         <f t="shared" si="8"/>
         <v>2135</v>
@@ -23679,7 +23679,7 @@
         <v>3145</v>
       </c>
     </row>
-    <row r="305" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="305" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L305">
         <f t="shared" si="8"/>
         <v>2136</v>
@@ -23689,7 +23689,7 @@
         <v>3153</v>
       </c>
     </row>
-    <row r="306" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="306" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L306">
         <f t="shared" si="8"/>
         <v>2137</v>
@@ -23699,7 +23699,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="307" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="307" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L307">
         <f t="shared" si="8"/>
         <v>2138</v>
@@ -23709,7 +23709,7 @@
         <v>3168</v>
       </c>
     </row>
-    <row r="308" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="308" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L308">
         <f t="shared" si="8"/>
         <v>2139</v>
@@ -23719,7 +23719,7 @@
         <v>3175</v>
       </c>
     </row>
-    <row r="309" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="309" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L309">
         <f t="shared" si="8"/>
         <v>2140</v>
@@ -23729,7 +23729,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="310" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="310" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L310">
         <f t="shared" si="8"/>
         <v>2141</v>
@@ -23739,7 +23739,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="311" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="311" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L311">
         <f t="shared" si="8"/>
         <v>2142</v>
@@ -23749,7 +23749,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="312" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="312" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L312">
         <f t="shared" si="8"/>
         <v>2143</v>
@@ -23759,7 +23759,7 @@
         <v>3205</v>
       </c>
     </row>
-    <row r="313" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="313" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L313">
         <f t="shared" si="8"/>
         <v>2144</v>
@@ -23769,7 +23769,7 @@
         <v>3212</v>
       </c>
     </row>
-    <row r="314" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="314" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L314">
         <f t="shared" si="8"/>
         <v>2145</v>
@@ -23779,7 +23779,7 @@
         <v>3220</v>
       </c>
     </row>
-    <row r="315" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="315" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L315">
         <f t="shared" si="8"/>
         <v>2146</v>
@@ -23789,7 +23789,7 @@
         <v>3227</v>
       </c>
     </row>
-    <row r="316" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="316" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L316">
         <f t="shared" si="8"/>
         <v>2147</v>
@@ -23799,7 +23799,7 @@
         <v>3234</v>
       </c>
     </row>
-    <row r="317" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="317" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L317">
         <f t="shared" si="8"/>
         <v>2148</v>
@@ -23809,7 +23809,7 @@
         <v>3242</v>
       </c>
     </row>
-    <row r="318" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="318" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L318">
         <f t="shared" si="8"/>
         <v>2149</v>
@@ -23819,7 +23819,7 @@
         <v>3249</v>
       </c>
     </row>
-    <row r="319" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="319" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L319">
         <f t="shared" si="8"/>
         <v>2150</v>
@@ -23829,7 +23829,7 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="320" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="320" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L320">
         <f t="shared" si="8"/>
         <v>2151</v>
@@ -23839,7 +23839,7 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="321" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="321" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L321">
         <f t="shared" si="8"/>
         <v>2152</v>
@@ -23849,7 +23849,7 @@
         <v>3272</v>
       </c>
     </row>
-    <row r="322" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="322" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L322">
         <f t="shared" si="8"/>
         <v>2153</v>
@@ -23859,7 +23859,7 @@
         <v>3279</v>
       </c>
     </row>
-    <row r="323" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="323" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L323">
         <f t="shared" si="8"/>
         <v>2154</v>
@@ -23869,7 +23869,7 @@
         <v>3286</v>
       </c>
     </row>
-    <row r="324" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="324" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L324">
         <f t="shared" ref="L324:L336" si="10">L323+1</f>
         <v>2155</v>
@@ -23879,7 +23879,7 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="325" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="325" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L325">
         <f t="shared" si="10"/>
         <v>2156</v>
@@ -23889,7 +23889,7 @@
         <v>3301</v>
       </c>
     </row>
-    <row r="326" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="326" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L326">
         <f t="shared" si="10"/>
         <v>2157</v>
@@ -23899,7 +23899,7 @@
         <v>3309</v>
       </c>
     </row>
-    <row r="327" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="327" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L327">
         <f t="shared" si="10"/>
         <v>2158</v>
@@ -23909,7 +23909,7 @@
         <v>3316</v>
       </c>
     </row>
-    <row r="328" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="328" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L328">
         <f t="shared" si="10"/>
         <v>2159</v>
@@ -23919,7 +23919,7 @@
         <v>3323</v>
       </c>
     </row>
-    <row r="329" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="329" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L329">
         <f t="shared" si="10"/>
         <v>2160</v>
@@ -23929,7 +23929,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="330" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="330" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L330">
         <f t="shared" si="10"/>
         <v>2161</v>
@@ -23939,7 +23939,7 @@
         <v>3338</v>
       </c>
     </row>
-    <row r="331" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="331" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L331">
         <f t="shared" si="10"/>
         <v>2162</v>
@@ -23949,7 +23949,7 @@
         <v>3346</v>
       </c>
     </row>
-    <row r="332" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="332" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L332">
         <f t="shared" si="10"/>
         <v>2163</v>
@@ -23959,7 +23959,7 @@
         <v>3353</v>
       </c>
     </row>
-    <row r="333" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="333" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L333">
         <f t="shared" si="10"/>
         <v>2164</v>
@@ -23969,7 +23969,7 @@
         <v>3361</v>
       </c>
     </row>
-    <row r="334" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="334" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L334">
         <f t="shared" si="10"/>
         <v>2165</v>
@@ -23979,7 +23979,7 @@
         <v>3368</v>
       </c>
     </row>
-    <row r="335" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="335" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L335">
         <f t="shared" si="10"/>
         <v>2166</v>
@@ -23989,7 +23989,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="336" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="336" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L336">
         <f t="shared" si="10"/>
         <v>2167</v>
@@ -24008,12 +24008,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B976ED82-D377-452B-98DC-3515CED81A81}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C1" t="s">
         <v>325</v>
       </c>
@@ -24021,7 +24021,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -24032,7 +24032,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -24046,7 +24046,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -24060,7 +24060,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -24074,7 +24074,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>86</v>
       </c>
@@ -24088,7 +24088,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>168</v>
       </c>
@@ -24102,7 +24102,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -24116,7 +24116,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>85</v>
       </c>
@@ -24141,14 +24141,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A66C56-C25D-4E4C-815E-A8416CC0CC5B}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>64</v>
       </c>
@@ -24156,7 +24156,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>56</v>
       </c>
@@ -24164,7 +24164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>180</v>
       </c>
@@ -24172,7 +24172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>181</v>
       </c>
@@ -24180,7 +24180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>188</v>
       </c>
@@ -24188,12 +24188,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>183</v>
       </c>
@@ -24201,7 +24201,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>184</v>
       </c>
@@ -24209,7 +24209,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>185</v>
       </c>
@@ -24217,7 +24217,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>186</v>
       </c>
@@ -24225,7 +24225,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>187</v>
       </c>
@@ -24233,7 +24233,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>189</v>
       </c>
@@ -24249,12 +24249,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F1D77F-0E43-499A-A11C-88B275139916}">
   <dimension ref="A1:J61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="10" width="14.44140625" customWidth="1"/>
+    <col min="3" max="10" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>90</v>
       </c>
@@ -24286,7 +24286,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -24312,7 +24312,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -24338,7 +24338,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>7</v>
       </c>
@@ -24358,7 +24358,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>8</v>
       </c>
@@ -24390,7 +24390,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>9</v>
       </c>
@@ -24422,7 +24422,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>10</v>
       </c>
@@ -24448,7 +24448,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>11</v>
       </c>
@@ -24477,7 +24477,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>14</v>
       </c>
@@ -24506,7 +24506,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>19</v>
       </c>
@@ -24529,7 +24529,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>20</v>
       </c>
@@ -24561,7 +24561,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>21</v>
       </c>
@@ -24593,7 +24593,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>22</v>
       </c>
@@ -24622,7 +24622,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>34</v>
       </c>
@@ -24648,7 +24648,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>35</v>
       </c>
@@ -24674,7 +24674,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>36</v>
       </c>
@@ -24697,7 +24697,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>37</v>
       </c>
@@ -24726,7 +24726,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>38</v>
       </c>
@@ -24755,7 +24755,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>39</v>
       </c>
@@ -24781,7 +24781,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>40</v>
       </c>
@@ -24807,7 +24807,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>41</v>
       </c>
@@ -24818,7 +24818,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>42</v>
       </c>
@@ -24829,7 +24829,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>46</v>
       </c>
@@ -24852,7 +24852,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>47</v>
       </c>
@@ -24881,7 +24881,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>53</v>
       </c>
@@ -24910,7 +24910,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>54</v>
       </c>
@@ -24939,7 +24939,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>55</v>
       </c>
@@ -24962,7 +24962,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>59</v>
       </c>
@@ -24988,7 +24988,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>60</v>
       </c>
@@ -25014,7 +25014,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>3</v>
       </c>
@@ -25040,7 +25040,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>4</v>
       </c>
@@ -25060,7 +25060,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>5</v>
       </c>
@@ -25080,7 +25080,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>6</v>
       </c>
@@ -25109,7 +25109,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>12</v>
       </c>
@@ -25129,7 +25129,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>13</v>
       </c>
@@ -25149,7 +25149,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>15</v>
       </c>
@@ -25178,7 +25178,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>16</v>
       </c>
@@ -25207,7 +25207,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>17</v>
       </c>
@@ -25230,7 +25230,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>18</v>
       </c>
@@ -25253,7 +25253,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>23</v>
       </c>
@@ -25282,7 +25282,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>24</v>
       </c>
@@ -25311,7 +25311,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>25</v>
       </c>
@@ -25331,7 +25331,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>26</v>
       </c>
@@ -25351,7 +25351,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>27</v>
       </c>
@@ -25371,7 +25371,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>28</v>
       </c>
@@ -25391,7 +25391,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>29</v>
       </c>
@@ -25411,7 +25411,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>30</v>
       </c>
@@ -25431,7 +25431,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>31</v>
       </c>
@@ -25457,7 +25457,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>32</v>
       </c>
@@ -25480,7 +25480,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>33</v>
       </c>
@@ -25503,7 +25503,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>43</v>
       </c>
@@ -25526,7 +25526,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>44</v>
       </c>
@@ -25549,7 +25549,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>45</v>
       </c>
@@ -25572,7 +25572,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>48</v>
       </c>
@@ -25601,7 +25601,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>49</v>
       </c>
@@ -25615,7 +25615,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>50</v>
       </c>
@@ -25629,7 +25629,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>51</v>
       </c>
@@ -25646,7 +25646,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>52</v>
       </c>
@@ -25672,7 +25672,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>56</v>
       </c>
@@ -25689,7 +25689,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>57</v>
       </c>
@@ -25712,7 +25712,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>58</v>
       </c>

--- a/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
+++ b/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghakk\ece445l_lab7-10_fall26-4-ew-js-tp-ak\sw\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF195610-3F4D-44B3-9BEF-DDE3E1F20168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223E2441-0589-4651-9B83-F68C468B083D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="398">
   <si>
     <t>PA25</t>
   </si>
@@ -1190,10 +1190,49 @@
     <t>Free Pins: 2</t>
   </si>
   <si>
-    <t>Free Pins: 4</t>
-  </si>
-  <si>
-    <t>(6 if including PA0/1)</t>
+    <t>Keypad Output 1</t>
+  </si>
+  <si>
+    <t>Keypad Output 2</t>
+  </si>
+  <si>
+    <t>Keypad Output 3</t>
+  </si>
+  <si>
+    <t>Keypad Input 1</t>
+  </si>
+  <si>
+    <t>Keypad Input 2</t>
+  </si>
+  <si>
+    <t>Keypad Input 3</t>
+  </si>
+  <si>
+    <t>Keypad Output 4</t>
+  </si>
+  <si>
+    <t>Keypad Input 4</t>
+  </si>
+  <si>
+    <t>Flywheels</t>
+  </si>
+  <si>
+    <t>LEDs</t>
+  </si>
+  <si>
+    <t>Free Pins: 3</t>
+  </si>
+  <si>
+    <t>(5 if including PA0/1)</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>+3V3</t>
+  </si>
+  <si>
+    <t>GND</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1464,6 +1503,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12573,7 +12615,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>3</v>
@@ -12589,12 +12631,12 @@
       <c r="F2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="23" t="s">
-        <v>211</v>
-      </c>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>210</v>
+      </c>
       <c r="B3" s="24" t="s">
         <v>15</v>
       </c>
@@ -12628,12 +12670,12 @@
         <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>37</v>
@@ -12654,7 +12696,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>38</v>
@@ -12674,7 +12716,9 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>395</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>172</v>
       </c>
@@ -12693,7 +12737,9 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
+      <c r="A8" s="38" t="s">
+        <v>396</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>173</v>
       </c>
@@ -12712,7 +12758,9 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>397</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>174</v>
       </c>
@@ -12753,7 +12801,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>10</v>
@@ -12768,11 +12816,13 @@
       <c r="F11" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="25" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>11</v>
@@ -12835,7 +12885,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>14</v>
@@ -12875,7 +12925,7 @@
         <v>28</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
@@ -13000,7 +13050,9 @@
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>395</v>
+      </c>
       <c r="B23" s="2" t="s">
         <v>37</v>
       </c>
@@ -13014,13 +13066,17 @@
       <c r="F23" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="27"/>
+      <c r="G23" t="s">
+        <v>391</v>
+      </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A24" s="1"/>
+      <c r="A24" s="1" t="s">
+        <v>395</v>
+      </c>
       <c r="B24" s="2" t="s">
         <v>38</v>
       </c>
@@ -13034,12 +13090,17 @@
       <c r="F24" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="G24" t="s">
+        <v>392</v>
+      </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A25" s="1"/>
+      <c r="A25" s="1" t="s">
+        <v>395</v>
+      </c>
       <c r="B25" s="2" t="s">
         <v>172</v>
       </c>
@@ -13061,7 +13122,9 @@
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A26" s="1"/>
+      <c r="A26" s="38" t="s">
+        <v>396</v>
+      </c>
       <c r="B26" s="2" t="s">
         <v>173</v>
       </c>
@@ -13083,7 +13146,9 @@
       <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A27" s="1"/>
+      <c r="A27" s="1" t="s">
+        <v>397</v>
+      </c>
       <c r="B27" s="2" t="s">
         <v>174</v>
       </c>
@@ -19411,13 +19476,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B36"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B37"/>
     </row>

--- a/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
+++ b/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghakk\ece445l_lab7-10_fall26-4-ew-js-tp-ak\sw\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223E2441-0589-4651-9B83-F68C468B083D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071FD2E4-C11F-4AB9-A625-5AE9B0CA35B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="417">
   <si>
     <t>PA25</t>
   </si>
@@ -1187,9 +1187,6 @@
     <t>uC - SPI0_PICO</t>
   </si>
   <si>
-    <t>Free Pins: 2</t>
-  </si>
-  <si>
     <t>Keypad Output 1</t>
   </si>
   <si>
@@ -1220,12 +1217,6 @@
     <t>LEDs</t>
   </si>
   <si>
-    <t>Free Pins: 3</t>
-  </si>
-  <si>
-    <t>(5 if including PA0/1)</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -1233,6 +1224,96 @@
   </si>
   <si>
     <t>GND</t>
+  </si>
+  <si>
+    <t>ESP8266 Reset</t>
+  </si>
+  <si>
+    <t>ESP8266 GPIO2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Free Pins: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+  </si>
+  <si>
+    <t>Smoke Enable</t>
+  </si>
+  <si>
+    <t>(4 if including PA0/1)</t>
+  </si>
+  <si>
+    <t>Key:</t>
+  </si>
+  <si>
+    <t>Keypad</t>
+  </si>
+  <si>
+    <t>Screen</t>
+  </si>
+  <si>
+    <t>SPI - uC</t>
+  </si>
+  <si>
+    <t>Electromech</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t>Wifi Module</t>
+  </si>
+  <si>
+    <t>ID Reader</t>
+  </si>
+  <si>
+    <t>Flash</t>
+  </si>
+  <si>
+    <t>80MHz SiO2</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Unused</t>
+  </si>
+  <si>
+    <t>NC/Free</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Free Pins: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1323,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1273,8 +1354,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1308,6 +1403,72 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7C80"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99CCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCC00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9999FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1404,7 +1565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1503,8 +1664,83 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1514,16 +1750,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF99FF"/>
+      <color rgb="FF9999FF"/>
+      <color rgb="FFFFFFCC"/>
+      <color rgb="FFCCCC00"/>
+      <color rgb="FFCCFFFF"/>
+      <color rgb="FFCCFFCC"/>
       <color rgb="FF99CCFF"/>
+      <color rgb="FFFFCCFF"/>
       <color rgb="FFFF7C80"/>
-      <color rgb="FFCCFFFF"/>
-      <color rgb="FFFFCCFF"/>
-      <color rgb="FFCCCC00"/>
-      <color rgb="FFFFFFCC"/>
       <color rgb="FFDDDDDD"/>
-      <color rgb="FF9999FF"/>
-      <color rgb="FFFF99FF"/>
-      <color rgb="FFCCFFCC"/>
     </mruColors>
   </colors>
   <extLst>
@@ -5501,15 +5737,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>400050</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>58964</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>419862</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>151738</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>210312</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>29273</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5532,8 +5768,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7231380" y="182880"/>
-          <a:ext cx="7125462" cy="5089498"/>
+          <a:off x="7902121" y="240393"/>
+          <a:ext cx="7103691" cy="5050309"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12588,7 +12824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC81E62-902F-426A-8169-496CDAF34664}">
-  <dimension ref="A1:XEU44"/>
+  <dimension ref="A1:XEU49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.54296875" customWidth="1"/>
@@ -12599,6 +12835,7 @@
     <col min="6" max="6" width="9.08984375" style="2" customWidth="1"/>
     <col min="7" max="7" width="30.36328125" customWidth="1"/>
     <col min="8" max="8" width="5.90625" customWidth="1"/>
+    <col min="9" max="9" width="10.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -12612,12 +12849,15 @@
         <v>91</v>
       </c>
       <c r="G1" s="7"/>
+      <c r="I1" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="44" t="s">
+        <v>389</v>
+      </c>
+      <c r="B2" s="39" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="18">
@@ -12628,16 +12868,21 @@
         <f t="shared" ref="E2:E15" si="0">E3+1</f>
         <v>32</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="23"/>
+      <c r="G2" s="59" t="s">
+        <v>395</v>
+      </c>
+      <c r="I2" s="43" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="47" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="3">
@@ -12647,16 +12892,19 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="48" t="s">
         <v>213</v>
       </c>
+      <c r="I3" s="46" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="72"/>
+      <c r="B4" s="39" t="s">
         <v>171</v>
       </c>
       <c r="C4" s="3">
@@ -12666,18 +12914,21 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="G4" t="s">
-        <v>388</v>
+      <c r="G4" s="43" t="s">
+        <v>387</v>
+      </c>
+      <c r="I4" s="51" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>37</v>
       </c>
       <c r="C5" s="3">
@@ -12687,18 +12938,21 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="58" t="s">
         <v>376</v>
       </c>
+      <c r="I5" s="55" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="44" t="s">
+        <v>383</v>
+      </c>
+      <c r="B6" s="39" t="s">
         <v>38</v>
       </c>
       <c r="C6" s="3">
@@ -12708,18 +12962,21 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="57" t="s">
         <v>377</v>
       </c>
+      <c r="I6" s="56" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="62" t="s">
+        <v>392</v>
+      </c>
+      <c r="B7" s="39" t="s">
         <v>172</v>
       </c>
       <c r="C7" s="3">
@@ -12729,18 +12986,21 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="64" t="s">
         <v>158</v>
       </c>
+      <c r="I7" s="57" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
-        <v>396</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="71" t="s">
+        <v>393</v>
+      </c>
+      <c r="B8" s="39" t="s">
         <v>173</v>
       </c>
       <c r="C8" s="3">
@@ -12750,18 +13010,21 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="65" t="s">
         <v>156</v>
       </c>
+      <c r="I8" s="63" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="72" t="s">
+        <v>394</v>
+      </c>
+      <c r="B9" s="39" t="s">
         <v>174</v>
       </c>
       <c r="C9" s="3">
@@ -12771,18 +13034,21 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="49" t="s">
         <v>209</v>
       </c>
+      <c r="I9" s="64" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="50" t="s">
         <v>372</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3">
@@ -12792,18 +13058,21 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="49" t="s">
         <v>208</v>
       </c>
+      <c r="I10" s="66" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="44" t="s">
+        <v>384</v>
+      </c>
+      <c r="B11" s="39" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3">
@@ -12813,18 +13082,21 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="G11" s="25" t="s">
-        <v>207</v>
+      <c r="G11" s="58" t="s">
+        <v>396</v>
+      </c>
+      <c r="I11" s="68" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="44" t="s">
+        <v>385</v>
+      </c>
+      <c r="B12" s="39" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3">
@@ -12834,18 +13106,21 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="39" t="s">
         <v>24</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>362</v>
       </c>
+      <c r="I12" s="61" t="s">
+        <v>413</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="3">
@@ -12855,18 +13130,21 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="51" t="s">
         <v>373</v>
       </c>
+      <c r="I13" s="70" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="39" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3">
@@ -12876,18 +13154,21 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="49" t="s">
         <v>212</v>
       </c>
+      <c r="I14" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="44" t="s">
+        <v>386</v>
+      </c>
+      <c r="B15" s="39" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3">
@@ -12897,10 +13178,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="51" t="s">
         <v>374</v>
       </c>
       <c r="I15" s="7"/>
@@ -12908,10 +13189,10 @@
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="60" t="s">
         <v>378</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="39" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="3">
@@ -12921,21 +13202,21 @@
         <f>E17+1</f>
         <v>18</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>389</v>
+      <c r="G16" s="45" t="s">
+        <v>388</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
     <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="60" t="s">
         <v>379</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="39" t="s">
         <v>88</v>
       </c>
       <c r="C17" s="5">
@@ -12945,10 +13226,10 @@
       <c r="E17" s="6">
         <v>17</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="52" t="s">
         <v>375</v>
       </c>
       <c r="I17" s="7"/>
@@ -12956,33 +13237,38 @@
       <c r="K17" s="7"/>
     </row>
     <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>382</v>
-      </c>
+      <c r="A18" s="38" t="s">
+        <v>397</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="40"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" s="40" t="s">
         <v>370</v>
       </c>
+      <c r="B19" s="38"/>
       <c r="C19" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G19" s="7"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="42"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="53" t="s">
         <v>365</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="39" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="18">
@@ -12993,10 +13279,10 @@
         <f t="shared" ref="E20:E33" si="1">E21+1</f>
         <v>32</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="48" t="s">
         <v>211</v>
       </c>
       <c r="I20" s="7"/>
@@ -13004,10 +13290,10 @@
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="47" t="s">
         <v>210</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="3">
@@ -13017,10 +13303,10 @@
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="48" t="s">
         <v>213</v>
       </c>
       <c r="I21" s="7"/>
@@ -13028,8 +13314,8 @@
       <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="72"/>
+      <c r="B22" s="39" t="s">
         <v>171</v>
       </c>
       <c r="C22" s="3">
@@ -13039,10 +13325,10 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="G22" s="54" t="s">
         <v>366</v>
       </c>
       <c r="I22" s="7"/>
@@ -13050,10 +13336,10 @@
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="A23" s="62" t="s">
+        <v>392</v>
+      </c>
+      <c r="B23" s="39" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="3">
@@ -13063,21 +13349,21 @@
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="G23" t="s">
-        <v>391</v>
+      <c r="G23" s="55" t="s">
+        <v>390</v>
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="69" t="s">
+        <v>398</v>
+      </c>
+      <c r="B24" s="39" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="3">
@@ -13087,21 +13373,21 @@
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="G24" t="s">
-        <v>392</v>
+      <c r="G24" s="68" t="s">
+        <v>391</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="A25" s="62" t="s">
+        <v>392</v>
+      </c>
+      <c r="B25" s="39" t="s">
         <v>172</v>
       </c>
       <c r="C25" s="3">
@@ -13111,10 +13397,10 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="64" t="s">
         <v>158</v>
       </c>
       <c r="I25" s="7"/>
@@ -13122,10 +13408,10 @@
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A26" s="38" t="s">
-        <v>396</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="A26" s="71" t="s">
+        <v>393</v>
+      </c>
+      <c r="B26" s="39" t="s">
         <v>173</v>
       </c>
       <c r="C26" s="3">
@@ -13135,10 +13421,10 @@
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="65" t="s">
         <v>156</v>
       </c>
       <c r="I26" s="7"/>
@@ -13146,10 +13432,10 @@
       <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="A27" s="72" t="s">
+        <v>394</v>
+      </c>
+      <c r="B27" s="39" t="s">
         <v>174</v>
       </c>
       <c r="C27" s="3">
@@ -13159,10 +13445,10 @@
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="F27" s="24" t="s">
+      <c r="F27" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="G27" s="49" t="s">
         <v>209</v>
       </c>
       <c r="I27" s="7"/>
@@ -13170,10 +13456,10 @@
       <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="50" t="s">
         <v>372</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="3">
@@ -13183,10 +13469,10 @@
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="G28" s="25" t="s">
+      <c r="G28" s="49" t="s">
         <v>208</v>
       </c>
       <c r="I28" s="7"/>
@@ -13194,8 +13480,10 @@
       <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A29" s="1"/>
-      <c r="B29" s="2" t="s">
+      <c r="A29" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="B29" s="39" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="3">
@@ -13205,19 +13493,19 @@
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="F29" s="24" t="s">
+      <c r="F29" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="G29" s="25" t="s">
+      <c r="G29" s="49" t="s">
         <v>207</v>
       </c>
       <c r="K29" s="7"/>
     </row>
     <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="50" t="s">
         <v>380</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="39" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="3">
@@ -13227,7 +13515,7 @@
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="39" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="28" t="s">
@@ -13237,10 +13525,10 @@
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="3">
@@ -13250,8 +13538,11 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="39" t="s">
         <v>39</v>
+      </c>
+      <c r="G31" s="73" t="s">
+        <v>414</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -19393,10 +19684,10 @@
       <c r="XEU31" s="2"/>
     </row>
     <row r="32" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="39" t="s">
         <v>13</v>
       </c>
       <c r="C32" s="3">
@@ -19406,16 +19697,18 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="25" t="s">
+      <c r="G32" s="49" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="1"/>
-      <c r="B33" s="2" t="s">
+      <c r="A33" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="B33" s="39" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="3">
@@ -19425,18 +19718,18 @@
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="55" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="53" t="s">
         <v>367</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="39" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="3">
@@ -19446,18 +19739,18 @@
         <f>E35+1</f>
         <v>18</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="51" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="50" t="s">
         <v>381</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="39" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="5">
@@ -19467,22 +19760,22 @@
       <c r="E35" s="6">
         <v>17</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="54" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="B36"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B37"/>
     </row>
@@ -19516,6 +19809,11 @@
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>416</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
+++ b/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghakk\ece445l_lab7-10_fall26-4-ew-js-tp-ak\sw\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eganw\ece445l_lab7-10_fall26-4-ew-js-tp-ak\sw\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071FD2E4-C11F-4AB9-A625-5AE9B0CA35B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D69A5EC-FFC8-44F9-8CFA-AC84E841CCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VSSOP-32" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="418">
   <si>
     <t>PA25</t>
   </si>
@@ -1212,9 +1212,6 @@
   </si>
   <si>
     <t>Flywheels</t>
-  </si>
-  <si>
-    <t>LEDs</t>
   </si>
   <si>
     <t>NC</t>
@@ -1314,6 +1311,12 @@
   </si>
   <si>
     <t>S</t>
+  </si>
+  <si>
+    <t>LED Group 1</t>
+  </si>
+  <si>
+    <t>LED Group 2</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1664,18 +1667,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1738,9 +1731,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6183,19 +6173,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:XEU44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.54296875" customWidth="1"/>
+    <col min="1" max="1" width="23.5546875" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.08984375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="6" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.36328125" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -6207,7 +6197,7 @@
       </c>
       <c r="G1" s="7"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>364</v>
       </c>
@@ -6229,7 +6219,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>210</v>
       </c>
@@ -6250,7 +6240,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>171</v>
@@ -6269,7 +6259,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>363</v>
       </c>
@@ -6290,7 +6280,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>363</v>
       </c>
@@ -6311,7 +6301,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>172</v>
@@ -6330,7 +6320,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>173</v>
@@ -6349,7 +6339,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>174</v>
@@ -6368,7 +6358,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>363</v>
       </c>
@@ -6389,7 +6379,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>363</v>
       </c>
@@ -6410,7 +6400,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>364</v>
       </c>
@@ -6431,7 +6421,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>176</v>
       </c>
@@ -6452,7 +6442,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>175</v>
       </c>
@@ -6473,7 +6463,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>364</v>
       </c>
@@ -6497,7 +6487,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>134</v>
       </c>
@@ -6521,7 +6511,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>137</v>
       </c>
@@ -6545,13 +6535,13 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>324</v>
       </c>
@@ -6563,12 +6553,12 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>331</v>
       </c>
@@ -6576,7 +6566,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>332</v>
       </c>
@@ -6584,27 +6574,27 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -6612,19 +6602,19 @@
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -12769,48 +12759,48 @@
       <c r="XET31" s="2"/>
       <c r="XEU31" s="2"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B33"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B34"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B35"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B36"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B37"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B38"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="14"/>
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="15"/>
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
@@ -12825,20 +12815,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC81E62-902F-426A-8169-496CDAF34664}">
   <dimension ref="A1:XEU49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.54296875" customWidth="1"/>
+    <col min="1" max="1" width="23.5546875" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.54296875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.08984375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="6" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.36328125" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" customWidth="1"/>
-    <col min="9" max="9" width="10.90625" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>369</v>
       </c>
@@ -12850,14 +12840,14 @@
       </c>
       <c r="G1" s="7"/>
       <c r="I1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="44" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="40" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="18">
@@ -12868,21 +12858,21 @@
         <f t="shared" ref="E2:E15" si="0">E3+1</f>
         <v>32</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="59" t="s">
-        <v>395</v>
-      </c>
-      <c r="I2" s="43" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="47" t="s">
+      <c r="G2" s="55" t="s">
+        <v>394</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="3">
@@ -12892,19 +12882,19 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="48" t="s">
+      <c r="G3" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="I3" s="46" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="72"/>
-      <c r="B4" s="39" t="s">
+      <c r="I3" s="42" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="68"/>
+      <c r="B4" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C4" s="3">
@@ -12914,21 +12904,21 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="39" t="s">
         <v>387</v>
       </c>
-      <c r="I4" s="51" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="44" t="s">
+      <c r="I4" s="47" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="40" t="s">
         <v>382</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C5" s="3">
@@ -12938,21 +12928,21 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="58" t="s">
+      <c r="G5" s="54" t="s">
         <v>376</v>
       </c>
-      <c r="I5" s="55" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="44" t="s">
+      <c r="I5" s="51" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="40" t="s">
         <v>383</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C6" s="3">
@@ -12962,21 +12952,21 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="F6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="53" t="s">
         <v>377</v>
       </c>
-      <c r="I6" s="56" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="62" t="s">
-        <v>392</v>
-      </c>
-      <c r="B7" s="39" t="s">
+      <c r="I6" s="52" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="58" t="s">
+        <v>391</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C7" s="3">
@@ -12986,21 +12976,21 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="F7" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="60" t="s">
         <v>158</v>
       </c>
-      <c r="I7" s="57" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="71" t="s">
-        <v>393</v>
-      </c>
-      <c r="B8" s="39" t="s">
+      <c r="I7" s="53" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C8" s="3">
@@ -13010,21 +13000,21 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G8" s="65" t="s">
+      <c r="G8" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="I8" s="63" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="72" t="s">
-        <v>394</v>
-      </c>
-      <c r="B9" s="39" t="s">
+      <c r="I8" s="59" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="68" t="s">
+        <v>393</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C9" s="3">
@@ -13034,21 +13024,21 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="F9" s="39" t="s">
+      <c r="F9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="49" t="s">
+      <c r="G9" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="I9" s="64" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="50" t="s">
+      <c r="I9" s="60" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="46" t="s">
         <v>372</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3">
@@ -13058,21 +13048,21 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="I10" s="66" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="44" t="s">
+      <c r="I10" s="62" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="40" t="s">
         <v>384</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3">
@@ -13082,21 +13072,21 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G11" s="58" t="s">
-        <v>396</v>
-      </c>
-      <c r="I11" s="68" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="44" t="s">
+      <c r="G11" s="54" t="s">
+        <v>395</v>
+      </c>
+      <c r="I11" s="64" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="40" t="s">
         <v>385</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3">
@@ -13106,21 +13096,21 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="F12" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>362</v>
       </c>
-      <c r="I12" s="61" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="67" t="s">
+      <c r="I12" s="57" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="63" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="3">
@@ -13130,21 +13120,21 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="51" t="s">
+      <c r="G13" s="47" t="s">
         <v>373</v>
       </c>
-      <c r="I13" s="70" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="67" t="s">
+      <c r="I13" s="66" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="63" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3">
@@ -13154,21 +13144,21 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="49" t="s">
+      <c r="G14" s="45" t="s">
         <v>212</v>
       </c>
       <c r="I14" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="44" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="40" t="s">
         <v>386</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3">
@@ -13178,21 +13168,21 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="51" t="s">
+      <c r="G15" s="47" t="s">
         <v>374</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="60" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="56" t="s">
         <v>378</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="3">
@@ -13202,21 +13192,21 @@
         <f>E17+1</f>
         <v>18</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="45" t="s">
+      <c r="G16" s="41" t="s">
         <v>388</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A17" s="60" t="s">
+    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A17" s="56" t="s">
         <v>379</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C17" s="5">
@@ -13226,49 +13216,44 @@
       <c r="E17" s="6">
         <v>17</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="52" t="s">
+      <c r="G17" s="48" t="s">
         <v>375</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A18" s="38" t="s">
-        <v>397</v>
-      </c>
-      <c r="B18" s="38"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="40"/>
+    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>396</v>
+      </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A19" s="40" t="s">
+    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>370</v>
       </c>
-      <c r="B19" s="38"/>
       <c r="C19" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="42"/>
+      <c r="G19" s="7"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A20" s="53" t="s">
+    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A20" s="49" t="s">
         <v>365</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="18">
@@ -13279,21 +13264,21 @@
         <f t="shared" ref="E20:E33" si="1">E21+1</f>
         <v>32</v>
       </c>
-      <c r="F20" s="41" t="s">
+      <c r="F20" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="G20" s="48" t="s">
+      <c r="G20" s="44" t="s">
         <v>211</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A21" s="47" t="s">
+    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A21" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="3">
@@ -13303,19 +13288,19 @@
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="F21" s="41" t="s">
+      <c r="F21" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="48" t="s">
+      <c r="G21" s="44" t="s">
         <v>213</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A22" s="72"/>
-      <c r="B22" s="39" t="s">
+    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A22" s="68"/>
+      <c r="B22" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C22" s="3">
@@ -13325,21 +13310,21 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="F22" s="39" t="s">
+      <c r="F22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="54" t="s">
+      <c r="G22" s="50" t="s">
         <v>366</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A23" s="62" t="s">
-        <v>392</v>
-      </c>
-      <c r="B23" s="39" t="s">
+    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A23" s="58" t="s">
+        <v>391</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="3">
@@ -13349,21 +13334,21 @@
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="F23" s="39" t="s">
+      <c r="F23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="55" t="s">
+      <c r="G23" s="51" t="s">
         <v>390</v>
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A24" s="69" t="s">
-        <v>398</v>
-      </c>
-      <c r="B24" s="39" t="s">
+    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A24" s="65" t="s">
+        <v>397</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="3">
@@ -13373,21 +13358,21 @@
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="F24" s="39" t="s">
+      <c r="F24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G24" s="68" t="s">
-        <v>391</v>
+      <c r="G24" s="64" t="s">
+        <v>416</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A25" s="62" t="s">
-        <v>392</v>
-      </c>
-      <c r="B25" s="39" t="s">
+    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A25" s="58" t="s">
+        <v>391</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C25" s="3">
@@ -13397,21 +13382,21 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="F25" s="39" t="s">
+      <c r="F25" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G25" s="64" t="s">
+      <c r="G25" s="60" t="s">
         <v>158</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A26" s="71" t="s">
-        <v>393</v>
-      </c>
-      <c r="B26" s="39" t="s">
+    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A26" s="67" t="s">
+        <v>392</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C26" s="3">
@@ -13421,21 +13406,21 @@
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="F26" s="39" t="s">
+      <c r="F26" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G26" s="65" t="s">
+      <c r="G26" s="61" t="s">
         <v>156</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A27" s="72" t="s">
-        <v>394</v>
-      </c>
-      <c r="B27" s="39" t="s">
+    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A27" s="68" t="s">
+        <v>393</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C27" s="3">
@@ -13445,21 +13430,21 @@
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="F27" s="39" t="s">
+      <c r="F27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="49" t="s">
+      <c r="G27" s="45" t="s">
         <v>209</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A28" s="50" t="s">
+    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A28" s="46" t="s">
         <v>372</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="3">
@@ -13469,21 +13454,21 @@
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="F28" s="39" t="s">
+      <c r="F28" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G28" s="49" t="s">
+      <c r="G28" s="45" t="s">
         <v>208</v>
       </c>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A29" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="B29" s="39" t="s">
+    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A29" s="58" t="s">
+        <v>413</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="3">
@@ -13493,19 +13478,19 @@
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="F29" s="39" t="s">
+      <c r="F29" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G29" s="49" t="s">
+      <c r="G29" s="45" t="s">
         <v>207</v>
       </c>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A30" s="50" t="s">
+    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A30" s="46" t="s">
         <v>380</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="3">
@@ -13515,7 +13500,7 @@
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="F30" s="39" t="s">
+      <c r="F30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="28" t="s">
@@ -13524,11 +13509,11 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A31" s="67" t="s">
+    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A31" s="63" t="s">
         <v>176</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="3">
@@ -13538,11 +13523,11 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="F31" s="39" t="s">
+      <c r="F31" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G31" s="73" t="s">
-        <v>414</v>
+      <c r="G31" s="64" t="s">
+        <v>417</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -19683,11 +19668,11 @@
       <c r="XET31" s="2"/>
       <c r="XEU31" s="2"/>
     </row>
-    <row r="32" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
-      <c r="A32" s="67" t="s">
+    <row r="32" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+      <c r="A32" s="63" t="s">
         <v>175</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C32" s="3">
@@ -19697,18 +19682,18 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="F32" s="39" t="s">
+      <c r="F32" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="49" t="s">
+      <c r="G32" s="45" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="B33" s="39" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="58" t="s">
+        <v>413</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="3">
@@ -19718,18 +19703,18 @@
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="F33" s="39" t="s">
+      <c r="F33" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G33" s="55" t="s">
+      <c r="G33" s="51" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="53" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="49" t="s">
         <v>367</v>
       </c>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="3">
@@ -19739,18 +19724,18 @@
         <f>E35+1</f>
         <v>18</v>
       </c>
-      <c r="F34" s="39" t="s">
+      <c r="F34" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G34" s="51" t="s">
+      <c r="G34" s="47" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="50" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="46" t="s">
         <v>381</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="5">
@@ -19760,59 +19745,59 @@
       <c r="E35" s="6">
         <v>17</v>
       </c>
-      <c r="F35" s="39" t="s">
+      <c r="F35" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G35" s="54" t="s">
+      <c r="G35" s="50" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B36"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B37"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B38"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="14"/>
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="15"/>
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -19825,22 +19810,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E972CE-2F8B-4DAB-AD48-DA87002CAF65}">
   <dimension ref="A1:O44"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.90625" style="31" customWidth="1"/>
-    <col min="2" max="2" width="11.08984375" style="30" customWidth="1"/>
-    <col min="3" max="3" width="27.08984375" style="30" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" style="31" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="30" customWidth="1"/>
+    <col min="3" max="3" width="27.109375" style="30" customWidth="1"/>
     <col min="4" max="4" width="14" style="30" customWidth="1"/>
-    <col min="5" max="5" width="14.6328125" style="30" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" style="30" customWidth="1"/>
     <col min="6" max="6" width="24" style="30" customWidth="1"/>
-    <col min="7" max="7" width="12.6328125" style="30" customWidth="1"/>
-    <col min="8" max="8" width="29.6328125" style="30" customWidth="1"/>
-    <col min="9" max="9" width="14.36328125" style="30" customWidth="1"/>
-    <col min="10" max="10" width="9.08984375" style="36"/>
-    <col min="11" max="16384" width="9.08984375" style="30"/>
+    <col min="7" max="7" width="12.6640625" style="30" customWidth="1"/>
+    <col min="8" max="8" width="29.6640625" style="30" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" style="30" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" style="36"/>
+    <col min="11" max="16384" width="9.109375" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="I1" s="30" t="s">
         <v>350</v>
       </c>
@@ -19848,7 +19833,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="I2" s="30">
         <f>SUM(I4:I51)</f>
         <v>36.134999999999998</v>
@@ -19858,7 +19843,7 @@
         <v>83.68</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>190</v>
       </c>
@@ -19893,7 +19878,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="31">
         <v>2</v>
       </c>
@@ -19920,7 +19905,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="31">
         <v>2</v>
       </c>
@@ -19953,7 +19938,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="31">
         <v>1</v>
       </c>
@@ -19980,7 +19965,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="31">
         <v>2</v>
       </c>
@@ -20007,7 +19992,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="31">
         <v>1</v>
       </c>
@@ -20040,7 +20025,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="31">
         <v>1</v>
       </c>
@@ -20067,7 +20052,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="31">
         <v>2</v>
       </c>
@@ -20097,7 +20082,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="31">
         <v>0</v>
       </c>
@@ -20127,7 +20112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="31">
         <v>1</v>
       </c>
@@ -20160,7 +20145,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="31">
         <v>1</v>
       </c>
@@ -20205,7 +20190,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="31">
         <v>0</v>
       </c>
@@ -20235,7 +20220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="31">
         <v>1</v>
       </c>
@@ -20271,7 +20256,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="31">
         <v>1</v>
       </c>
@@ -20307,7 +20292,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="31">
         <v>1</v>
       </c>
@@ -20343,7 +20328,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="31">
         <v>1</v>
       </c>
@@ -20375,7 +20360,7 @@
         <v>29.81</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="31">
         <v>1</v>
       </c>
@@ -20410,7 +20395,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="31">
         <v>2</v>
       </c>
@@ -20446,7 +20431,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="31">
         <v>1</v>
       </c>
@@ -20469,7 +20454,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="31">
         <v>1</v>
       </c>
@@ -20505,7 +20490,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="31">
         <v>2</v>
       </c>
@@ -20538,7 +20523,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="31">
         <v>1</v>
       </c>
@@ -20571,7 +20556,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="31">
         <v>2</v>
       </c>
@@ -20604,7 +20589,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="31">
         <v>1</v>
       </c>
@@ -20637,7 +20622,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="31">
         <v>0</v>
       </c>
@@ -20670,10 +20655,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B34" s="32"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="31">
         <v>5</v>
       </c>
@@ -20703,7 +20688,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="31">
         <v>1</v>
       </c>
@@ -20717,7 +20702,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="31">
         <v>1</v>
       </c>
@@ -20728,7 +20713,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="31">
         <v>1</v>
       </c>
@@ -20739,7 +20724,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="31">
         <v>1</v>
       </c>
@@ -20750,7 +20735,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="31">
         <v>1</v>
       </c>
@@ -20780,7 +20765,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="31">
         <v>1</v>
       </c>
@@ -20810,7 +20795,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="31">
         <v>1</v>
       </c>
@@ -20848,14 +20833,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E84313-7CEE-4179-AFC3-CFF55EB9327F}">
   <dimension ref="A1:M336"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.90625" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" customWidth="1"/>
-    <col min="7" max="7" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>69</v>
       </c>
@@ -20879,7 +20864,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -20901,7 +20886,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -20917,7 +20902,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -20951,7 +20936,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>10</v>
       </c>
@@ -20991,7 +20976,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>25</v>
       </c>
@@ -21032,7 +21017,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>35</v>
       </c>
@@ -21072,7 +21057,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L8">
         <f t="shared" si="0"/>
         <v>1839</v>
@@ -21082,7 +21067,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L9">
         <f t="shared" si="0"/>
         <v>1840</v>
@@ -21092,7 +21077,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L10">
         <f t="shared" si="0"/>
         <v>1841</v>
@@ -21102,7 +21087,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L11">
         <f t="shared" si="0"/>
         <v>1842</v>
@@ -21112,7 +21097,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L12">
         <f t="shared" si="0"/>
         <v>1843</v>
@@ -21122,7 +21107,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L13">
         <f t="shared" si="0"/>
         <v>1844</v>
@@ -21132,7 +21117,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L14">
         <f t="shared" si="0"/>
         <v>1845</v>
@@ -21142,7 +21127,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L15">
         <f t="shared" si="0"/>
         <v>1846</v>
@@ -21152,7 +21137,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L16">
         <f t="shared" si="0"/>
         <v>1847</v>
@@ -21162,7 +21147,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="17" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L17">
         <f t="shared" si="0"/>
         <v>1848</v>
@@ -21172,7 +21157,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="18" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L18">
         <f t="shared" si="0"/>
         <v>1849</v>
@@ -21182,7 +21167,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="19" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L19">
         <f t="shared" si="0"/>
         <v>1850</v>
@@ -21192,7 +21177,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="20" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L20">
         <f t="shared" si="0"/>
         <v>1851</v>
@@ -21202,7 +21187,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="21" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L21">
         <f t="shared" si="0"/>
         <v>1852</v>
@@ -21212,7 +21197,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="22" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L22">
         <f t="shared" si="0"/>
         <v>1853</v>
@@ -21222,7 +21207,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="23" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L23">
         <f t="shared" si="0"/>
         <v>1854</v>
@@ -21232,7 +21217,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="24" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L24">
         <f t="shared" si="0"/>
         <v>1855</v>
@@ -21242,7 +21227,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="25" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L25">
         <f t="shared" si="0"/>
         <v>1856</v>
@@ -21252,7 +21237,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="26" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L26">
         <f t="shared" si="0"/>
         <v>1857</v>
@@ -21262,7 +21247,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="27" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L27">
         <f t="shared" si="0"/>
         <v>1858</v>
@@ -21272,7 +21257,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="28" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L28">
         <f t="shared" si="0"/>
         <v>1859</v>
@@ -21282,7 +21267,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="29" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L29">
         <f t="shared" si="0"/>
         <v>1860</v>
@@ -21292,7 +21277,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="30" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L30">
         <f t="shared" si="0"/>
         <v>1861</v>
@@ -21302,7 +21287,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="31" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L31">
         <f t="shared" si="0"/>
         <v>1862</v>
@@ -21312,7 +21297,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="32" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L32">
         <f t="shared" si="0"/>
         <v>1863</v>
@@ -21322,7 +21307,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="33" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L33">
         <f t="shared" si="0"/>
         <v>1864</v>
@@ -21332,7 +21317,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="34" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L34">
         <f t="shared" si="0"/>
         <v>1865</v>
@@ -21342,7 +21327,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="35" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L35">
         <f t="shared" si="0"/>
         <v>1866</v>
@@ -21352,7 +21337,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="36" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L36">
         <f t="shared" si="0"/>
         <v>1867</v>
@@ -21362,7 +21347,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="37" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L37">
         <f t="shared" si="0"/>
         <v>1868</v>
@@ -21372,7 +21357,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="38" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L38">
         <f t="shared" si="0"/>
         <v>1869</v>
@@ -21382,7 +21367,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="39" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L39">
         <f t="shared" si="0"/>
         <v>1870</v>
@@ -21392,7 +21377,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="40" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L40">
         <f t="shared" si="0"/>
         <v>1871</v>
@@ -21402,7 +21387,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="41" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L41">
         <f t="shared" si="0"/>
         <v>1872</v>
@@ -21412,7 +21397,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="42" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L42">
         <f t="shared" si="0"/>
         <v>1873</v>
@@ -21422,7 +21407,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="43" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L43">
         <f t="shared" si="0"/>
         <v>1874</v>
@@ -21432,7 +21417,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="44" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L44">
         <f t="shared" si="0"/>
         <v>1875</v>
@@ -21442,7 +21427,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="45" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L45">
         <f t="shared" si="0"/>
         <v>1876</v>
@@ -21452,7 +21437,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="46" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L46">
         <f t="shared" si="0"/>
         <v>1877</v>
@@ -21462,7 +21447,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="47" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L47">
         <f t="shared" si="0"/>
         <v>1878</v>
@@ -21472,7 +21457,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="48" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L48">
         <f t="shared" si="0"/>
         <v>1879</v>
@@ -21482,7 +21467,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="49" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L49">
         <f t="shared" si="0"/>
         <v>1880</v>
@@ -21492,7 +21477,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="50" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L50">
         <f t="shared" si="0"/>
         <v>1881</v>
@@ -21502,7 +21487,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="51" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L51">
         <f t="shared" si="0"/>
         <v>1882</v>
@@ -21512,7 +21497,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="52" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L52">
         <f t="shared" si="0"/>
         <v>1883</v>
@@ -21522,7 +21507,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="53" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L53">
         <f t="shared" si="0"/>
         <v>1884</v>
@@ -21532,7 +21517,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="54" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L54">
         <f t="shared" si="0"/>
         <v>1885</v>
@@ -21542,7 +21527,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="55" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L55">
         <f t="shared" si="0"/>
         <v>1886</v>
@@ -21552,7 +21537,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="56" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L56">
         <f t="shared" si="0"/>
         <v>1887</v>
@@ -21562,7 +21547,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="57" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L57">
         <f t="shared" si="0"/>
         <v>1888</v>
@@ -21572,7 +21557,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="58" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L58">
         <f t="shared" si="0"/>
         <v>1889</v>
@@ -21582,7 +21567,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="59" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="59" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L59">
         <f t="shared" si="0"/>
         <v>1890</v>
@@ -21592,7 +21577,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="60" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L60">
         <f t="shared" si="0"/>
         <v>1891</v>
@@ -21602,7 +21587,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="61" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L61">
         <f t="shared" si="0"/>
         <v>1892</v>
@@ -21612,7 +21597,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="62" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L62">
         <f t="shared" si="0"/>
         <v>1893</v>
@@ -21622,7 +21607,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="63" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L63">
         <f t="shared" si="0"/>
         <v>1894</v>
@@ -21632,7 +21617,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="64" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L64">
         <f t="shared" si="0"/>
         <v>1895</v>
@@ -21642,7 +21627,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="65" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L65">
         <f t="shared" si="0"/>
         <v>1896</v>
@@ -21652,7 +21637,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="66" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="66" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L66">
         <f t="shared" si="0"/>
         <v>1897</v>
@@ -21662,7 +21647,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="67" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L67">
         <f t="shared" si="0"/>
         <v>1898</v>
@@ -21672,7 +21657,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="68" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L68">
         <f t="shared" ref="L68:L131" si="2">L67+1</f>
         <v>1899</v>
@@ -21682,7 +21667,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="69" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L69">
         <f t="shared" si="2"/>
         <v>1900</v>
@@ -21692,7 +21677,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="70" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L70">
         <f t="shared" si="2"/>
         <v>1901</v>
@@ -21702,7 +21687,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="71" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L71">
         <f t="shared" si="2"/>
         <v>1902</v>
@@ -21712,7 +21697,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="72" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L72">
         <f t="shared" si="2"/>
         <v>1903</v>
@@ -21722,7 +21707,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="73" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="73" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L73">
         <f t="shared" si="2"/>
         <v>1904</v>
@@ -21732,7 +21717,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="74" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="74" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L74">
         <f t="shared" si="2"/>
         <v>1905</v>
@@ -21742,7 +21727,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="75" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L75">
         <f t="shared" si="2"/>
         <v>1906</v>
@@ -21752,7 +21737,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="76" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L76">
         <f t="shared" si="2"/>
         <v>1907</v>
@@ -21762,7 +21747,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="77" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L77">
         <f t="shared" si="2"/>
         <v>1908</v>
@@ -21772,7 +21757,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="78" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L78">
         <f t="shared" si="2"/>
         <v>1909</v>
@@ -21782,7 +21767,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="79" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L79">
         <f t="shared" si="2"/>
         <v>1910</v>
@@ -21792,7 +21777,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="80" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L80">
         <f t="shared" si="2"/>
         <v>1911</v>
@@ -21802,7 +21787,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="81" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="81" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L81">
         <f t="shared" si="2"/>
         <v>1912</v>
@@ -21812,7 +21797,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="82" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="82" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L82">
         <f t="shared" si="2"/>
         <v>1913</v>
@@ -21822,7 +21807,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="83" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="83" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L83">
         <f t="shared" si="2"/>
         <v>1914</v>
@@ -21832,7 +21817,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="84" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="84" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L84">
         <f t="shared" si="2"/>
         <v>1915</v>
@@ -21842,7 +21827,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="85" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="85" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L85">
         <f t="shared" si="2"/>
         <v>1916</v>
@@ -21852,7 +21837,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="86" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="86" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L86">
         <f t="shared" si="2"/>
         <v>1917</v>
@@ -21862,7 +21847,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="87" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="87" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L87">
         <f t="shared" si="2"/>
         <v>1918</v>
@@ -21872,7 +21857,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="88" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="88" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L88">
         <f t="shared" si="2"/>
         <v>1919</v>
@@ -21882,7 +21867,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="89" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="89" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L89">
         <f t="shared" si="2"/>
         <v>1920</v>
@@ -21892,7 +21877,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="90" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="90" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L90">
         <f t="shared" si="2"/>
         <v>1921</v>
@@ -21902,7 +21887,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="91" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="91" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L91">
         <f t="shared" si="2"/>
         <v>1922</v>
@@ -21912,7 +21897,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="92" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="92" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L92">
         <f t="shared" si="2"/>
         <v>1923</v>
@@ -21922,7 +21907,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="93" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="93" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L93">
         <f t="shared" si="2"/>
         <v>1924</v>
@@ -21932,7 +21917,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="94" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="94" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L94">
         <f t="shared" si="2"/>
         <v>1925</v>
@@ -21942,7 +21927,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="95" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="95" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L95">
         <f t="shared" si="2"/>
         <v>1926</v>
@@ -21952,7 +21937,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="96" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="96" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L96">
         <f t="shared" si="2"/>
         <v>1927</v>
@@ -21962,7 +21947,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="97" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="97" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L97">
         <f t="shared" si="2"/>
         <v>1928</v>
@@ -21972,7 +21957,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="98" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="98" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L98">
         <f t="shared" si="2"/>
         <v>1929</v>
@@ -21982,7 +21967,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="99" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="99" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L99">
         <f t="shared" si="2"/>
         <v>1930</v>
@@ -21992,7 +21977,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="100" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="100" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L100">
         <f t="shared" si="2"/>
         <v>1931</v>
@@ -22002,7 +21987,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="101" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="101" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L101">
         <f t="shared" si="2"/>
         <v>1932</v>
@@ -22012,7 +21997,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="102" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="102" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L102">
         <f t="shared" si="2"/>
         <v>1933</v>
@@ -22022,7 +22007,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="103" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="103" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L103">
         <f t="shared" si="2"/>
         <v>1934</v>
@@ -22032,7 +22017,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="104" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="104" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L104">
         <f t="shared" si="2"/>
         <v>1935</v>
@@ -22042,7 +22027,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="105" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="105" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L105">
         <f t="shared" si="2"/>
         <v>1936</v>
@@ -22052,7 +22037,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="106" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="106" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L106">
         <f t="shared" si="2"/>
         <v>1937</v>
@@ -22062,7 +22047,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="107" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="107" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L107">
         <f t="shared" si="2"/>
         <v>1938</v>
@@ -22072,7 +22057,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="108" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="108" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L108">
         <f t="shared" si="2"/>
         <v>1939</v>
@@ -22082,7 +22067,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="109" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="109" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L109">
         <f t="shared" si="2"/>
         <v>1940</v>
@@ -22092,7 +22077,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="110" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="110" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L110">
         <f t="shared" si="2"/>
         <v>1941</v>
@@ -22102,7 +22087,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="111" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="111" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L111">
         <f t="shared" si="2"/>
         <v>1942</v>
@@ -22112,7 +22097,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="112" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="112" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L112">
         <f t="shared" si="2"/>
         <v>1943</v>
@@ -22122,7 +22107,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="113" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="113" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L113">
         <f t="shared" si="2"/>
         <v>1944</v>
@@ -22132,7 +22117,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="114" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="114" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L114">
         <f t="shared" si="2"/>
         <v>1945</v>
@@ -22142,7 +22127,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="115" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="115" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L115">
         <f t="shared" si="2"/>
         <v>1946</v>
@@ -22152,7 +22137,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="116" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="116" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L116">
         <f t="shared" si="2"/>
         <v>1947</v>
@@ -22162,7 +22147,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="117" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="117" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L117">
         <f t="shared" si="2"/>
         <v>1948</v>
@@ -22172,7 +22157,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="118" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="118" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L118">
         <f t="shared" si="2"/>
         <v>1949</v>
@@ -22182,7 +22167,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="119" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="119" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L119">
         <f t="shared" si="2"/>
         <v>1950</v>
@@ -22192,7 +22177,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="120" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="120" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L120">
         <f t="shared" si="2"/>
         <v>1951</v>
@@ -22202,7 +22187,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="121" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="121" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L121">
         <f t="shared" si="2"/>
         <v>1952</v>
@@ -22212,7 +22197,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="122" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="122" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L122">
         <f t="shared" si="2"/>
         <v>1953</v>
@@ -22222,7 +22207,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="123" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="123" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L123">
         <f t="shared" si="2"/>
         <v>1954</v>
@@ -22232,7 +22217,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="124" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="124" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L124">
         <f t="shared" si="2"/>
         <v>1955</v>
@@ -22242,7 +22227,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="125" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="125" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L125">
         <f t="shared" si="2"/>
         <v>1956</v>
@@ -22252,7 +22237,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="126" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="126" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L126">
         <f t="shared" si="2"/>
         <v>1957</v>
@@ -22262,7 +22247,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="127" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="127" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L127">
         <f t="shared" si="2"/>
         <v>1958</v>
@@ -22272,7 +22257,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="128" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="128" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L128">
         <f t="shared" si="2"/>
         <v>1959</v>
@@ -22282,7 +22267,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="129" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="129" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L129">
         <f t="shared" si="2"/>
         <v>1960</v>
@@ -22292,7 +22277,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="130" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="130" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L130">
         <f t="shared" si="2"/>
         <v>1961</v>
@@ -22302,7 +22287,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="131" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="131" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L131">
         <f t="shared" si="2"/>
         <v>1962</v>
@@ -22312,7 +22297,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="132" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="132" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L132">
         <f t="shared" ref="L132:L195" si="4">L131+1</f>
         <v>1963</v>
@@ -22322,7 +22307,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="133" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="133" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L133">
         <f t="shared" si="4"/>
         <v>1964</v>
@@ -22332,7 +22317,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="134" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="134" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L134">
         <f t="shared" si="4"/>
         <v>1965</v>
@@ -22342,7 +22327,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="135" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="135" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L135">
         <f t="shared" si="4"/>
         <v>1966</v>
@@ -22352,7 +22337,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="136" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="136" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L136">
         <f t="shared" si="4"/>
         <v>1967</v>
@@ -22362,7 +22347,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="137" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="137" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L137">
         <f t="shared" si="4"/>
         <v>1968</v>
@@ -22372,7 +22357,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="138" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="138" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L138">
         <f t="shared" si="4"/>
         <v>1969</v>
@@ -22382,7 +22367,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="139" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="139" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L139">
         <f t="shared" si="4"/>
         <v>1970</v>
@@ -22392,7 +22377,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="140" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="140" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L140">
         <f t="shared" si="4"/>
         <v>1971</v>
@@ -22402,7 +22387,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="141" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="141" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L141">
         <f t="shared" si="4"/>
         <v>1972</v>
@@ -22412,7 +22397,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="142" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="142" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L142">
         <f t="shared" si="4"/>
         <v>1973</v>
@@ -22422,7 +22407,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="143" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="143" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L143">
         <f t="shared" si="4"/>
         <v>1974</v>
@@ -22432,7 +22417,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="144" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="144" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L144">
         <f t="shared" si="4"/>
         <v>1975</v>
@@ -22442,7 +22427,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="145" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="145" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L145">
         <f t="shared" si="4"/>
         <v>1976</v>
@@ -22452,7 +22437,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="146" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="146" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L146">
         <f t="shared" si="4"/>
         <v>1977</v>
@@ -22462,7 +22447,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="147" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="147" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L147">
         <f t="shared" si="4"/>
         <v>1978</v>
@@ -22472,7 +22457,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="148" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="148" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L148">
         <f t="shared" si="4"/>
         <v>1979</v>
@@ -22482,7 +22467,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="149" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="149" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L149">
         <f t="shared" si="4"/>
         <v>1980</v>
@@ -22492,7 +22477,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="150" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="150" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L150">
         <f t="shared" si="4"/>
         <v>1981</v>
@@ -22502,7 +22487,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="151" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="151" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L151">
         <f t="shared" si="4"/>
         <v>1982</v>
@@ -22512,7 +22497,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="152" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="152" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L152">
         <f t="shared" si="4"/>
         <v>1983</v>
@@ -22522,7 +22507,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="153" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="153" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L153">
         <f t="shared" si="4"/>
         <v>1984</v>
@@ -22532,7 +22517,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="154" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="154" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L154">
         <f t="shared" si="4"/>
         <v>1985</v>
@@ -22542,7 +22527,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="155" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="155" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L155">
         <f t="shared" si="4"/>
         <v>1986</v>
@@ -22552,7 +22537,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="156" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="156" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L156">
         <f t="shared" si="4"/>
         <v>1987</v>
@@ -22562,7 +22547,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="157" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="157" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L157">
         <f t="shared" si="4"/>
         <v>1988</v>
@@ -22572,7 +22557,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="158" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="158" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L158">
         <f t="shared" si="4"/>
         <v>1989</v>
@@ -22582,7 +22567,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="159" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="159" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L159">
         <f t="shared" si="4"/>
         <v>1990</v>
@@ -22592,7 +22577,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="160" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="160" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L160">
         <f t="shared" si="4"/>
         <v>1991</v>
@@ -22602,7 +22587,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="161" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="161" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L161">
         <f t="shared" si="4"/>
         <v>1992</v>
@@ -22612,7 +22597,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="162" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="162" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L162">
         <f t="shared" si="4"/>
         <v>1993</v>
@@ -22622,7 +22607,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="163" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="163" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L163">
         <f t="shared" si="4"/>
         <v>1994</v>
@@ -22632,7 +22617,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="164" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="164" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L164">
         <f t="shared" si="4"/>
         <v>1995</v>
@@ -22642,7 +22627,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="165" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="165" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L165">
         <f t="shared" si="4"/>
         <v>1996</v>
@@ -22652,7 +22637,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="166" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="166" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L166">
         <f t="shared" si="4"/>
         <v>1997</v>
@@ -22662,7 +22647,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="167" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="167" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L167">
         <f t="shared" si="4"/>
         <v>1998</v>
@@ -22672,7 +22657,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="168" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="168" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L168">
         <f t="shared" si="4"/>
         <v>1999</v>
@@ -22682,7 +22667,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="169" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="169" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L169">
         <f t="shared" si="4"/>
         <v>2000</v>
@@ -22692,7 +22677,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="170" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="170" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L170">
         <f t="shared" si="4"/>
         <v>2001</v>
@@ -22702,7 +22687,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="171" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="171" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L171">
         <f t="shared" si="4"/>
         <v>2002</v>
@@ -22712,7 +22697,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="172" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="172" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L172">
         <f t="shared" si="4"/>
         <v>2003</v>
@@ -22722,7 +22707,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="173" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="173" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L173">
         <f t="shared" si="4"/>
         <v>2004</v>
@@ -22732,7 +22717,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="174" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="174" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L174">
         <f t="shared" si="4"/>
         <v>2005</v>
@@ -22742,7 +22727,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="175" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="175" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L175">
         <f t="shared" si="4"/>
         <v>2006</v>
@@ -22752,7 +22737,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="176" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="176" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L176">
         <f t="shared" si="4"/>
         <v>2007</v>
@@ -22762,7 +22747,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="177" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="177" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L177">
         <f t="shared" si="4"/>
         <v>2008</v>
@@ -22772,7 +22757,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="178" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="178" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L178">
         <f t="shared" si="4"/>
         <v>2009</v>
@@ -22782,7 +22767,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="179" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="179" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L179">
         <f t="shared" si="4"/>
         <v>2010</v>
@@ -22792,7 +22777,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="180" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="180" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L180">
         <f t="shared" si="4"/>
         <v>2011</v>
@@ -22802,7 +22787,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="181" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="181" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L181">
         <f t="shared" si="4"/>
         <v>2012</v>
@@ -22812,7 +22797,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="182" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="182" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L182">
         <f t="shared" si="4"/>
         <v>2013</v>
@@ -22822,7 +22807,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="183" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="183" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L183">
         <f t="shared" si="4"/>
         <v>2014</v>
@@ -22832,7 +22817,7 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="184" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="184" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L184">
         <f t="shared" si="4"/>
         <v>2015</v>
@@ -22842,7 +22827,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="185" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L185">
         <f t="shared" si="4"/>
         <v>2016</v>
@@ -22852,7 +22837,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="186" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="186" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L186">
         <f t="shared" si="4"/>
         <v>2017</v>
@@ -22862,7 +22847,7 @@
         <v>2270</v>
       </c>
     </row>
-    <row r="187" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="187" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L187">
         <f t="shared" si="4"/>
         <v>2018</v>
@@ -22872,7 +22857,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="188" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="188" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L188">
         <f t="shared" si="4"/>
         <v>2019</v>
@@ -22882,7 +22867,7 @@
         <v>2285</v>
       </c>
     </row>
-    <row r="189" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="189" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L189">
         <f t="shared" si="4"/>
         <v>2020</v>
@@ -22892,7 +22877,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="190" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="190" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L190">
         <f t="shared" si="4"/>
         <v>2021</v>
@@ -22902,7 +22887,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="191" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="191" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L191">
         <f t="shared" si="4"/>
         <v>2022</v>
@@ -22912,7 +22897,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="192" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="192" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L192">
         <f t="shared" si="4"/>
         <v>2023</v>
@@ -22922,7 +22907,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="193" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="193" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L193">
         <f t="shared" si="4"/>
         <v>2024</v>
@@ -22932,7 +22917,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="194" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="194" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L194">
         <f t="shared" si="4"/>
         <v>2025</v>
@@ -22942,7 +22927,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="195" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="195" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L195">
         <f t="shared" si="4"/>
         <v>2026</v>
@@ -22952,7 +22937,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="196" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="196" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L196">
         <f t="shared" ref="L196:L259" si="6">L195+1</f>
         <v>2027</v>
@@ -22962,7 +22947,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="197" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="197" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L197">
         <f t="shared" si="6"/>
         <v>2028</v>
@@ -22972,7 +22957,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="198" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="198" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L198">
         <f t="shared" si="6"/>
         <v>2029</v>
@@ -22982,7 +22967,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="199" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="199" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L199">
         <f t="shared" si="6"/>
         <v>2030</v>
@@ -22992,7 +22977,7 @@
         <v>2366</v>
       </c>
     </row>
-    <row r="200" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="200" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L200">
         <f t="shared" si="6"/>
         <v>2031</v>
@@ -23002,7 +22987,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="201" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="201" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L201">
         <f t="shared" si="6"/>
         <v>2032</v>
@@ -23012,7 +22997,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="202" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="202" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L202">
         <f t="shared" si="6"/>
         <v>2033</v>
@@ -23022,7 +23007,7 @@
         <v>2389</v>
       </c>
     </row>
-    <row r="203" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="203" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L203">
         <f t="shared" si="6"/>
         <v>2034</v>
@@ -23032,7 +23017,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="204" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="204" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L204">
         <f t="shared" si="6"/>
         <v>2035</v>
@@ -23042,7 +23027,7 @@
         <v>2404</v>
       </c>
     </row>
-    <row r="205" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="205" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L205">
         <f t="shared" si="6"/>
         <v>2036</v>
@@ -23052,7 +23037,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="206" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="206" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L206">
         <f t="shared" si="6"/>
         <v>2037</v>
@@ -23062,7 +23047,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="207" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="207" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L207">
         <f t="shared" si="6"/>
         <v>2038</v>
@@ -23072,7 +23057,7 @@
         <v>2426</v>
       </c>
     </row>
-    <row r="208" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="208" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L208">
         <f t="shared" si="6"/>
         <v>2039</v>
@@ -23082,7 +23067,7 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="209" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="209" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L209">
         <f t="shared" si="6"/>
         <v>2040</v>
@@ -23092,7 +23077,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="210" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="210" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L210">
         <f t="shared" si="6"/>
         <v>2041</v>
@@ -23102,7 +23087,7 @@
         <v>2448</v>
       </c>
     </row>
-    <row r="211" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="211" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L211">
         <f t="shared" si="6"/>
         <v>2042</v>
@@ -23112,7 +23097,7 @@
         <v>2455</v>
       </c>
     </row>
-    <row r="212" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="212" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L212">
         <f t="shared" si="6"/>
         <v>2043</v>
@@ -23122,7 +23107,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="213" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="213" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L213">
         <f t="shared" si="6"/>
         <v>2044</v>
@@ -23132,7 +23117,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="214" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="214" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L214">
         <f t="shared" si="6"/>
         <v>2045</v>
@@ -23142,7 +23127,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="215" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="215" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L215">
         <f t="shared" si="6"/>
         <v>2046</v>
@@ -23152,7 +23137,7 @@
         <v>2485</v>
       </c>
     </row>
-    <row r="216" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="216" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L216">
         <f t="shared" si="6"/>
         <v>2047</v>
@@ -23162,7 +23147,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="217" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="217" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L217">
         <f t="shared" si="6"/>
         <v>2048</v>
@@ -23172,7 +23157,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="218" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="218" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L218">
         <f t="shared" si="6"/>
         <v>2049</v>
@@ -23182,7 +23167,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="219" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="219" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L219">
         <f t="shared" si="6"/>
         <v>2050</v>
@@ -23192,7 +23177,7 @@
         <v>2515</v>
       </c>
     </row>
-    <row r="220" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="220" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L220">
         <f t="shared" si="6"/>
         <v>2051</v>
@@ -23202,7 +23187,7 @@
         <v>2522</v>
       </c>
     </row>
-    <row r="221" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="221" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L221">
         <f t="shared" si="6"/>
         <v>2052</v>
@@ -23212,7 +23197,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="222" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="222" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L222">
         <f t="shared" si="6"/>
         <v>2053</v>
@@ -23222,7 +23207,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="223" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="223" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L223">
         <f t="shared" si="6"/>
         <v>2054</v>
@@ -23232,7 +23217,7 @@
         <v>2545</v>
       </c>
     </row>
-    <row r="224" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="224" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L224">
         <f t="shared" si="6"/>
         <v>2055</v>
@@ -23242,7 +23227,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="225" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="225" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L225">
         <f t="shared" si="6"/>
         <v>2056</v>
@@ -23252,7 +23237,7 @@
         <v>2559</v>
       </c>
     </row>
-    <row r="226" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="226" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L226">
         <f t="shared" si="6"/>
         <v>2057</v>
@@ -23262,7 +23247,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="227" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="227" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L227">
         <f t="shared" si="6"/>
         <v>2058</v>
@@ -23272,7 +23257,7 @@
         <v>2574</v>
       </c>
     </row>
-    <row r="228" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="228" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L228">
         <f t="shared" si="6"/>
         <v>2059</v>
@@ -23282,7 +23267,7 @@
         <v>2582</v>
       </c>
     </row>
-    <row r="229" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="229" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L229">
         <f t="shared" si="6"/>
         <v>2060</v>
@@ -23292,7 +23277,7 @@
         <v>2589</v>
       </c>
     </row>
-    <row r="230" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="230" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L230">
         <f t="shared" si="6"/>
         <v>2061</v>
@@ -23302,7 +23287,7 @@
         <v>2596</v>
       </c>
     </row>
-    <row r="231" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="231" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L231">
         <f t="shared" si="6"/>
         <v>2062</v>
@@ -23312,7 +23297,7 @@
         <v>2604</v>
       </c>
     </row>
-    <row r="232" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="232" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L232">
         <f t="shared" si="6"/>
         <v>2063</v>
@@ -23322,7 +23307,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="233" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="233" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L233">
         <f t="shared" si="6"/>
         <v>2064</v>
@@ -23332,7 +23317,7 @@
         <v>2619</v>
       </c>
     </row>
-    <row r="234" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="234" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L234">
         <f t="shared" si="6"/>
         <v>2065</v>
@@ -23342,7 +23327,7 @@
         <v>2626</v>
       </c>
     </row>
-    <row r="235" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="235" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L235">
         <f t="shared" si="6"/>
         <v>2066</v>
@@ -23352,7 +23337,7 @@
         <v>2634</v>
       </c>
     </row>
-    <row r="236" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="236" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L236">
         <f t="shared" si="6"/>
         <v>2067</v>
@@ -23362,7 +23347,7 @@
         <v>2641</v>
       </c>
     </row>
-    <row r="237" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="237" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L237">
         <f t="shared" si="6"/>
         <v>2068</v>
@@ -23372,7 +23357,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="238" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="238" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L238">
         <f t="shared" si="6"/>
         <v>2069</v>
@@ -23382,7 +23367,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="239" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="239" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L239">
         <f t="shared" si="6"/>
         <v>2070</v>
@@ -23392,7 +23377,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="240" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="240" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L240">
         <f t="shared" si="6"/>
         <v>2071</v>
@@ -23402,7 +23387,7 @@
         <v>2671</v>
       </c>
     </row>
-    <row r="241" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="241" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L241">
         <f t="shared" si="6"/>
         <v>2072</v>
@@ -23412,7 +23397,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="242" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="242" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L242">
         <f t="shared" si="6"/>
         <v>2073</v>
@@ -23422,7 +23407,7 @@
         <v>2685</v>
       </c>
     </row>
-    <row r="243" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="243" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L243">
         <f t="shared" si="6"/>
         <v>2074</v>
@@ -23432,7 +23417,7 @@
         <v>2693</v>
       </c>
     </row>
-    <row r="244" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="244" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L244">
         <f t="shared" si="6"/>
         <v>2075</v>
@@ -23442,7 +23427,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="245" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="245" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L245">
         <f t="shared" si="6"/>
         <v>2076</v>
@@ -23452,7 +23437,7 @@
         <v>2708</v>
       </c>
     </row>
-    <row r="246" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="246" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L246">
         <f t="shared" si="6"/>
         <v>2077</v>
@@ -23462,7 +23447,7 @@
         <v>2715</v>
       </c>
     </row>
-    <row r="247" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="247" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L247">
         <f t="shared" si="6"/>
         <v>2078</v>
@@ -23472,7 +23457,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="248" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="248" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L248">
         <f t="shared" si="6"/>
         <v>2079</v>
@@ -23482,7 +23467,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="249" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="249" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L249">
         <f t="shared" si="6"/>
         <v>2080</v>
@@ -23492,7 +23477,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="250" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="250" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L250">
         <f t="shared" si="6"/>
         <v>2081</v>
@@ -23502,7 +23487,7 @@
         <v>2745</v>
       </c>
     </row>
-    <row r="251" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="251" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L251">
         <f t="shared" si="6"/>
         <v>2082</v>
@@ -23512,7 +23497,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="252" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="252" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L252">
         <f t="shared" si="6"/>
         <v>2083</v>
@@ -23522,7 +23507,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="253" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="253" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L253">
         <f t="shared" si="6"/>
         <v>2084</v>
@@ -23532,7 +23517,7 @@
         <v>2767</v>
       </c>
     </row>
-    <row r="254" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="254" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L254">
         <f t="shared" si="6"/>
         <v>2085</v>
@@ -23542,7 +23527,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="255" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="255" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L255">
         <f t="shared" si="6"/>
         <v>2086</v>
@@ -23552,7 +23537,7 @@
         <v>2782</v>
       </c>
     </row>
-    <row r="256" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="256" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L256">
         <f t="shared" si="6"/>
         <v>2087</v>
@@ -23562,7 +23547,7 @@
         <v>2789</v>
       </c>
     </row>
-    <row r="257" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="257" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L257">
         <f t="shared" si="6"/>
         <v>2088</v>
@@ -23572,7 +23557,7 @@
         <v>2797</v>
       </c>
     </row>
-    <row r="258" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="258" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L258">
         <f t="shared" si="6"/>
         <v>2089</v>
@@ -23582,7 +23567,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="259" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="259" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L259">
         <f t="shared" si="6"/>
         <v>2090</v>
@@ -23592,7 +23577,7 @@
         <v>2812</v>
       </c>
     </row>
-    <row r="260" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="260" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L260">
         <f t="shared" ref="L260:L323" si="8">L259+1</f>
         <v>2091</v>
@@ -23602,7 +23587,7 @@
         <v>2819</v>
       </c>
     </row>
-    <row r="261" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="261" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L261">
         <f t="shared" si="8"/>
         <v>2092</v>
@@ -23612,7 +23597,7 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="262" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="262" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L262">
         <f t="shared" si="8"/>
         <v>2093</v>
@@ -23622,7 +23607,7 @@
         <v>2834</v>
       </c>
     </row>
-    <row r="263" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="263" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L263">
         <f t="shared" si="8"/>
         <v>2094</v>
@@ -23632,7 +23617,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="264" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="264" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L264">
         <f t="shared" si="8"/>
         <v>2095</v>
@@ -23642,7 +23627,7 @@
         <v>2849</v>
       </c>
     </row>
-    <row r="265" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="265" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L265">
         <f t="shared" si="8"/>
         <v>2096</v>
@@ -23652,7 +23637,7 @@
         <v>2856</v>
       </c>
     </row>
-    <row r="266" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="266" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L266">
         <f t="shared" si="8"/>
         <v>2097</v>
@@ -23662,7 +23647,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="267" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="267" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L267">
         <f t="shared" si="8"/>
         <v>2098</v>
@@ -23672,7 +23657,7 @@
         <v>2871</v>
       </c>
     </row>
-    <row r="268" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="268" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L268">
         <f t="shared" si="8"/>
         <v>2099</v>
@@ -23682,7 +23667,7 @@
         <v>2878</v>
       </c>
     </row>
-    <row r="269" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="269" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L269">
         <f t="shared" si="8"/>
         <v>2100</v>
@@ -23692,7 +23677,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="270" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="270" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L270">
         <f t="shared" si="8"/>
         <v>2101</v>
@@ -23702,7 +23687,7 @@
         <v>2893</v>
       </c>
     </row>
-    <row r="271" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="271" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L271">
         <f t="shared" si="8"/>
         <v>2102</v>
@@ -23712,7 +23697,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="272" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="272" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L272">
         <f t="shared" si="8"/>
         <v>2103</v>
@@ -23722,7 +23707,7 @@
         <v>2908</v>
       </c>
     </row>
-    <row r="273" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="273" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L273">
         <f t="shared" si="8"/>
         <v>2104</v>
@@ -23732,7 +23717,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="274" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="274" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L274">
         <f t="shared" si="8"/>
         <v>2105</v>
@@ -23742,7 +23727,7 @@
         <v>2923</v>
       </c>
     </row>
-    <row r="275" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="275" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L275">
         <f t="shared" si="8"/>
         <v>2106</v>
@@ -23752,7 +23737,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="276" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="276" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L276">
         <f t="shared" si="8"/>
         <v>2107</v>
@@ -23762,7 +23747,7 @@
         <v>2938</v>
       </c>
     </row>
-    <row r="277" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="277" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L277">
         <f t="shared" si="8"/>
         <v>2108</v>
@@ -23772,7 +23757,7 @@
         <v>2945</v>
       </c>
     </row>
-    <row r="278" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="278" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L278">
         <f t="shared" si="8"/>
         <v>2109</v>
@@ -23782,7 +23767,7 @@
         <v>2953</v>
       </c>
     </row>
-    <row r="279" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="279" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L279">
         <f t="shared" si="8"/>
         <v>2110</v>
@@ -23792,7 +23777,7 @@
         <v>2960</v>
       </c>
     </row>
-    <row r="280" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="280" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L280">
         <f t="shared" si="8"/>
         <v>2111</v>
@@ -23802,7 +23787,7 @@
         <v>2967</v>
       </c>
     </row>
-    <row r="281" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="281" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L281">
         <f t="shared" si="8"/>
         <v>2112</v>
@@ -23812,7 +23797,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="282" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="282" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L282">
         <f t="shared" si="8"/>
         <v>2113</v>
@@ -23822,7 +23807,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="283" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="283" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L283">
         <f t="shared" si="8"/>
         <v>2114</v>
@@ -23832,7 +23817,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="284" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="284" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L284">
         <f t="shared" si="8"/>
         <v>2115</v>
@@ -23842,7 +23827,7 @@
         <v>2997</v>
       </c>
     </row>
-    <row r="285" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="285" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L285">
         <f t="shared" si="8"/>
         <v>2116</v>
@@ -23852,7 +23837,7 @@
         <v>3004</v>
       </c>
     </row>
-    <row r="286" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="286" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L286">
         <f t="shared" si="8"/>
         <v>2117</v>
@@ -23862,7 +23847,7 @@
         <v>3012</v>
       </c>
     </row>
-    <row r="287" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="287" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L287">
         <f t="shared" si="8"/>
         <v>2118</v>
@@ -23872,7 +23857,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="288" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="288" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L288">
         <f t="shared" si="8"/>
         <v>2119</v>
@@ -23882,7 +23867,7 @@
         <v>3027</v>
       </c>
     </row>
-    <row r="289" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="289" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L289">
         <f t="shared" si="8"/>
         <v>2120</v>
@@ -23892,7 +23877,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="290" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="290" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L290">
         <f t="shared" si="8"/>
         <v>2121</v>
@@ -23902,7 +23887,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="291" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="291" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L291">
         <f t="shared" si="8"/>
         <v>2122</v>
@@ -23912,7 +23897,7 @@
         <v>3049</v>
       </c>
     </row>
-    <row r="292" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="292" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L292">
         <f t="shared" si="8"/>
         <v>2123</v>
@@ -23922,7 +23907,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="293" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="293" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L293">
         <f t="shared" si="8"/>
         <v>2124</v>
@@ -23932,7 +23917,7 @@
         <v>3064</v>
       </c>
     </row>
-    <row r="294" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="294" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L294">
         <f t="shared" si="8"/>
         <v>2125</v>
@@ -23942,7 +23927,7 @@
         <v>3071</v>
       </c>
     </row>
-    <row r="295" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="295" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L295">
         <f t="shared" si="8"/>
         <v>2126</v>
@@ -23952,7 +23937,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="296" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="296" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L296">
         <f t="shared" si="8"/>
         <v>2127</v>
@@ -23962,7 +23947,7 @@
         <v>3086</v>
       </c>
     </row>
-    <row r="297" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="297" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L297">
         <f t="shared" si="8"/>
         <v>2128</v>
@@ -23972,7 +23957,7 @@
         <v>3093</v>
       </c>
     </row>
-    <row r="298" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="298" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L298">
         <f t="shared" si="8"/>
         <v>2129</v>
@@ -23982,7 +23967,7 @@
         <v>3101</v>
       </c>
     </row>
-    <row r="299" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="299" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L299">
         <f t="shared" si="8"/>
         <v>2130</v>
@@ -23992,7 +23977,7 @@
         <v>3108</v>
       </c>
     </row>
-    <row r="300" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="300" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L300">
         <f t="shared" si="8"/>
         <v>2131</v>
@@ -24002,7 +23987,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="301" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="301" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L301">
         <f t="shared" si="8"/>
         <v>2132</v>
@@ -24012,7 +23997,7 @@
         <v>3123</v>
       </c>
     </row>
-    <row r="302" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="302" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L302">
         <f t="shared" si="8"/>
         <v>2133</v>
@@ -24022,7 +24007,7 @@
         <v>3131</v>
       </c>
     </row>
-    <row r="303" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="303" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L303">
         <f t="shared" si="8"/>
         <v>2134</v>
@@ -24032,7 +24017,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="304" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="304" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L304">
         <f t="shared" si="8"/>
         <v>2135</v>
@@ -24042,7 +24027,7 @@
         <v>3145</v>
       </c>
     </row>
-    <row r="305" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="305" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L305">
         <f t="shared" si="8"/>
         <v>2136</v>
@@ -24052,7 +24037,7 @@
         <v>3153</v>
       </c>
     </row>
-    <row r="306" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="306" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L306">
         <f t="shared" si="8"/>
         <v>2137</v>
@@ -24062,7 +24047,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="307" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="307" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L307">
         <f t="shared" si="8"/>
         <v>2138</v>
@@ -24072,7 +24057,7 @@
         <v>3168</v>
       </c>
     </row>
-    <row r="308" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="308" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L308">
         <f t="shared" si="8"/>
         <v>2139</v>
@@ -24082,7 +24067,7 @@
         <v>3175</v>
       </c>
     </row>
-    <row r="309" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="309" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L309">
         <f t="shared" si="8"/>
         <v>2140</v>
@@ -24092,7 +24077,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="310" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="310" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L310">
         <f t="shared" si="8"/>
         <v>2141</v>
@@ -24102,7 +24087,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="311" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="311" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L311">
         <f t="shared" si="8"/>
         <v>2142</v>
@@ -24112,7 +24097,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="312" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="312" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L312">
         <f t="shared" si="8"/>
         <v>2143</v>
@@ -24122,7 +24107,7 @@
         <v>3205</v>
       </c>
     </row>
-    <row r="313" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="313" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L313">
         <f t="shared" si="8"/>
         <v>2144</v>
@@ -24132,7 +24117,7 @@
         <v>3212</v>
       </c>
     </row>
-    <row r="314" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="314" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L314">
         <f t="shared" si="8"/>
         <v>2145</v>
@@ -24142,7 +24127,7 @@
         <v>3220</v>
       </c>
     </row>
-    <row r="315" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="315" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L315">
         <f t="shared" si="8"/>
         <v>2146</v>
@@ -24152,7 +24137,7 @@
         <v>3227</v>
       </c>
     </row>
-    <row r="316" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="316" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L316">
         <f t="shared" si="8"/>
         <v>2147</v>
@@ -24162,7 +24147,7 @@
         <v>3234</v>
       </c>
     </row>
-    <row r="317" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="317" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L317">
         <f t="shared" si="8"/>
         <v>2148</v>
@@ -24172,7 +24157,7 @@
         <v>3242</v>
       </c>
     </row>
-    <row r="318" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="318" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L318">
         <f t="shared" si="8"/>
         <v>2149</v>
@@ -24182,7 +24167,7 @@
         <v>3249</v>
       </c>
     </row>
-    <row r="319" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="319" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L319">
         <f t="shared" si="8"/>
         <v>2150</v>
@@ -24192,7 +24177,7 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="320" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="320" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L320">
         <f t="shared" si="8"/>
         <v>2151</v>
@@ -24202,7 +24187,7 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="321" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="321" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L321">
         <f t="shared" si="8"/>
         <v>2152</v>
@@ -24212,7 +24197,7 @@
         <v>3272</v>
       </c>
     </row>
-    <row r="322" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="322" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L322">
         <f t="shared" si="8"/>
         <v>2153</v>
@@ -24222,7 +24207,7 @@
         <v>3279</v>
       </c>
     </row>
-    <row r="323" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="323" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L323">
         <f t="shared" si="8"/>
         <v>2154</v>
@@ -24232,7 +24217,7 @@
         <v>3286</v>
       </c>
     </row>
-    <row r="324" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="324" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L324">
         <f t="shared" ref="L324:L336" si="10">L323+1</f>
         <v>2155</v>
@@ -24242,7 +24227,7 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="325" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="325" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L325">
         <f t="shared" si="10"/>
         <v>2156</v>
@@ -24252,7 +24237,7 @@
         <v>3301</v>
       </c>
     </row>
-    <row r="326" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="326" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L326">
         <f t="shared" si="10"/>
         <v>2157</v>
@@ -24262,7 +24247,7 @@
         <v>3309</v>
       </c>
     </row>
-    <row r="327" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="327" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L327">
         <f t="shared" si="10"/>
         <v>2158</v>
@@ -24272,7 +24257,7 @@
         <v>3316</v>
       </c>
     </row>
-    <row r="328" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="328" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L328">
         <f t="shared" si="10"/>
         <v>2159</v>
@@ -24282,7 +24267,7 @@
         <v>3323</v>
       </c>
     </row>
-    <row r="329" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="329" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L329">
         <f t="shared" si="10"/>
         <v>2160</v>
@@ -24292,7 +24277,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="330" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="330" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L330">
         <f t="shared" si="10"/>
         <v>2161</v>
@@ -24302,7 +24287,7 @@
         <v>3338</v>
       </c>
     </row>
-    <row r="331" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="331" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L331">
         <f t="shared" si="10"/>
         <v>2162</v>
@@ -24312,7 +24297,7 @@
         <v>3346</v>
       </c>
     </row>
-    <row r="332" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="332" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L332">
         <f t="shared" si="10"/>
         <v>2163</v>
@@ -24322,7 +24307,7 @@
         <v>3353</v>
       </c>
     </row>
-    <row r="333" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="333" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L333">
         <f t="shared" si="10"/>
         <v>2164</v>
@@ -24332,7 +24317,7 @@
         <v>3361</v>
       </c>
     </row>
-    <row r="334" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="334" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L334">
         <f t="shared" si="10"/>
         <v>2165</v>
@@ -24342,7 +24327,7 @@
         <v>3368</v>
       </c>
     </row>
-    <row r="335" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="335" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L335">
         <f t="shared" si="10"/>
         <v>2166</v>
@@ -24352,7 +24337,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="336" spans="12:13" x14ac:dyDescent="0.35">
+    <row r="336" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L336">
         <f t="shared" si="10"/>
         <v>2167</v>
@@ -24371,12 +24356,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B976ED82-D377-452B-98DC-3515CED81A81}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>325</v>
       </c>
@@ -24384,7 +24369,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -24395,7 +24380,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -24409,7 +24394,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -24423,7 +24408,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -24437,7 +24422,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>86</v>
       </c>
@@ -24451,7 +24436,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>168</v>
       </c>
@@ -24465,7 +24450,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -24479,7 +24464,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>85</v>
       </c>
@@ -24504,14 +24489,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A66C56-C25D-4E4C-815E-A8416CC0CC5B}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>64</v>
       </c>
@@ -24519,7 +24504,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>56</v>
       </c>
@@ -24527,7 +24512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>180</v>
       </c>
@@ -24535,7 +24520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>181</v>
       </c>
@@ -24543,7 +24528,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>188</v>
       </c>
@@ -24551,12 +24536,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>183</v>
       </c>
@@ -24564,7 +24549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>184</v>
       </c>
@@ -24572,7 +24557,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>185</v>
       </c>
@@ -24580,7 +24565,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>186</v>
       </c>
@@ -24588,7 +24573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>187</v>
       </c>
@@ -24596,7 +24581,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>189</v>
       </c>
@@ -24612,12 +24597,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F1D77F-0E43-499A-A11C-88B275139916}">
   <dimension ref="A1:J61"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="10" width="14.453125" customWidth="1"/>
+    <col min="3" max="10" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>90</v>
       </c>
@@ -24649,7 +24634,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -24675,7 +24660,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -24701,7 +24686,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>7</v>
       </c>
@@ -24721,7 +24706,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>8</v>
       </c>
@@ -24753,7 +24738,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>9</v>
       </c>
@@ -24785,7 +24770,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>10</v>
       </c>
@@ -24811,7 +24796,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>11</v>
       </c>
@@ -24840,7 +24825,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>14</v>
       </c>
@@ -24869,7 +24854,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>19</v>
       </c>
@@ -24892,7 +24877,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>20</v>
       </c>
@@ -24924,7 +24909,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>21</v>
       </c>
@@ -24956,7 +24941,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>22</v>
       </c>
@@ -24985,7 +24970,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>34</v>
       </c>
@@ -25011,7 +24996,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>35</v>
       </c>
@@ -25037,7 +25022,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>36</v>
       </c>
@@ -25060,7 +25045,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>37</v>
       </c>
@@ -25089,7 +25074,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>38</v>
       </c>
@@ -25118,7 +25103,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>39</v>
       </c>
@@ -25144,7 +25129,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>40</v>
       </c>
@@ -25170,7 +25155,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>41</v>
       </c>
@@ -25181,7 +25166,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>42</v>
       </c>
@@ -25192,7 +25177,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>46</v>
       </c>
@@ -25215,7 +25200,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>47</v>
       </c>
@@ -25244,7 +25229,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>53</v>
       </c>
@@ -25273,7 +25258,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>54</v>
       </c>
@@ -25302,7 +25287,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>55</v>
       </c>
@@ -25325,7 +25310,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>59</v>
       </c>
@@ -25351,7 +25336,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>60</v>
       </c>
@@ -25377,7 +25362,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -25403,7 +25388,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>4</v>
       </c>
@@ -25423,7 +25408,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>5</v>
       </c>
@@ -25443,7 +25428,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>6</v>
       </c>
@@ -25472,7 +25457,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>12</v>
       </c>
@@ -25492,7 +25477,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>13</v>
       </c>
@@ -25512,7 +25497,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>15</v>
       </c>
@@ -25541,7 +25526,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>16</v>
       </c>
@@ -25570,7 +25555,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>17</v>
       </c>
@@ -25593,7 +25578,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>18</v>
       </c>
@@ -25616,7 +25601,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>23</v>
       </c>
@@ -25645,7 +25630,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>24</v>
       </c>
@@ -25674,7 +25659,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>25</v>
       </c>
@@ -25694,7 +25679,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>26</v>
       </c>
@@ -25714,7 +25699,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>27</v>
       </c>
@@ -25734,7 +25719,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>28</v>
       </c>
@@ -25754,7 +25739,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>29</v>
       </c>
@@ -25774,7 +25759,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>30</v>
       </c>
@@ -25794,7 +25779,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>31</v>
       </c>
@@ -25820,7 +25805,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>32</v>
       </c>
@@ -25843,7 +25828,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>33</v>
       </c>
@@ -25866,7 +25851,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>43</v>
       </c>
@@ -25889,7 +25874,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>44</v>
       </c>
@@ -25912,7 +25897,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>45</v>
       </c>
@@ -25935,7 +25920,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>48</v>
       </c>
@@ -25964,7 +25949,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>49</v>
       </c>
@@ -25978,7 +25963,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>50</v>
       </c>
@@ -25992,7 +25977,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>51</v>
       </c>
@@ -26009,7 +25994,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>52</v>
       </c>
@@ -26035,7 +26020,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>56</v>
       </c>
@@ -26052,7 +26037,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>57</v>
       </c>
@@ -26075,7 +26060,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>58</v>
       </c>

--- a/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
+++ b/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eganw\ece445l_lab7-10_fall26-4-ew-js-tp-ak\sw\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghakk\ece445l_lab7-10_fall26-4-ew-js-tp-ak\sw\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D69A5EC-FFC8-44F9-8CFA-AC84E841CCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5557FAB4-C80B-4455-A2E2-56555B9F6CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VSSOP-32" sheetId="1" r:id="rId1"/>
@@ -21,25 +21,12 @@
     <sheet name="ADC" sheetId="12" r:id="rId6"/>
     <sheet name="PINCM" sheetId="11" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="418">
   <si>
     <t>PA25</t>
   </si>
@@ -1247,9 +1234,6 @@
     <t>Smoke Enable</t>
   </si>
   <si>
-    <t>(4 if including PA0/1)</t>
-  </si>
-  <si>
     <t>Key:</t>
   </si>
   <si>
@@ -1317,6 +1301,9 @@
   </si>
   <si>
     <t>LED Group 2</t>
+  </si>
+  <si>
+    <t>Motor PWM</t>
   </si>
 </sst>
 </file>
@@ -6173,19 +6160,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:XEU44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.5546875" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.08984375" style="2" customWidth="1"/>
     <col min="5" max="5" width="6" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30.36328125" customWidth="1"/>
+    <col min="8" max="8" width="5.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -6197,7 +6184,7 @@
       </c>
       <c r="G1" s="7"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>364</v>
       </c>
@@ -6219,7 +6206,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>210</v>
       </c>
@@ -6240,7 +6227,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>171</v>
@@ -6259,7 +6246,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>363</v>
       </c>
@@ -6280,7 +6267,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>363</v>
       </c>
@@ -6301,7 +6288,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>172</v>
@@ -6320,7 +6307,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>173</v>
@@ -6339,7 +6326,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>174</v>
@@ -6358,7 +6345,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>363</v>
       </c>
@@ -6379,7 +6366,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>363</v>
       </c>
@@ -6400,7 +6387,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>364</v>
       </c>
@@ -6421,7 +6408,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>176</v>
       </c>
@@ -6442,7 +6429,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>175</v>
       </c>
@@ -6463,7 +6450,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>364</v>
       </c>
@@ -6487,7 +6474,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>134</v>
       </c>
@@ -6511,7 +6498,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>137</v>
       </c>
@@ -6535,13 +6522,13 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>324</v>
       </c>
@@ -6553,12 +6540,12 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>331</v>
       </c>
@@ -6566,7 +6553,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>332</v>
       </c>
@@ -6574,27 +6561,27 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -6602,19 +6589,19 @@
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -12759,48 +12746,48 @@
       <c r="XET31" s="2"/>
       <c r="XEU31" s="2"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B33"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B34"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B35"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B36"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B37"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B38"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="14"/>
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="15"/>
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
@@ -12815,20 +12802,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC81E62-902F-426A-8169-496CDAF34664}">
   <dimension ref="A1:XEU49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.5546875" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.08984375" style="2" customWidth="1"/>
     <col min="5" max="5" width="6" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="10.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30.36328125" customWidth="1"/>
+    <col min="8" max="8" width="5.90625" customWidth="1"/>
+    <col min="9" max="9" width="10.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>369</v>
       </c>
@@ -12840,10 +12827,10 @@
       </c>
       <c r="G1" s="7"/>
       <c r="I1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="40" t="s">
         <v>389</v>
       </c>
@@ -12865,10 +12852,10 @@
         <v>394</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="43" t="s">
         <v>210</v>
       </c>
@@ -12889,10 +12876,10 @@
         <v>213</v>
       </c>
       <c r="I3" s="42" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="68"/>
       <c r="B4" s="2" t="s">
         <v>171</v>
@@ -12911,10 +12898,10 @@
         <v>387</v>
       </c>
       <c r="I4" s="47" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="40" t="s">
         <v>382</v>
       </c>
@@ -12935,10 +12922,10 @@
         <v>376</v>
       </c>
       <c r="I5" s="51" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="40" t="s">
         <v>383</v>
       </c>
@@ -12959,10 +12946,10 @@
         <v>377</v>
       </c>
       <c r="I6" s="52" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="58" t="s">
         <v>391</v>
       </c>
@@ -12983,10 +12970,10 @@
         <v>158</v>
       </c>
       <c r="I7" s="53" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="67" t="s">
         <v>392</v>
       </c>
@@ -13007,10 +12994,10 @@
         <v>156</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="68" t="s">
         <v>393</v>
       </c>
@@ -13031,10 +13018,10 @@
         <v>209</v>
       </c>
       <c r="I9" s="60" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="46" t="s">
         <v>372</v>
       </c>
@@ -13055,10 +13042,10 @@
         <v>208</v>
       </c>
       <c r="I10" s="62" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="40" t="s">
         <v>384</v>
       </c>
@@ -13079,10 +13066,10 @@
         <v>395</v>
       </c>
       <c r="I11" s="64" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="40" t="s">
         <v>385</v>
       </c>
@@ -13103,10 +13090,10 @@
         <v>362</v>
       </c>
       <c r="I12" s="57" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="63" t="s">
         <v>176</v>
       </c>
@@ -13127,10 +13114,10 @@
         <v>373</v>
       </c>
       <c r="I13" s="66" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="63" t="s">
         <v>175</v>
       </c>
@@ -13151,10 +13138,10 @@
         <v>212</v>
       </c>
       <c r="I14" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="40" t="s">
         <v>386</v>
       </c>
@@ -13178,7 +13165,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="56" t="s">
         <v>378</v>
       </c>
@@ -13202,7 +13189,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A17" s="56" t="s">
         <v>379</v>
       </c>
@@ -13226,7 +13213,7 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>396</v>
       </c>
@@ -13234,7 +13221,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>370</v>
       </c>
@@ -13249,7 +13236,7 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A20" s="49" t="s">
         <v>365</v>
       </c>
@@ -13274,7 +13261,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A21" s="43" t="s">
         <v>210</v>
       </c>
@@ -13298,7 +13285,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A22" s="68"/>
       <c r="B22" s="2" t="s">
         <v>171</v>
@@ -13320,9 +13307,9 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
-      <c r="A23" s="58" t="s">
-        <v>391</v>
+    <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
+      <c r="A23" s="49" t="s">
+        <v>417</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>37</v>
@@ -13344,7 +13331,7 @@
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A24" s="65" t="s">
         <v>397</v>
       </c>
@@ -13362,13 +13349,13 @@
         <v>40</v>
       </c>
       <c r="G24" s="64" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A25" s="58" t="s">
         <v>391</v>
       </c>
@@ -13392,7 +13379,7 @@
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A26" s="67" t="s">
         <v>392</v>
       </c>
@@ -13416,7 +13403,7 @@
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A27" s="68" t="s">
         <v>393</v>
       </c>
@@ -13440,7 +13427,7 @@
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A28" s="46" t="s">
         <v>372</v>
       </c>
@@ -13464,9 +13451,9 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A29" s="58" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>10</v>
@@ -13486,7 +13473,7 @@
       </c>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A30" s="46" t="s">
         <v>380</v>
       </c>
@@ -13509,7 +13496,7 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A31" s="63" t="s">
         <v>176</v>
       </c>
@@ -13527,7 +13514,7 @@
         <v>39</v>
       </c>
       <c r="G31" s="64" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -19668,7 +19655,7 @@
       <c r="XET31" s="2"/>
       <c r="XEU31" s="2"/>
     </row>
-    <row r="32" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A32" s="63" t="s">
         <v>175</v>
       </c>
@@ -19689,9 +19676,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="58" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>14</v>
@@ -19710,7 +19697,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="49" t="s">
         <v>367</v>
       </c>
@@ -19731,7 +19718,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="46" t="s">
         <v>381</v>
       </c>
@@ -19752,52 +19739,50 @@
         <v>368</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B36"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>398</v>
-      </c>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="1"/>
       <c r="B37"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B38"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="14"/>
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="15"/>
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -19810,22 +19795,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E972CE-2F8B-4DAB-AD48-DA87002CAF65}">
   <dimension ref="A1:O44"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" style="31" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="30" customWidth="1"/>
-    <col min="3" max="3" width="27.109375" style="30" customWidth="1"/>
+    <col min="1" max="1" width="12.90625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" style="30" customWidth="1"/>
+    <col min="3" max="3" width="27.08984375" style="30" customWidth="1"/>
     <col min="4" max="4" width="14" style="30" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" style="30" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" style="30" customWidth="1"/>
     <col min="6" max="6" width="24" style="30" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" style="30" customWidth="1"/>
-    <col min="8" max="8" width="29.6640625" style="30" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" style="30" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" style="36"/>
-    <col min="11" max="16384" width="9.109375" style="30"/>
+    <col min="7" max="7" width="12.6328125" style="30" customWidth="1"/>
+    <col min="8" max="8" width="29.6328125" style="30" customWidth="1"/>
+    <col min="9" max="9" width="14.36328125" style="30" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="36"/>
+    <col min="11" max="16384" width="9.08984375" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="I1" s="30" t="s">
         <v>350</v>
       </c>
@@ -19833,7 +19818,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="I2" s="30">
         <f>SUM(I4:I51)</f>
         <v>36.134999999999998</v>
@@ -19843,7 +19828,7 @@
         <v>83.68</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="31" t="s">
         <v>190</v>
       </c>
@@ -19878,7 +19863,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="31">
         <v>2</v>
       </c>
@@ -19905,7 +19890,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="31">
         <v>2</v>
       </c>
@@ -19938,7 +19923,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="31">
         <v>1</v>
       </c>
@@ -19965,7 +19950,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="31">
         <v>2</v>
       </c>
@@ -19992,7 +19977,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="31">
         <v>1</v>
       </c>
@@ -20025,7 +20010,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="31">
         <v>1</v>
       </c>
@@ -20052,7 +20037,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="31">
         <v>2</v>
       </c>
@@ -20082,7 +20067,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="31">
         <v>0</v>
       </c>
@@ -20112,7 +20097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="31">
         <v>1</v>
       </c>
@@ -20145,7 +20130,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="31">
         <v>1</v>
       </c>
@@ -20190,7 +20175,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="31">
         <v>0</v>
       </c>
@@ -20220,7 +20205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="31">
         <v>1</v>
       </c>
@@ -20256,7 +20241,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="31">
         <v>1</v>
       </c>
@@ -20292,7 +20277,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="31">
         <v>1</v>
       </c>
@@ -20328,7 +20313,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="31">
         <v>1</v>
       </c>
@@ -20360,7 +20345,7 @@
         <v>29.81</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="31">
         <v>1</v>
       </c>
@@ -20395,7 +20380,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="31">
         <v>2</v>
       </c>
@@ -20431,7 +20416,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="31">
         <v>1</v>
       </c>
@@ -20454,7 +20439,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="31">
         <v>1</v>
       </c>
@@ -20490,7 +20475,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="31">
         <v>2</v>
       </c>
@@ -20523,7 +20508,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="31">
         <v>1</v>
       </c>
@@ -20556,7 +20541,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="31">
         <v>2</v>
       </c>
@@ -20589,7 +20574,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="31">
         <v>1</v>
       </c>
@@ -20622,7 +20607,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="31">
         <v>0</v>
       </c>
@@ -20655,10 +20640,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B34" s="32"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="31">
         <v>5</v>
       </c>
@@ -20688,7 +20673,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="31">
         <v>1</v>
       </c>
@@ -20702,7 +20687,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="31">
         <v>1</v>
       </c>
@@ -20713,7 +20698,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="31">
         <v>1</v>
       </c>
@@ -20724,7 +20709,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="31">
         <v>1</v>
       </c>
@@ -20735,7 +20720,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="31">
         <v>1</v>
       </c>
@@ -20765,7 +20750,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="31">
         <v>1</v>
       </c>
@@ -20795,7 +20780,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="31">
         <v>1</v>
       </c>
@@ -20833,14 +20818,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E84313-7CEE-4179-AFC3-CFF55EB9327F}">
   <dimension ref="A1:M336"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" customWidth="1"/>
-    <col min="7" max="7" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.90625" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" customWidth="1"/>
+    <col min="7" max="7" width="17.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>69</v>
       </c>
@@ -20864,7 +20849,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -20886,7 +20871,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -20902,7 +20887,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -20936,7 +20921,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>10</v>
       </c>
@@ -20976,7 +20961,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>25</v>
       </c>
@@ -21017,7 +21002,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>35</v>
       </c>
@@ -21057,7 +21042,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L8">
         <f t="shared" si="0"/>
         <v>1839</v>
@@ -21067,7 +21052,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L9">
         <f t="shared" si="0"/>
         <v>1840</v>
@@ -21077,7 +21062,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L10">
         <f t="shared" si="0"/>
         <v>1841</v>
@@ -21087,7 +21072,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L11">
         <f t="shared" si="0"/>
         <v>1842</v>
@@ -21097,7 +21082,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L12">
         <f t="shared" si="0"/>
         <v>1843</v>
@@ -21107,7 +21092,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L13">
         <f t="shared" si="0"/>
         <v>1844</v>
@@ -21117,7 +21102,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L14">
         <f t="shared" si="0"/>
         <v>1845</v>
@@ -21127,7 +21112,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L15">
         <f t="shared" si="0"/>
         <v>1846</v>
@@ -21137,7 +21122,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="L16">
         <f t="shared" si="0"/>
         <v>1847</v>
@@ -21147,7 +21132,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="17" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L17">
         <f t="shared" si="0"/>
         <v>1848</v>
@@ -21157,7 +21142,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="18" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L18">
         <f t="shared" si="0"/>
         <v>1849</v>
@@ -21167,7 +21152,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="19" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L19">
         <f t="shared" si="0"/>
         <v>1850</v>
@@ -21177,7 +21162,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="20" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L20">
         <f t="shared" si="0"/>
         <v>1851</v>
@@ -21187,7 +21172,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="21" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L21">
         <f t="shared" si="0"/>
         <v>1852</v>
@@ -21197,7 +21182,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="22" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L22">
         <f t="shared" si="0"/>
         <v>1853</v>
@@ -21207,7 +21192,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="23" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L23">
         <f t="shared" si="0"/>
         <v>1854</v>
@@ -21217,7 +21202,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="24" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L24">
         <f t="shared" si="0"/>
         <v>1855</v>
@@ -21227,7 +21212,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="25" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L25">
         <f t="shared" si="0"/>
         <v>1856</v>
@@ -21237,7 +21222,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="26" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L26">
         <f t="shared" si="0"/>
         <v>1857</v>
@@ -21247,7 +21232,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="27" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L27">
         <f t="shared" si="0"/>
         <v>1858</v>
@@ -21257,7 +21242,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="28" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L28">
         <f t="shared" si="0"/>
         <v>1859</v>
@@ -21267,7 +21252,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="29" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L29">
         <f t="shared" si="0"/>
         <v>1860</v>
@@ -21277,7 +21262,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="30" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L30">
         <f t="shared" si="0"/>
         <v>1861</v>
@@ -21287,7 +21272,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="31" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L31">
         <f t="shared" si="0"/>
         <v>1862</v>
@@ -21297,7 +21282,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="32" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L32">
         <f t="shared" si="0"/>
         <v>1863</v>
@@ -21307,7 +21292,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="33" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L33">
         <f t="shared" si="0"/>
         <v>1864</v>
@@ -21317,7 +21302,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="34" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L34">
         <f t="shared" si="0"/>
         <v>1865</v>
@@ -21327,7 +21312,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="35" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L35">
         <f t="shared" si="0"/>
         <v>1866</v>
@@ -21337,7 +21322,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="36" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L36">
         <f t="shared" si="0"/>
         <v>1867</v>
@@ -21347,7 +21332,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="37" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L37">
         <f t="shared" si="0"/>
         <v>1868</v>
@@ -21357,7 +21342,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="38" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L38">
         <f t="shared" si="0"/>
         <v>1869</v>
@@ -21367,7 +21352,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="39" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L39">
         <f t="shared" si="0"/>
         <v>1870</v>
@@ -21377,7 +21362,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="40" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L40">
         <f t="shared" si="0"/>
         <v>1871</v>
@@ -21387,7 +21372,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="41" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L41">
         <f t="shared" si="0"/>
         <v>1872</v>
@@ -21397,7 +21382,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="42" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L42">
         <f t="shared" si="0"/>
         <v>1873</v>
@@ -21407,7 +21392,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="43" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L43">
         <f t="shared" si="0"/>
         <v>1874</v>
@@ -21417,7 +21402,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="44" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L44">
         <f t="shared" si="0"/>
         <v>1875</v>
@@ -21427,7 +21412,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="45" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L45">
         <f t="shared" si="0"/>
         <v>1876</v>
@@ -21437,7 +21422,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="46" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L46">
         <f t="shared" si="0"/>
         <v>1877</v>
@@ -21447,7 +21432,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="47" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L47">
         <f t="shared" si="0"/>
         <v>1878</v>
@@ -21457,7 +21442,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="48" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L48">
         <f t="shared" si="0"/>
         <v>1879</v>
@@ -21467,7 +21452,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="49" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L49">
         <f t="shared" si="0"/>
         <v>1880</v>
@@ -21477,7 +21462,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="50" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L50">
         <f t="shared" si="0"/>
         <v>1881</v>
@@ -21487,7 +21472,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="51" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L51">
         <f t="shared" si="0"/>
         <v>1882</v>
@@ -21497,7 +21482,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="52" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L52">
         <f t="shared" si="0"/>
         <v>1883</v>
@@ -21507,7 +21492,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="53" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L53">
         <f t="shared" si="0"/>
         <v>1884</v>
@@ -21517,7 +21502,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="54" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L54">
         <f t="shared" si="0"/>
         <v>1885</v>
@@ -21527,7 +21512,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="55" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L55">
         <f t="shared" si="0"/>
         <v>1886</v>
@@ -21537,7 +21522,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="56" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L56">
         <f t="shared" si="0"/>
         <v>1887</v>
@@ -21547,7 +21532,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="57" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L57">
         <f t="shared" si="0"/>
         <v>1888</v>
@@ -21557,7 +21542,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="58" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L58">
         <f t="shared" si="0"/>
         <v>1889</v>
@@ -21567,7 +21552,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="59" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L59">
         <f t="shared" si="0"/>
         <v>1890</v>
@@ -21577,7 +21562,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="60" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L60">
         <f t="shared" si="0"/>
         <v>1891</v>
@@ -21587,7 +21572,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="61" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L61">
         <f t="shared" si="0"/>
         <v>1892</v>
@@ -21597,7 +21582,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="62" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L62">
         <f t="shared" si="0"/>
         <v>1893</v>
@@ -21607,7 +21592,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="63" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L63">
         <f t="shared" si="0"/>
         <v>1894</v>
@@ -21617,7 +21602,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="64" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L64">
         <f t="shared" si="0"/>
         <v>1895</v>
@@ -21627,7 +21612,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="65" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L65">
         <f t="shared" si="0"/>
         <v>1896</v>
@@ -21637,7 +21622,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="66" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L66">
         <f t="shared" si="0"/>
         <v>1897</v>
@@ -21647,7 +21632,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="67" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L67">
         <f t="shared" si="0"/>
         <v>1898</v>
@@ -21657,7 +21642,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="68" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L68">
         <f t="shared" ref="L68:L131" si="2">L67+1</f>
         <v>1899</v>
@@ -21667,7 +21652,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="69" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L69">
         <f t="shared" si="2"/>
         <v>1900</v>
@@ -21677,7 +21662,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="70" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L70">
         <f t="shared" si="2"/>
         <v>1901</v>
@@ -21687,7 +21672,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="71" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L71">
         <f t="shared" si="2"/>
         <v>1902</v>
@@ -21697,7 +21682,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="72" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L72">
         <f t="shared" si="2"/>
         <v>1903</v>
@@ -21707,7 +21692,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="73" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L73">
         <f t="shared" si="2"/>
         <v>1904</v>
@@ -21717,7 +21702,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="74" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L74">
         <f t="shared" si="2"/>
         <v>1905</v>
@@ -21727,7 +21712,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="75" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L75">
         <f t="shared" si="2"/>
         <v>1906</v>
@@ -21737,7 +21722,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="76" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L76">
         <f t="shared" si="2"/>
         <v>1907</v>
@@ -21747,7 +21732,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="77" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L77">
         <f t="shared" si="2"/>
         <v>1908</v>
@@ -21757,7 +21742,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="78" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L78">
         <f t="shared" si="2"/>
         <v>1909</v>
@@ -21767,7 +21752,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="79" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L79">
         <f t="shared" si="2"/>
         <v>1910</v>
@@ -21777,7 +21762,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="80" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L80">
         <f t="shared" si="2"/>
         <v>1911</v>
@@ -21787,7 +21772,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="81" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L81">
         <f t="shared" si="2"/>
         <v>1912</v>
@@ -21797,7 +21782,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="82" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L82">
         <f t="shared" si="2"/>
         <v>1913</v>
@@ -21807,7 +21792,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="83" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L83">
         <f t="shared" si="2"/>
         <v>1914</v>
@@ -21817,7 +21802,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="84" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L84">
         <f t="shared" si="2"/>
         <v>1915</v>
@@ -21827,7 +21812,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="85" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L85">
         <f t="shared" si="2"/>
         <v>1916</v>
@@ -21837,7 +21822,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="86" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L86">
         <f t="shared" si="2"/>
         <v>1917</v>
@@ -21847,7 +21832,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="87" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L87">
         <f t="shared" si="2"/>
         <v>1918</v>
@@ -21857,7 +21842,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="88" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L88">
         <f t="shared" si="2"/>
         <v>1919</v>
@@ -21867,7 +21852,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="89" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L89">
         <f t="shared" si="2"/>
         <v>1920</v>
@@ -21877,7 +21862,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="90" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L90">
         <f t="shared" si="2"/>
         <v>1921</v>
@@ -21887,7 +21872,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="91" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L91">
         <f t="shared" si="2"/>
         <v>1922</v>
@@ -21897,7 +21882,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="92" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L92">
         <f t="shared" si="2"/>
         <v>1923</v>
@@ -21907,7 +21892,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="93" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L93">
         <f t="shared" si="2"/>
         <v>1924</v>
@@ -21917,7 +21902,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="94" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L94">
         <f t="shared" si="2"/>
         <v>1925</v>
@@ -21927,7 +21912,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="95" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L95">
         <f t="shared" si="2"/>
         <v>1926</v>
@@ -21937,7 +21922,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="96" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L96">
         <f t="shared" si="2"/>
         <v>1927</v>
@@ -21947,7 +21932,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="97" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L97">
         <f t="shared" si="2"/>
         <v>1928</v>
@@ -21957,7 +21942,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="98" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L98">
         <f t="shared" si="2"/>
         <v>1929</v>
@@ -21967,7 +21952,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="99" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L99">
         <f t="shared" si="2"/>
         <v>1930</v>
@@ -21977,7 +21962,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="100" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L100">
         <f t="shared" si="2"/>
         <v>1931</v>
@@ -21987,7 +21972,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="101" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L101">
         <f t="shared" si="2"/>
         <v>1932</v>
@@ -21997,7 +21982,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="102" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L102">
         <f t="shared" si="2"/>
         <v>1933</v>
@@ -22007,7 +21992,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="103" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L103">
         <f t="shared" si="2"/>
         <v>1934</v>
@@ -22017,7 +22002,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="104" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L104">
         <f t="shared" si="2"/>
         <v>1935</v>
@@ -22027,7 +22012,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="105" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L105">
         <f t="shared" si="2"/>
         <v>1936</v>
@@ -22037,7 +22022,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="106" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L106">
         <f t="shared" si="2"/>
         <v>1937</v>
@@ -22047,7 +22032,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="107" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L107">
         <f t="shared" si="2"/>
         <v>1938</v>
@@ -22057,7 +22042,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="108" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L108">
         <f t="shared" si="2"/>
         <v>1939</v>
@@ -22067,7 +22052,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="109" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L109">
         <f t="shared" si="2"/>
         <v>1940</v>
@@ -22077,7 +22062,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="110" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L110">
         <f t="shared" si="2"/>
         <v>1941</v>
@@ -22087,7 +22072,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="111" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L111">
         <f t="shared" si="2"/>
         <v>1942</v>
@@ -22097,7 +22082,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="112" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L112">
         <f t="shared" si="2"/>
         <v>1943</v>
@@ -22107,7 +22092,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="113" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L113">
         <f t="shared" si="2"/>
         <v>1944</v>
@@ -22117,7 +22102,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="114" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L114">
         <f t="shared" si="2"/>
         <v>1945</v>
@@ -22127,7 +22112,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="115" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L115">
         <f t="shared" si="2"/>
         <v>1946</v>
@@ -22137,7 +22122,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="116" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L116">
         <f t="shared" si="2"/>
         <v>1947</v>
@@ -22147,7 +22132,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="117" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L117">
         <f t="shared" si="2"/>
         <v>1948</v>
@@ -22157,7 +22142,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="118" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L118">
         <f t="shared" si="2"/>
         <v>1949</v>
@@ -22167,7 +22152,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="119" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L119">
         <f t="shared" si="2"/>
         <v>1950</v>
@@ -22177,7 +22162,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="120" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L120">
         <f t="shared" si="2"/>
         <v>1951</v>
@@ -22187,7 +22172,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="121" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L121">
         <f t="shared" si="2"/>
         <v>1952</v>
@@ -22197,7 +22182,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="122" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L122">
         <f t="shared" si="2"/>
         <v>1953</v>
@@ -22207,7 +22192,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="123" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L123">
         <f t="shared" si="2"/>
         <v>1954</v>
@@ -22217,7 +22202,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="124" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L124">
         <f t="shared" si="2"/>
         <v>1955</v>
@@ -22227,7 +22212,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="125" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L125">
         <f t="shared" si="2"/>
         <v>1956</v>
@@ -22237,7 +22222,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="126" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L126">
         <f t="shared" si="2"/>
         <v>1957</v>
@@ -22247,7 +22232,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="127" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L127">
         <f t="shared" si="2"/>
         <v>1958</v>
@@ -22257,7 +22242,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="128" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L128">
         <f t="shared" si="2"/>
         <v>1959</v>
@@ -22267,7 +22252,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="129" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L129">
         <f t="shared" si="2"/>
         <v>1960</v>
@@ -22277,7 +22262,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="130" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L130">
         <f t="shared" si="2"/>
         <v>1961</v>
@@ -22287,7 +22272,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="131" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L131">
         <f t="shared" si="2"/>
         <v>1962</v>
@@ -22297,7 +22282,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="132" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L132">
         <f t="shared" ref="L132:L195" si="4">L131+1</f>
         <v>1963</v>
@@ -22307,7 +22292,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="133" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L133">
         <f t="shared" si="4"/>
         <v>1964</v>
@@ -22317,7 +22302,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="134" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L134">
         <f t="shared" si="4"/>
         <v>1965</v>
@@ -22327,7 +22312,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="135" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L135">
         <f t="shared" si="4"/>
         <v>1966</v>
@@ -22337,7 +22322,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="136" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L136">
         <f t="shared" si="4"/>
         <v>1967</v>
@@ -22347,7 +22332,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="137" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L137">
         <f t="shared" si="4"/>
         <v>1968</v>
@@ -22357,7 +22342,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="138" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L138">
         <f t="shared" si="4"/>
         <v>1969</v>
@@ -22367,7 +22352,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="139" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L139">
         <f t="shared" si="4"/>
         <v>1970</v>
@@ -22377,7 +22362,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="140" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L140">
         <f t="shared" si="4"/>
         <v>1971</v>
@@ -22387,7 +22372,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="141" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L141">
         <f t="shared" si="4"/>
         <v>1972</v>
@@ -22397,7 +22382,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="142" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L142">
         <f t="shared" si="4"/>
         <v>1973</v>
@@ -22407,7 +22392,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="143" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L143">
         <f t="shared" si="4"/>
         <v>1974</v>
@@ -22417,7 +22402,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="144" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L144">
         <f t="shared" si="4"/>
         <v>1975</v>
@@ -22427,7 +22412,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="145" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L145">
         <f t="shared" si="4"/>
         <v>1976</v>
@@ -22437,7 +22422,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="146" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L146">
         <f t="shared" si="4"/>
         <v>1977</v>
@@ -22447,7 +22432,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="147" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L147">
         <f t="shared" si="4"/>
         <v>1978</v>
@@ -22457,7 +22442,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="148" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L148">
         <f t="shared" si="4"/>
         <v>1979</v>
@@ -22467,7 +22452,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="149" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L149">
         <f t="shared" si="4"/>
         <v>1980</v>
@@ -22477,7 +22462,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="150" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L150">
         <f t="shared" si="4"/>
         <v>1981</v>
@@ -22487,7 +22472,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="151" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L151">
         <f t="shared" si="4"/>
         <v>1982</v>
@@ -22497,7 +22482,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="152" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L152">
         <f t="shared" si="4"/>
         <v>1983</v>
@@ -22507,7 +22492,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="153" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L153">
         <f t="shared" si="4"/>
         <v>1984</v>
@@ -22517,7 +22502,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="154" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L154">
         <f t="shared" si="4"/>
         <v>1985</v>
@@ -22527,7 +22512,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="155" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L155">
         <f t="shared" si="4"/>
         <v>1986</v>
@@ -22537,7 +22522,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="156" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L156">
         <f t="shared" si="4"/>
         <v>1987</v>
@@ -22547,7 +22532,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="157" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L157">
         <f t="shared" si="4"/>
         <v>1988</v>
@@ -22557,7 +22542,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="158" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L158">
         <f t="shared" si="4"/>
         <v>1989</v>
@@ -22567,7 +22552,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="159" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L159">
         <f t="shared" si="4"/>
         <v>1990</v>
@@ -22577,7 +22562,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="160" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L160">
         <f t="shared" si="4"/>
         <v>1991</v>
@@ -22587,7 +22572,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="161" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L161">
         <f t="shared" si="4"/>
         <v>1992</v>
@@ -22597,7 +22582,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="162" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L162">
         <f t="shared" si="4"/>
         <v>1993</v>
@@ -22607,7 +22592,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="163" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L163">
         <f t="shared" si="4"/>
         <v>1994</v>
@@ -22617,7 +22602,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="164" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L164">
         <f t="shared" si="4"/>
         <v>1995</v>
@@ -22627,7 +22612,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="165" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L165">
         <f t="shared" si="4"/>
         <v>1996</v>
@@ -22637,7 +22622,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="166" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L166">
         <f t="shared" si="4"/>
         <v>1997</v>
@@ -22647,7 +22632,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="167" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L167">
         <f t="shared" si="4"/>
         <v>1998</v>
@@ -22657,7 +22642,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="168" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L168">
         <f t="shared" si="4"/>
         <v>1999</v>
@@ -22667,7 +22652,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="169" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L169">
         <f t="shared" si="4"/>
         <v>2000</v>
@@ -22677,7 +22662,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="170" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L170">
         <f t="shared" si="4"/>
         <v>2001</v>
@@ -22687,7 +22672,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="171" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L171">
         <f t="shared" si="4"/>
         <v>2002</v>
@@ -22697,7 +22682,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="172" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L172">
         <f t="shared" si="4"/>
         <v>2003</v>
@@ -22707,7 +22692,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="173" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L173">
         <f t="shared" si="4"/>
         <v>2004</v>
@@ -22717,7 +22702,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="174" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L174">
         <f t="shared" si="4"/>
         <v>2005</v>
@@ -22727,7 +22712,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="175" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L175">
         <f t="shared" si="4"/>
         <v>2006</v>
@@ -22737,7 +22722,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="176" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L176">
         <f t="shared" si="4"/>
         <v>2007</v>
@@ -22747,7 +22732,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="177" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L177">
         <f t="shared" si="4"/>
         <v>2008</v>
@@ -22757,7 +22742,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="178" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L178">
         <f t="shared" si="4"/>
         <v>2009</v>
@@ -22767,7 +22752,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="179" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L179">
         <f t="shared" si="4"/>
         <v>2010</v>
@@ -22777,7 +22762,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="180" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L180">
         <f t="shared" si="4"/>
         <v>2011</v>
@@ -22787,7 +22772,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="181" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L181">
         <f t="shared" si="4"/>
         <v>2012</v>
@@ -22797,7 +22782,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="182" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L182">
         <f t="shared" si="4"/>
         <v>2013</v>
@@ -22807,7 +22792,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="183" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L183">
         <f t="shared" si="4"/>
         <v>2014</v>
@@ -22817,7 +22802,7 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="184" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L184">
         <f t="shared" si="4"/>
         <v>2015</v>
@@ -22827,7 +22812,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L185">
         <f t="shared" si="4"/>
         <v>2016</v>
@@ -22837,7 +22822,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="186" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L186">
         <f t="shared" si="4"/>
         <v>2017</v>
@@ -22847,7 +22832,7 @@
         <v>2270</v>
       </c>
     </row>
-    <row r="187" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L187">
         <f t="shared" si="4"/>
         <v>2018</v>
@@ -22857,7 +22842,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="188" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="188" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L188">
         <f t="shared" si="4"/>
         <v>2019</v>
@@ -22867,7 +22852,7 @@
         <v>2285</v>
       </c>
     </row>
-    <row r="189" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="189" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L189">
         <f t="shared" si="4"/>
         <v>2020</v>
@@ -22877,7 +22862,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="190" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="190" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L190">
         <f t="shared" si="4"/>
         <v>2021</v>
@@ -22887,7 +22872,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="191" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="191" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L191">
         <f t="shared" si="4"/>
         <v>2022</v>
@@ -22897,7 +22882,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="192" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L192">
         <f t="shared" si="4"/>
         <v>2023</v>
@@ -22907,7 +22892,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="193" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="193" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L193">
         <f t="shared" si="4"/>
         <v>2024</v>
@@ -22917,7 +22902,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="194" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="194" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L194">
         <f t="shared" si="4"/>
         <v>2025</v>
@@ -22927,7 +22912,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="195" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="195" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L195">
         <f t="shared" si="4"/>
         <v>2026</v>
@@ -22937,7 +22922,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="196" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="196" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L196">
         <f t="shared" ref="L196:L259" si="6">L195+1</f>
         <v>2027</v>
@@ -22947,7 +22932,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="197" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="197" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L197">
         <f t="shared" si="6"/>
         <v>2028</v>
@@ -22957,7 +22942,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="198" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="198" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L198">
         <f t="shared" si="6"/>
         <v>2029</v>
@@ -22967,7 +22952,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="199" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="199" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L199">
         <f t="shared" si="6"/>
         <v>2030</v>
@@ -22977,7 +22962,7 @@
         <v>2366</v>
       </c>
     </row>
-    <row r="200" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="200" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L200">
         <f t="shared" si="6"/>
         <v>2031</v>
@@ -22987,7 +22972,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="201" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="201" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L201">
         <f t="shared" si="6"/>
         <v>2032</v>
@@ -22997,7 +22982,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="202" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="202" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L202">
         <f t="shared" si="6"/>
         <v>2033</v>
@@ -23007,7 +22992,7 @@
         <v>2389</v>
       </c>
     </row>
-    <row r="203" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="203" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L203">
         <f t="shared" si="6"/>
         <v>2034</v>
@@ -23017,7 +23002,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="204" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="204" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L204">
         <f t="shared" si="6"/>
         <v>2035</v>
@@ -23027,7 +23012,7 @@
         <v>2404</v>
       </c>
     </row>
-    <row r="205" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="205" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L205">
         <f t="shared" si="6"/>
         <v>2036</v>
@@ -23037,7 +23022,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="206" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="206" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L206">
         <f t="shared" si="6"/>
         <v>2037</v>
@@ -23047,7 +23032,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="207" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="207" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L207">
         <f t="shared" si="6"/>
         <v>2038</v>
@@ -23057,7 +23042,7 @@
         <v>2426</v>
       </c>
     </row>
-    <row r="208" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="208" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L208">
         <f t="shared" si="6"/>
         <v>2039</v>
@@ -23067,7 +23052,7 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="209" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L209">
         <f t="shared" si="6"/>
         <v>2040</v>
@@ -23077,7 +23062,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="210" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L210">
         <f t="shared" si="6"/>
         <v>2041</v>
@@ -23087,7 +23072,7 @@
         <v>2448</v>
       </c>
     </row>
-    <row r="211" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L211">
         <f t="shared" si="6"/>
         <v>2042</v>
@@ -23097,7 +23082,7 @@
         <v>2455</v>
       </c>
     </row>
-    <row r="212" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="212" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L212">
         <f t="shared" si="6"/>
         <v>2043</v>
@@ -23107,7 +23092,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="213" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L213">
         <f t="shared" si="6"/>
         <v>2044</v>
@@ -23117,7 +23102,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="214" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L214">
         <f t="shared" si="6"/>
         <v>2045</v>
@@ -23127,7 +23112,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="215" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L215">
         <f t="shared" si="6"/>
         <v>2046</v>
@@ -23137,7 +23122,7 @@
         <v>2485</v>
       </c>
     </row>
-    <row r="216" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L216">
         <f t="shared" si="6"/>
         <v>2047</v>
@@ -23147,7 +23132,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="217" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L217">
         <f t="shared" si="6"/>
         <v>2048</v>
@@ -23157,7 +23142,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="218" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L218">
         <f t="shared" si="6"/>
         <v>2049</v>
@@ -23167,7 +23152,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="219" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L219">
         <f t="shared" si="6"/>
         <v>2050</v>
@@ -23177,7 +23162,7 @@
         <v>2515</v>
       </c>
     </row>
-    <row r="220" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L220">
         <f t="shared" si="6"/>
         <v>2051</v>
@@ -23187,7 +23172,7 @@
         <v>2522</v>
       </c>
     </row>
-    <row r="221" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L221">
         <f t="shared" si="6"/>
         <v>2052</v>
@@ -23197,7 +23182,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="222" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L222">
         <f t="shared" si="6"/>
         <v>2053</v>
@@ -23207,7 +23192,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="223" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L223">
         <f t="shared" si="6"/>
         <v>2054</v>
@@ -23217,7 +23202,7 @@
         <v>2545</v>
       </c>
     </row>
-    <row r="224" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L224">
         <f t="shared" si="6"/>
         <v>2055</v>
@@ -23227,7 +23212,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="225" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="225" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L225">
         <f t="shared" si="6"/>
         <v>2056</v>
@@ -23237,7 +23222,7 @@
         <v>2559</v>
       </c>
     </row>
-    <row r="226" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L226">
         <f t="shared" si="6"/>
         <v>2057</v>
@@ -23247,7 +23232,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="227" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="227" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L227">
         <f t="shared" si="6"/>
         <v>2058</v>
@@ -23257,7 +23242,7 @@
         <v>2574</v>
       </c>
     </row>
-    <row r="228" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="228" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L228">
         <f t="shared" si="6"/>
         <v>2059</v>
@@ -23267,7 +23252,7 @@
         <v>2582</v>
       </c>
     </row>
-    <row r="229" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="229" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L229">
         <f t="shared" si="6"/>
         <v>2060</v>
@@ -23277,7 +23262,7 @@
         <v>2589</v>
       </c>
     </row>
-    <row r="230" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="230" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L230">
         <f t="shared" si="6"/>
         <v>2061</v>
@@ -23287,7 +23272,7 @@
         <v>2596</v>
       </c>
     </row>
-    <row r="231" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="231" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L231">
         <f t="shared" si="6"/>
         <v>2062</v>
@@ -23297,7 +23282,7 @@
         <v>2604</v>
       </c>
     </row>
-    <row r="232" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="232" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L232">
         <f t="shared" si="6"/>
         <v>2063</v>
@@ -23307,7 +23292,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="233" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="233" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L233">
         <f t="shared" si="6"/>
         <v>2064</v>
@@ -23317,7 +23302,7 @@
         <v>2619</v>
       </c>
     </row>
-    <row r="234" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="234" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L234">
         <f t="shared" si="6"/>
         <v>2065</v>
@@ -23327,7 +23312,7 @@
         <v>2626</v>
       </c>
     </row>
-    <row r="235" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="235" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L235">
         <f t="shared" si="6"/>
         <v>2066</v>
@@ -23337,7 +23322,7 @@
         <v>2634</v>
       </c>
     </row>
-    <row r="236" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="236" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L236">
         <f t="shared" si="6"/>
         <v>2067</v>
@@ -23347,7 +23332,7 @@
         <v>2641</v>
       </c>
     </row>
-    <row r="237" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="237" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L237">
         <f t="shared" si="6"/>
         <v>2068</v>
@@ -23357,7 +23342,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="238" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="238" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L238">
         <f t="shared" si="6"/>
         <v>2069</v>
@@ -23367,7 +23352,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="239" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="239" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L239">
         <f t="shared" si="6"/>
         <v>2070</v>
@@ -23377,7 +23362,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="240" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="240" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L240">
         <f t="shared" si="6"/>
         <v>2071</v>
@@ -23387,7 +23372,7 @@
         <v>2671</v>
       </c>
     </row>
-    <row r="241" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="241" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L241">
         <f t="shared" si="6"/>
         <v>2072</v>
@@ -23397,7 +23382,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="242" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="242" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L242">
         <f t="shared" si="6"/>
         <v>2073</v>
@@ -23407,7 +23392,7 @@
         <v>2685</v>
       </c>
     </row>
-    <row r="243" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="243" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L243">
         <f t="shared" si="6"/>
         <v>2074</v>
@@ -23417,7 +23402,7 @@
         <v>2693</v>
       </c>
     </row>
-    <row r="244" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="244" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L244">
         <f t="shared" si="6"/>
         <v>2075</v>
@@ -23427,7 +23412,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="245" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="245" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L245">
         <f t="shared" si="6"/>
         <v>2076</v>
@@ -23437,7 +23422,7 @@
         <v>2708</v>
       </c>
     </row>
-    <row r="246" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="246" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L246">
         <f t="shared" si="6"/>
         <v>2077</v>
@@ -23447,7 +23432,7 @@
         <v>2715</v>
       </c>
     </row>
-    <row r="247" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="247" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L247">
         <f t="shared" si="6"/>
         <v>2078</v>
@@ -23457,7 +23442,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="248" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="248" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L248">
         <f t="shared" si="6"/>
         <v>2079</v>
@@ -23467,7 +23452,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="249" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="249" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L249">
         <f t="shared" si="6"/>
         <v>2080</v>
@@ -23477,7 +23462,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="250" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="250" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L250">
         <f t="shared" si="6"/>
         <v>2081</v>
@@ -23487,7 +23472,7 @@
         <v>2745</v>
       </c>
     </row>
-    <row r="251" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="251" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L251">
         <f t="shared" si="6"/>
         <v>2082</v>
@@ -23497,7 +23482,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="252" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="252" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L252">
         <f t="shared" si="6"/>
         <v>2083</v>
@@ -23507,7 +23492,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="253" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="253" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L253">
         <f t="shared" si="6"/>
         <v>2084</v>
@@ -23517,7 +23502,7 @@
         <v>2767</v>
       </c>
     </row>
-    <row r="254" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="254" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L254">
         <f t="shared" si="6"/>
         <v>2085</v>
@@ -23527,7 +23512,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="255" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="255" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L255">
         <f t="shared" si="6"/>
         <v>2086</v>
@@ -23537,7 +23522,7 @@
         <v>2782</v>
       </c>
     </row>
-    <row r="256" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="256" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L256">
         <f t="shared" si="6"/>
         <v>2087</v>
@@ -23547,7 +23532,7 @@
         <v>2789</v>
       </c>
     </row>
-    <row r="257" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="257" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L257">
         <f t="shared" si="6"/>
         <v>2088</v>
@@ -23557,7 +23542,7 @@
         <v>2797</v>
       </c>
     </row>
-    <row r="258" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="258" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L258">
         <f t="shared" si="6"/>
         <v>2089</v>
@@ -23567,7 +23552,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="259" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="259" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L259">
         <f t="shared" si="6"/>
         <v>2090</v>
@@ -23577,7 +23562,7 @@
         <v>2812</v>
       </c>
     </row>
-    <row r="260" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="260" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L260">
         <f t="shared" ref="L260:L323" si="8">L259+1</f>
         <v>2091</v>
@@ -23587,7 +23572,7 @@
         <v>2819</v>
       </c>
     </row>
-    <row r="261" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="261" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L261">
         <f t="shared" si="8"/>
         <v>2092</v>
@@ -23597,7 +23582,7 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="262" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="262" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L262">
         <f t="shared" si="8"/>
         <v>2093</v>
@@ -23607,7 +23592,7 @@
         <v>2834</v>
       </c>
     </row>
-    <row r="263" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="263" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L263">
         <f t="shared" si="8"/>
         <v>2094</v>
@@ -23617,7 +23602,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="264" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="264" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L264">
         <f t="shared" si="8"/>
         <v>2095</v>
@@ -23627,7 +23612,7 @@
         <v>2849</v>
       </c>
     </row>
-    <row r="265" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="265" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L265">
         <f t="shared" si="8"/>
         <v>2096</v>
@@ -23637,7 +23622,7 @@
         <v>2856</v>
       </c>
     </row>
-    <row r="266" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="266" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L266">
         <f t="shared" si="8"/>
         <v>2097</v>
@@ -23647,7 +23632,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="267" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="267" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L267">
         <f t="shared" si="8"/>
         <v>2098</v>
@@ -23657,7 +23642,7 @@
         <v>2871</v>
       </c>
     </row>
-    <row r="268" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="268" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L268">
         <f t="shared" si="8"/>
         <v>2099</v>
@@ -23667,7 +23652,7 @@
         <v>2878</v>
       </c>
     </row>
-    <row r="269" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="269" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L269">
         <f t="shared" si="8"/>
         <v>2100</v>
@@ -23677,7 +23662,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="270" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="270" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L270">
         <f t="shared" si="8"/>
         <v>2101</v>
@@ -23687,7 +23672,7 @@
         <v>2893</v>
       </c>
     </row>
-    <row r="271" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="271" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L271">
         <f t="shared" si="8"/>
         <v>2102</v>
@@ -23697,7 +23682,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="272" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="272" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L272">
         <f t="shared" si="8"/>
         <v>2103</v>
@@ -23707,7 +23692,7 @@
         <v>2908</v>
       </c>
     </row>
-    <row r="273" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="273" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L273">
         <f t="shared" si="8"/>
         <v>2104</v>
@@ -23717,7 +23702,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="274" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="274" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L274">
         <f t="shared" si="8"/>
         <v>2105</v>
@@ -23727,7 +23712,7 @@
         <v>2923</v>
       </c>
     </row>
-    <row r="275" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="275" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L275">
         <f t="shared" si="8"/>
         <v>2106</v>
@@ -23737,7 +23722,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="276" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="276" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L276">
         <f t="shared" si="8"/>
         <v>2107</v>
@@ -23747,7 +23732,7 @@
         <v>2938</v>
       </c>
     </row>
-    <row r="277" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="277" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L277">
         <f t="shared" si="8"/>
         <v>2108</v>
@@ -23757,7 +23742,7 @@
         <v>2945</v>
       </c>
     </row>
-    <row r="278" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="278" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L278">
         <f t="shared" si="8"/>
         <v>2109</v>
@@ -23767,7 +23752,7 @@
         <v>2953</v>
       </c>
     </row>
-    <row r="279" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="279" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L279">
         <f t="shared" si="8"/>
         <v>2110</v>
@@ -23777,7 +23762,7 @@
         <v>2960</v>
       </c>
     </row>
-    <row r="280" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="280" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L280">
         <f t="shared" si="8"/>
         <v>2111</v>
@@ -23787,7 +23772,7 @@
         <v>2967</v>
       </c>
     </row>
-    <row r="281" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="281" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L281">
         <f t="shared" si="8"/>
         <v>2112</v>
@@ -23797,7 +23782,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="282" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="282" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L282">
         <f t="shared" si="8"/>
         <v>2113</v>
@@ -23807,7 +23792,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="283" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="283" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L283">
         <f t="shared" si="8"/>
         <v>2114</v>
@@ -23817,7 +23802,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="284" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="284" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L284">
         <f t="shared" si="8"/>
         <v>2115</v>
@@ -23827,7 +23812,7 @@
         <v>2997</v>
       </c>
     </row>
-    <row r="285" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="285" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L285">
         <f t="shared" si="8"/>
         <v>2116</v>
@@ -23837,7 +23822,7 @@
         <v>3004</v>
       </c>
     </row>
-    <row r="286" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="286" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L286">
         <f t="shared" si="8"/>
         <v>2117</v>
@@ -23847,7 +23832,7 @@
         <v>3012</v>
       </c>
     </row>
-    <row r="287" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="287" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L287">
         <f t="shared" si="8"/>
         <v>2118</v>
@@ -23857,7 +23842,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="288" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="288" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L288">
         <f t="shared" si="8"/>
         <v>2119</v>
@@ -23867,7 +23852,7 @@
         <v>3027</v>
       </c>
     </row>
-    <row r="289" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="289" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L289">
         <f t="shared" si="8"/>
         <v>2120</v>
@@ -23877,7 +23862,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="290" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="290" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L290">
         <f t="shared" si="8"/>
         <v>2121</v>
@@ -23887,7 +23872,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="291" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="291" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L291">
         <f t="shared" si="8"/>
         <v>2122</v>
@@ -23897,7 +23882,7 @@
         <v>3049</v>
       </c>
     </row>
-    <row r="292" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="292" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L292">
         <f t="shared" si="8"/>
         <v>2123</v>
@@ -23907,7 +23892,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="293" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="293" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L293">
         <f t="shared" si="8"/>
         <v>2124</v>
@@ -23917,7 +23902,7 @@
         <v>3064</v>
       </c>
     </row>
-    <row r="294" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="294" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L294">
         <f t="shared" si="8"/>
         <v>2125</v>
@@ -23927,7 +23912,7 @@
         <v>3071</v>
       </c>
     </row>
-    <row r="295" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="295" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L295">
         <f t="shared" si="8"/>
         <v>2126</v>
@@ -23937,7 +23922,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="296" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="296" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L296">
         <f t="shared" si="8"/>
         <v>2127</v>
@@ -23947,7 +23932,7 @@
         <v>3086</v>
       </c>
     </row>
-    <row r="297" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="297" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L297">
         <f t="shared" si="8"/>
         <v>2128</v>
@@ -23957,7 +23942,7 @@
         <v>3093</v>
       </c>
     </row>
-    <row r="298" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="298" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L298">
         <f t="shared" si="8"/>
         <v>2129</v>
@@ -23967,7 +23952,7 @@
         <v>3101</v>
       </c>
     </row>
-    <row r="299" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="299" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L299">
         <f t="shared" si="8"/>
         <v>2130</v>
@@ -23977,7 +23962,7 @@
         <v>3108</v>
       </c>
     </row>
-    <row r="300" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="300" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L300">
         <f t="shared" si="8"/>
         <v>2131</v>
@@ -23987,7 +23972,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="301" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="301" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L301">
         <f t="shared" si="8"/>
         <v>2132</v>
@@ -23997,7 +23982,7 @@
         <v>3123</v>
       </c>
     </row>
-    <row r="302" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="302" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L302">
         <f t="shared" si="8"/>
         <v>2133</v>
@@ -24007,7 +23992,7 @@
         <v>3131</v>
       </c>
     </row>
-    <row r="303" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="303" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L303">
         <f t="shared" si="8"/>
         <v>2134</v>
@@ -24017,7 +24002,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="304" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="304" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L304">
         <f t="shared" si="8"/>
         <v>2135</v>
@@ -24027,7 +24012,7 @@
         <v>3145</v>
       </c>
     </row>
-    <row r="305" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="305" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L305">
         <f t="shared" si="8"/>
         <v>2136</v>
@@ -24037,7 +24022,7 @@
         <v>3153</v>
       </c>
     </row>
-    <row r="306" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="306" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L306">
         <f t="shared" si="8"/>
         <v>2137</v>
@@ -24047,7 +24032,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="307" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="307" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L307">
         <f t="shared" si="8"/>
         <v>2138</v>
@@ -24057,7 +24042,7 @@
         <v>3168</v>
       </c>
     </row>
-    <row r="308" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="308" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L308">
         <f t="shared" si="8"/>
         <v>2139</v>
@@ -24067,7 +24052,7 @@
         <v>3175</v>
       </c>
     </row>
-    <row r="309" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="309" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L309">
         <f t="shared" si="8"/>
         <v>2140</v>
@@ -24077,7 +24062,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="310" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="310" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L310">
         <f t="shared" si="8"/>
         <v>2141</v>
@@ -24087,7 +24072,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="311" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="311" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L311">
         <f t="shared" si="8"/>
         <v>2142</v>
@@ -24097,7 +24082,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="312" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="312" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L312">
         <f t="shared" si="8"/>
         <v>2143</v>
@@ -24107,7 +24092,7 @@
         <v>3205</v>
       </c>
     </row>
-    <row r="313" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="313" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L313">
         <f t="shared" si="8"/>
         <v>2144</v>
@@ -24117,7 +24102,7 @@
         <v>3212</v>
       </c>
     </row>
-    <row r="314" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="314" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L314">
         <f t="shared" si="8"/>
         <v>2145</v>
@@ -24127,7 +24112,7 @@
         <v>3220</v>
       </c>
     </row>
-    <row r="315" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="315" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L315">
         <f t="shared" si="8"/>
         <v>2146</v>
@@ -24137,7 +24122,7 @@
         <v>3227</v>
       </c>
     </row>
-    <row r="316" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="316" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L316">
         <f t="shared" si="8"/>
         <v>2147</v>
@@ -24147,7 +24132,7 @@
         <v>3234</v>
       </c>
     </row>
-    <row r="317" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="317" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L317">
         <f t="shared" si="8"/>
         <v>2148</v>
@@ -24157,7 +24142,7 @@
         <v>3242</v>
       </c>
     </row>
-    <row r="318" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="318" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L318">
         <f t="shared" si="8"/>
         <v>2149</v>
@@ -24167,7 +24152,7 @@
         <v>3249</v>
       </c>
     </row>
-    <row r="319" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="319" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L319">
         <f t="shared" si="8"/>
         <v>2150</v>
@@ -24177,7 +24162,7 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="320" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="320" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L320">
         <f t="shared" si="8"/>
         <v>2151</v>
@@ -24187,7 +24172,7 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="321" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="321" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L321">
         <f t="shared" si="8"/>
         <v>2152</v>
@@ -24197,7 +24182,7 @@
         <v>3272</v>
       </c>
     </row>
-    <row r="322" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="322" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L322">
         <f t="shared" si="8"/>
         <v>2153</v>
@@ -24207,7 +24192,7 @@
         <v>3279</v>
       </c>
     </row>
-    <row r="323" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="323" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L323">
         <f t="shared" si="8"/>
         <v>2154</v>
@@ -24217,7 +24202,7 @@
         <v>3286</v>
       </c>
     </row>
-    <row r="324" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="324" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L324">
         <f t="shared" ref="L324:L336" si="10">L323+1</f>
         <v>2155</v>
@@ -24227,7 +24212,7 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="325" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="325" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L325">
         <f t="shared" si="10"/>
         <v>2156</v>
@@ -24237,7 +24222,7 @@
         <v>3301</v>
       </c>
     </row>
-    <row r="326" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="326" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L326">
         <f t="shared" si="10"/>
         <v>2157</v>
@@ -24247,7 +24232,7 @@
         <v>3309</v>
       </c>
     </row>
-    <row r="327" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="327" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L327">
         <f t="shared" si="10"/>
         <v>2158</v>
@@ -24257,7 +24242,7 @@
         <v>3316</v>
       </c>
     </row>
-    <row r="328" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="328" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L328">
         <f t="shared" si="10"/>
         <v>2159</v>
@@ -24267,7 +24252,7 @@
         <v>3323</v>
       </c>
     </row>
-    <row r="329" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="329" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L329">
         <f t="shared" si="10"/>
         <v>2160</v>
@@ -24277,7 +24262,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="330" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="330" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L330">
         <f t="shared" si="10"/>
         <v>2161</v>
@@ -24287,7 +24272,7 @@
         <v>3338</v>
       </c>
     </row>
-    <row r="331" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="331" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L331">
         <f t="shared" si="10"/>
         <v>2162</v>
@@ -24297,7 +24282,7 @@
         <v>3346</v>
       </c>
     </row>
-    <row r="332" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="332" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L332">
         <f t="shared" si="10"/>
         <v>2163</v>
@@ -24307,7 +24292,7 @@
         <v>3353</v>
       </c>
     </row>
-    <row r="333" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="333" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L333">
         <f t="shared" si="10"/>
         <v>2164</v>
@@ -24317,7 +24302,7 @@
         <v>3361</v>
       </c>
     </row>
-    <row r="334" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="334" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L334">
         <f t="shared" si="10"/>
         <v>2165</v>
@@ -24327,7 +24312,7 @@
         <v>3368</v>
       </c>
     </row>
-    <row r="335" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="335" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L335">
         <f t="shared" si="10"/>
         <v>2166</v>
@@ -24337,7 +24322,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="336" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="336" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L336">
         <f t="shared" si="10"/>
         <v>2167</v>
@@ -24356,12 +24341,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B976ED82-D377-452B-98DC-3515CED81A81}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C1" t="s">
         <v>325</v>
       </c>
@@ -24369,7 +24354,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -24380,7 +24365,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -24394,7 +24379,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -24408,7 +24393,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -24422,7 +24407,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>86</v>
       </c>
@@ -24436,7 +24421,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>168</v>
       </c>
@@ -24450,7 +24435,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -24464,7 +24449,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>85</v>
       </c>
@@ -24489,14 +24474,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A66C56-C25D-4E4C-815E-A8416CC0CC5B}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>64</v>
       </c>
@@ -24504,7 +24489,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>56</v>
       </c>
@@ -24512,7 +24497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>180</v>
       </c>
@@ -24520,7 +24505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>181</v>
       </c>
@@ -24528,7 +24513,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>188</v>
       </c>
@@ -24536,12 +24521,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>183</v>
       </c>
@@ -24549,7 +24534,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>184</v>
       </c>
@@ -24557,7 +24542,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>185</v>
       </c>
@@ -24565,7 +24550,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>186</v>
       </c>
@@ -24573,7 +24558,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>187</v>
       </c>
@@ -24581,7 +24566,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>189</v>
       </c>
@@ -24597,12 +24582,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F1D77F-0E43-499A-A11C-88B275139916}">
   <dimension ref="A1:J61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="10" width="14.44140625" customWidth="1"/>
+    <col min="3" max="10" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>90</v>
       </c>
@@ -24634,7 +24619,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -24660,7 +24645,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -24686,7 +24671,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>7</v>
       </c>
@@ -24706,7 +24691,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>8</v>
       </c>
@@ -24738,7 +24723,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>9</v>
       </c>
@@ -24770,7 +24755,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>10</v>
       </c>
@@ -24796,7 +24781,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>11</v>
       </c>
@@ -24825,7 +24810,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>14</v>
       </c>
@@ -24854,7 +24839,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>19</v>
       </c>
@@ -24877,7 +24862,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>20</v>
       </c>
@@ -24909,7 +24894,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>21</v>
       </c>
@@ -24941,7 +24926,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>22</v>
       </c>
@@ -24970,7 +24955,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>34</v>
       </c>
@@ -24996,7 +24981,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>35</v>
       </c>
@@ -25022,7 +25007,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>36</v>
       </c>
@@ -25045,7 +25030,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>37</v>
       </c>
@@ -25074,7 +25059,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>38</v>
       </c>
@@ -25103,7 +25088,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>39</v>
       </c>
@@ -25129,7 +25114,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>40</v>
       </c>
@@ -25155,7 +25140,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>41</v>
       </c>
@@ -25166,7 +25151,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>42</v>
       </c>
@@ -25177,7 +25162,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>46</v>
       </c>
@@ -25200,7 +25185,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>47</v>
       </c>
@@ -25229,7 +25214,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>53</v>
       </c>
@@ -25258,7 +25243,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>54</v>
       </c>
@@ -25287,7 +25272,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>55</v>
       </c>
@@ -25310,7 +25295,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>59</v>
       </c>
@@ -25336,7 +25321,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>60</v>
       </c>
@@ -25362,7 +25347,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>3</v>
       </c>
@@ -25388,7 +25373,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>4</v>
       </c>
@@ -25408,7 +25393,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>5</v>
       </c>
@@ -25428,7 +25413,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>6</v>
       </c>
@@ -25457,7 +25442,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>12</v>
       </c>
@@ -25477,7 +25462,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>13</v>
       </c>
@@ -25497,7 +25482,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>15</v>
       </c>
@@ -25526,7 +25511,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>16</v>
       </c>
@@ -25555,7 +25540,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>17</v>
       </c>
@@ -25578,7 +25563,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>18</v>
       </c>
@@ -25601,7 +25586,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>23</v>
       </c>
@@ -25630,7 +25615,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>24</v>
       </c>
@@ -25659,7 +25644,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>25</v>
       </c>
@@ -25679,7 +25664,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>26</v>
       </c>
@@ -25699,7 +25684,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>27</v>
       </c>
@@ -25719,7 +25704,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>28</v>
       </c>
@@ -25739,7 +25724,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>29</v>
       </c>
@@ -25759,7 +25744,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>30</v>
       </c>
@@ -25779,7 +25764,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>31</v>
       </c>
@@ -25805,7 +25790,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>32</v>
       </c>
@@ -25828,7 +25813,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>33</v>
       </c>
@@ -25851,7 +25836,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>43</v>
       </c>
@@ -25874,7 +25859,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>44</v>
       </c>
@@ -25897,7 +25882,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>45</v>
       </c>
@@ -25920,7 +25905,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>48</v>
       </c>
@@ -25949,7 +25934,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>49</v>
       </c>
@@ -25963,7 +25948,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>50</v>
       </c>
@@ -25977,7 +25962,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>51</v>
       </c>
@@ -25994,7 +25979,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>52</v>
       </c>
@@ -26020,7 +26005,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>56</v>
       </c>
@@ -26037,7 +26022,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>57</v>
       </c>
@@ -26060,7 +26045,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>58</v>
       </c>

--- a/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
+++ b/sw/src/MSPM0_Pins_AssignmentsLab7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghakk\ece445l_lab7-10_fall26-4-ew-js-tp-ak\sw\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5557FAB4-C80B-4455-A2E2-56555B9F6CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0600022-1FFE-4E09-A523-ADF0C02DC7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,20 @@
     <sheet name="ADC" sheetId="12" r:id="rId6"/>
     <sheet name="PINCM" sheetId="11" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1196,9 +1209,6 @@
   </si>
   <si>
     <t>Keypad Input 4</t>
-  </si>
-  <si>
-    <t>Flywheels</t>
   </si>
   <si>
     <t>NC</t>
@@ -1297,13 +1307,16 @@
     <t>S</t>
   </si>
   <si>
-    <t>LED Group 1</t>
-  </si>
-  <si>
     <t>LED Group 2</t>
   </si>
   <si>
     <t>Motor PWM</t>
+  </si>
+  <si>
+    <t>Winch+</t>
+  </si>
+  <si>
+    <t>Winch-</t>
   </si>
 </sst>
 </file>
@@ -12827,7 +12840,7 @@
       </c>
       <c r="G1" s="7"/>
       <c r="I1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -12849,10 +12862,10 @@
         <v>0</v>
       </c>
       <c r="G2" s="55" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -12876,7 +12889,7 @@
         <v>213</v>
       </c>
       <c r="I3" s="42" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -12898,7 +12911,7 @@
         <v>387</v>
       </c>
       <c r="I4" s="47" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -12922,7 +12935,7 @@
         <v>376</v>
       </c>
       <c r="I5" s="51" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -12946,12 +12959,12 @@
         <v>377</v>
       </c>
       <c r="I6" s="52" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="58" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>172</v>
@@ -12970,12 +12983,12 @@
         <v>158</v>
       </c>
       <c r="I7" s="53" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="67" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>173</v>
@@ -12994,12 +13007,12 @@
         <v>156</v>
       </c>
       <c r="I8" s="59" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="68" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>174</v>
@@ -13018,7 +13031,7 @@
         <v>209</v>
       </c>
       <c r="I9" s="60" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -13042,7 +13055,7 @@
         <v>208</v>
       </c>
       <c r="I10" s="62" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -13063,10 +13076,10 @@
         <v>153</v>
       </c>
       <c r="G11" s="54" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I11" s="64" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -13090,7 +13103,7 @@
         <v>362</v>
       </c>
       <c r="I12" s="57" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -13114,7 +13127,7 @@
         <v>373</v>
       </c>
       <c r="I13" s="66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -13138,7 +13151,7 @@
         <v>212</v>
       </c>
       <c r="I14" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -13215,7 +13228,7 @@
     </row>
     <row r="18" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -13309,7 +13322,7 @@
     </row>
     <row r="23" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A23" s="49" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>37</v>
@@ -13325,7 +13338,7 @@
         <v>19</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
@@ -13333,7 +13346,7 @@
     </row>
     <row r="24" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A24" s="65" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>38</v>
@@ -13348,8 +13361,8 @@
       <c r="F24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G24" s="64" t="s">
-        <v>415</v>
+      <c r="G24" s="51" t="s">
+        <v>417</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
@@ -13357,7 +13370,7 @@
     </row>
     <row r="25" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A25" s="58" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>172</v>
@@ -13381,7 +13394,7 @@
     </row>
     <row r="26" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A26" s="67" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>173</v>
@@ -13405,7 +13418,7 @@
     </row>
     <row r="27" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A27" s="68" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>174</v>
@@ -13453,7 +13466,7 @@
     </row>
     <row r="29" spans="1:1023 1029:2047 2053:3071 3077:4095 4101:5119 5125:6143 6149:7167 7173:8191 8197:9215 9221:10239 10245:11263 11269:12287 12293:13311 13317:14335 14341:15359 15365:16375" x14ac:dyDescent="0.35">
       <c r="A29" s="58" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>10</v>
@@ -13514,7 +13527,7 @@
         <v>39</v>
       </c>
       <c r="G31" s="64" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -19678,7 +19691,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="58" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>14</v>
@@ -19741,7 +19754,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B36"/>
     </row>
@@ -19782,7 +19795,7 @@
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
